--- a/tame_output/ON/bt/strategyON_20240928.xlsx
+++ b/tame_output/ON/bt/strategyON_20240928.xlsx
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607648</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.82855148672282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279187</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.78093391139299</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632784</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496263</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205897</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896929</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389349</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378392</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814669</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423391</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.82103066007763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121465</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906078</v>
+        <v>3.77523303390608</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912983</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539893</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811007</v>
+        <v>3.725010844811009</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382918</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013426</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660853</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395089</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791152</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620436</v>
+        <v>3.699115615620438</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285649</v>
+        <v>3.708182519285651</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399472</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437332</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298398</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353537</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.73682287011328</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113689</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016443</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.794705093307674</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863555</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883677</v>
+        <v>3.713762536883679</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236299</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427684</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610385</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667455</v>
+        <v>3.715544411667457</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889191</v>
+        <v>3.673978374889193</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.682476099409568</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762288</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.633213467988019</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740923</v>
+        <v>3.647907242740925</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663629</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.717071158424773</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149219</v>
+        <v>3.741942347149221</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383093</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720999</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455272</v>
+        <v>3.775357097455274</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963133</v>
+        <v>3.749078058963135</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162543</v>
+        <v>3.740284389162545</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652384</v>
+        <v>3.782482115652385</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108672</v>
+        <v>3.809055905108674</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103563</v>
+        <v>3.835202441103565</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047745</v>
+        <v>3.821827147047747</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650754</v>
+        <v>3.825268416650756</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
@@ -49730,7 +49730,7 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135749</v>
+        <v>3.845044666135751</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
@@ -49753,7 +49753,7 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479222</v>
+        <v>3.825931790479224</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
@@ -49776,7 +49776,7 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844247</v>
+        <v>3.847096478844248</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
@@ -49799,7 +49799,7 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.83242598779095</v>
+        <v>3.832425987790952</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
@@ -49822,7 +49822,7 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578996</v>
+        <v>3.861579399578998</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.836459310407268</v>
+        <v>3.836459310407269</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.352465646068676</v>
+        <v>-4.352503709059398</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.16860090088458</v>
+        <v>3.168585675688291</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.411719206959323</v>
+        <v>1.411681143968602</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.756975107801392</v>
+        <v>5.75695227000696</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240928.xlsx
+++ b/tame_output/ON/bt/strategyON_20240928.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.3%</t>
+          <t>421.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-596.8%</t>
+          <t>-592.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-59.4%</t>
+          <t>-57.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-297.3%</t>
+          <t>-295.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-82.8%</t>
+          <t>-83.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.4%</t>
+          <t>129.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>117.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>129.7%</t>
+          <t>129.4%</t>
         </is>
       </c>
     </row>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607648</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987905</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82855148672282</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279187</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.78093391139299</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632784</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883076</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496263</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111296</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532489</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397797</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316252</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896929</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347707</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.71289761234307</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389353</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787389</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814669</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423391</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
@@ -48011,10 +48011,10 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.051394179726834</v>
+        <v>-4.9985334175363</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.45508027219607</v>
+        <v>1.476224577072284</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1795924902331102</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.238058307861643</v>
+        <v>-5.185197545671108</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.384536363169468</v>
+        <v>1.405680668045682</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1528535194085503</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.384078994775605</v>
+        <v>-5.33121823258507</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.321205941140073</v>
+        <v>1.342350246016287</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1437704276146933</v>
@@ -48080,10 +48080,10 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.47579300388519</v>
+        <v>-5.422932241694655</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.446724394195283</v>
+        <v>1.467868699071497</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1437704276146933</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.50744466294516</v>
+        <v>-5.454583900754624</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.428910368535109</v>
+        <v>1.450054673411323</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1386019703702531</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.576510717518096</v>
+        <v>-5.523649955327561</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.411513364274426</v>
+        <v>1.43265766915064</v>
       </c>
       <c r="F2025" t="n">
         <v>0.07623109287664309</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.678486839766504</v>
+        <v>-5.625626077575968</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.379648553830965</v>
+        <v>1.400792858707179</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.02574502937176448</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.568480556289282</v>
+        <v>-5.515619794098747</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.415803954466029</v>
+        <v>1.436948259342243</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.002540457454489276</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.425420980548356</v>
+        <v>-5.372560218357821</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.477277795484374</v>
+        <v>1.498422100360588</v>
       </c>
       <c r="F2028" t="n">
         <v>0.005472969135490002</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.123974255076519</v>
+        <v>-5.071113492885983</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.605117368555645</v>
+        <v>1.626261673431859</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3069196946073273</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.148564499311703</v>
+        <v>-5.095703737121167</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.596252448614282</v>
+        <v>1.617396753490496</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3069196946073273</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.097526123305182</v>
+        <v>-5.044665361114647</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.617510703396646</v>
+        <v>1.63865500827286</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3069196946073273</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.068677446481722</v>
+        <v>-5.015816684291186</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.648088273000175</v>
+        <v>1.669232577876389</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3357683714307875</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.972042534463082</v>
+        <v>-4.919181772272546</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.502926233931566</v>
+        <v>1.52407053880778</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4324032834494275</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.903004523514614</v>
+        <v>-4.850143761324079</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.534043482384917</v>
+        <v>1.555187787261131</v>
       </c>
       <c r="F2034" t="n">
         <v>0.5014412943978955</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.738508189323652</v>
+        <v>-4.685647427133117</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.584268835137384</v>
+        <v>1.605413140013598</v>
       </c>
       <c r="F2035" t="n">
         <v>0.6659376285888574</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.82103066007763</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.66140958778178</v>
+        <v>-4.608548825591244</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.614295986190563</v>
+        <v>1.635440291066777</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6659376285888574</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147912</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.671794782671669</v>
+        <v>-4.618934020481134</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.62001068735968</v>
+        <v>1.641154992235894</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6555524336989681</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.690382941393894</v>
+        <v>-4.637522179203359</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.683412429647215</v>
+        <v>1.704556734523429</v>
       </c>
       <c r="F2038" t="n">
         <v>0.6369642749767428</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.69068148808993</v>
+        <v>-4.637820725899394</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.680162021787099</v>
+        <v>1.701306326663313</v>
       </c>
       <c r="F2039" t="n">
         <v>0.6366657282807069</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.589858354399502</v>
+        <v>-4.536997592208967</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.725022170202661</v>
+        <v>1.746166475078876</v>
       </c>
       <c r="F2040" t="n">
         <v>0.6491299437650607</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.399076993647094</v>
+        <v>-4.346216231456559</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.801463967982168</v>
+        <v>1.822608272858382</v>
       </c>
       <c r="F2041" t="n">
         <v>0.8399113045174681</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.77523303390608</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.292113635797673</v>
+        <v>-4.239252873607137</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.824086156859533</v>
+        <v>1.845230461735747</v>
       </c>
       <c r="F2042" t="n">
         <v>0.8983759124772696</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.23678304789591</v>
+        <v>-4.183922285705375</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.881185328632296</v>
+        <v>1.902329633508511</v>
       </c>
       <c r="F2043" t="n">
         <v>0.9537065003790317</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.224728920982947</v>
+        <v>-4.171868158792412</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.879693547298919</v>
+        <v>1.900837852175133</v>
       </c>
       <c r="F2044" t="n">
         <v>0.9657606272919945</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811009</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.265884040551168</v>
+        <v>-4.213023278360633</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.865112129655767</v>
+        <v>1.886256434531981</v>
       </c>
       <c r="F2045" t="n">
         <v>0.9246055077237736</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.197835477859639</v>
+        <v>-4.144974715669103</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.905182580610261</v>
+        <v>1.926326885486476</v>
       </c>
       <c r="F2046" t="n">
         <v>0.9926540704153033</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013426</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.429435871029139</v>
+        <v>-4.376575108838604</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.832745093516055</v>
+        <v>1.853889398392269</v>
       </c>
       <c r="F2047" t="n">
         <v>0.9926540704153033</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498971</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.479487416558358</v>
+        <v>-4.426626654367823</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.79633071137125</v>
+        <v>1.817475016247464</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9926540704153033</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.6700487028001</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.654594249134803</v>
+        <v>-4.601733486944267</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.686539891934138</v>
+        <v>1.707684196810352</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9926540704153033</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660853</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.45849409570428</v>
+        <v>-4.405633333513745</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.772002572303288</v>
+        <v>1.793146877179502</v>
       </c>
       <c r="F2050" t="n">
         <v>1.188754223845826</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.305468703590996</v>
+        <v>-4.25260794140046</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.932383728721506</v>
+        <v>1.95352803359772</v>
       </c>
       <c r="F2051" t="n">
         <v>1.34177961595911</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791152</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.333776017464266</v>
+        <v>-4.28091525527373</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.10852702808049</v>
+        <v>2.129671332956704</v>
       </c>
       <c r="F2052" t="n">
         <v>1.34177961595911</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620438</v>
+        <v>3.699115615620436</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.500369242577788</v>
+        <v>-4.447508480387253</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.011292689389164</v>
+        <v>2.032436994265378</v>
       </c>
       <c r="F2053" t="n">
         <v>1.175186390845588</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285651</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.477333449216222</v>
+        <v>-4.424472687025687</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.024183409395508</v>
+        <v>2.045327714271722</v>
       </c>
       <c r="F2054" t="n">
         <v>1.175186390845588</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.448087468760526</v>
+        <v>-4.39522670656999</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.033499856701282</v>
+        <v>2.054644161577496</v>
       </c>
       <c r="F2055" t="n">
         <v>1.175186390845588</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256375</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.555013016638377</v>
+        <v>-4.502152254447841</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.988022876707777</v>
+        <v>2.009167181583991</v>
       </c>
       <c r="F2056" t="n">
         <v>1.068260842967736</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600701005</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.700031575145625</v>
+        <v>-4.64717081295509</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.931444255448111</v>
+        <v>1.952588560324326</v>
       </c>
       <c r="F2057" t="n">
         <v>0.9232422844604879</v>
@@ -48879,16 +48879,16 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687016</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.818373340930343</v>
+        <v>-4.765512578739807</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.984038788391977</v>
+        <v>2.005183093268192</v>
       </c>
       <c r="F2058" t="n">
         <v>0.933928323023378</v>
@@ -48902,16 +48902,16 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790805</v>
+        <v>3.714879051790808</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.869783763251051</v>
+        <v>-4.816923001060515</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.961260316589633</v>
+        <v>1.982404621465848</v>
       </c>
       <c r="F2059" t="n">
         <v>0.933928323023378</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437332</v>
+        <v>3.704757949437336</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.949203214458803</v>
+        <v>-4.896342452268267</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.929395664180822</v>
+        <v>1.950539969057036</v>
       </c>
       <c r="F2060" t="n">
         <v>0.933928323023378</v>
@@ -48948,16 +48948,16 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298404</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.04466621237602</v>
+        <v>-4.991805450185485</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.891204358571978</v>
+        <v>1.912348663448192</v>
       </c>
       <c r="F2061" t="n">
         <v>0.933928323023378</v>
@@ -48971,16 +48971,16 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218001</v>
+        <v>3.715372960218006</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.980290301525305</v>
+        <v>-4.92742953933477</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.915051119474874</v>
+        <v>1.936195424351088</v>
       </c>
       <c r="F2062" t="n">
         <v>0.9983042338740931</v>
@@ -48994,16 +48994,16 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353537</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.035659463657499</v>
+        <v>-4.982798701466963</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.898637272369724</v>
+        <v>1.919781577245938</v>
       </c>
       <c r="F2063" t="n">
         <v>0.9983042338740931</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73682287011328</v>
+        <v>3.736822870113285</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.053877930655108</v>
+        <v>-5.001017168464572</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.890888248913612</v>
+        <v>1.912032553789827</v>
       </c>
       <c r="F2064" t="n">
         <v>0.9731977966182509</v>
@@ -49040,16 +49040,16 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113689</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.965671096507529</v>
+        <v>-4.912810334316994</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.946045375422962</v>
+        <v>1.967189680299176</v>
       </c>
       <c r="F2065" t="n">
         <v>0.9731977966182509</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016443</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.85963610130222</v>
+        <v>-4.806775339111685</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.972160074029814</v>
+        <v>1.993304378906028</v>
       </c>
       <c r="F2066" t="n">
         <v>0.9731977966182509</v>
@@ -49086,16 +49086,16 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307674</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.676424438169125</v>
+        <v>-4.623563675978589</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.047875688747097</v>
+        <v>2.069019993623312</v>
       </c>
       <c r="F2067" t="n">
         <v>0.9731977966182509</v>
@@ -49109,16 +49109,16 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863555</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.604702991155274</v>
+        <v>-4.551842228964738</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.059508673632015</v>
+        <v>2.080652978508229</v>
       </c>
       <c r="F2068" t="n">
         <v>1.044919243632102</v>
@@ -49138,10 +49138,10 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.582329965547568</v>
+        <v>-4.529469203357032</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.015373629796269</v>
+        <v>2.036517934672483</v>
       </c>
       <c r="F2069" t="n">
         <v>1.056174994745003</v>
@@ -49155,16 +49155,16 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456733</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.615346261458313</v>
+        <v>-4.562485499267777</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.187365316317327</v>
+        <v>2.208509621193541</v>
       </c>
       <c r="F2070" t="n">
         <v>0.9867376180782517</v>
@@ -49178,16 +49178,16 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883679</v>
+        <v>3.713762536883682</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.603818625808704</v>
+        <v>-4.550957863618168</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.183897596405419</v>
+        <v>2.205041901281633</v>
       </c>
       <c r="F2071" t="n">
         <v>1.045738276279614</v>
@@ -49201,16 +49201,16 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236299</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.701160127151073</v>
+        <v>-4.648299364960537</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.14862910839026</v>
+        <v>2.169773413266475</v>
       </c>
       <c r="F2072" t="n">
         <v>1.001318094114126</v>
@@ -49224,16 +49224,16 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.70520107942769</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.787016156491039</v>
+        <v>-4.734155394300504</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.115537778847112</v>
+        <v>2.136682083723326</v>
       </c>
       <c r="F2073" t="n">
         <v>0.9589420248879907</v>
@@ -49247,16 +49247,16 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610385</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.795852953907159</v>
+        <v>-4.742992191716623</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.094422261701166</v>
+        <v>2.11556656657738</v>
       </c>
       <c r="F2074" t="n">
         <v>0.95149985224664</v>
@@ -49270,16 +49270,16 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667457</v>
+        <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.887235516472617</v>
+        <v>-4.834374754282082</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.068033747720032</v>
+        <v>2.089178052596246</v>
       </c>
       <c r="F2075" t="n">
         <v>0.9149349675272953</v>
@@ -49293,16 +49293,16 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889193</v>
+        <v>3.673978374889197</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.875528798485611</v>
+        <v>-4.822668036295076</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.174844692739103</v>
+        <v>2.195988997615316</v>
       </c>
       <c r="F2076" t="n">
         <v>0.9266416855143017</v>
@@ -49316,16 +49316,16 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409568</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.946440872227889</v>
+        <v>-4.893580110037353</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.149512201973596</v>
+        <v>2.17065650684981</v>
       </c>
       <c r="F2077" t="n">
         <v>0.9266416855143017</v>
@@ -49345,10 +49345,10 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.956756970394241</v>
+        <v>-4.903896208203705</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.358290595985113</v>
+        <v>2.379434900861328</v>
       </c>
       <c r="F2078" t="n">
         <v>0.9266416855143017</v>
@@ -49362,16 +49362,16 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762288</v>
+        <v>3.623960959762294</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.956663002376868</v>
+        <v>-4.903802240186333</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.357506850104152</v>
+        <v>2.378651154980366</v>
       </c>
       <c r="F2079" t="n">
         <v>0.9270115468616197</v>
@@ -49385,16 +49385,16 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988019</v>
+        <v>3.633213467988025</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.105029230033013</v>
+        <v>-5.052168467842478</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.292392344986048</v>
+        <v>2.313536649862262</v>
       </c>
       <c r="F2080" t="n">
         <v>0.9270115468616197</v>
@@ -49408,16 +49408,16 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740925</v>
+        <v>3.647907242740924</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.104080806914975</v>
+        <v>-5.051220044724439</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.292771714233263</v>
+        <v>2.313916019109478</v>
       </c>
       <c r="F2081" t="n">
         <v>0.9270115468616197</v>
@@ -49431,16 +49431,16 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663629</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.204350624873996</v>
+        <v>-5.15148986268346</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.265391395030747</v>
+        <v>2.286535699906961</v>
       </c>
       <c r="F2082" t="n">
         <v>0.9270115468616197</v>
@@ -49454,16 +49454,16 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424773</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.198358378085184</v>
+        <v>-5.145497615894649</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.269734292170659</v>
+        <v>2.290878597046873</v>
       </c>
       <c r="F2083" t="n">
         <v>0.9270115468616197</v>
@@ -49477,16 +49477,16 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149221</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.109800416954417</v>
+        <v>-5.056939654763881</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.298811612640735</v>
+        <v>2.319955917516949</v>
       </c>
       <c r="F2084" t="n">
         <v>0.9270115468616197</v>
@@ -49500,16 +49500,16 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383093</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.092041339451343</v>
+        <v>-5.039180577260807</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.305223921080961</v>
+        <v>2.326368225957175</v>
       </c>
       <c r="F2085" t="n">
         <v>0.9270115468616197</v>
@@ -49523,16 +49523,16 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720999</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.992411188402275</v>
+        <v>-4.939550426211739</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.357858167409175</v>
+        <v>2.379002472285388</v>
       </c>
       <c r="F2086" t="n">
         <v>1.026641697910687</v>
@@ -49546,16 +49546,16 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455274</v>
+        <v>3.775357097455272</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.041810697091286</v>
+        <v>-4.98894993490075</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.527252629432296</v>
+        <v>2.548396934308511</v>
       </c>
       <c r="F2087" t="n">
         <v>1.036900531342432</v>
@@ -49569,16 +49569,16 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963135</v>
+        <v>3.749078058963136</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.83512622344891</v>
+        <v>-4.782265461258374</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.597115091992109</v>
+        <v>2.618259396868323</v>
       </c>
       <c r="F2088" t="n">
         <v>1.243585004984808</v>
@@ -49592,16 +49592,16 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162545</v>
+        <v>3.740284389162546</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.869283118446436</v>
+        <v>-4.816422356255901</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.585453847647203</v>
+        <v>2.606598152523418</v>
       </c>
       <c r="F2089" t="n">
         <v>1.160001235443995</v>
@@ -49615,16 +49615,16 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652385</v>
+        <v>3.782482115652386</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.776693639384979</v>
+        <v>-4.723832877194444</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.975986753261453</v>
+        <v>2.997131058137668</v>
       </c>
       <c r="F2090" t="n">
         <v>1.160001235443995</v>
@@ -49638,16 +49638,16 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108674</v>
+        <v>3.809055905108677</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.83658226720853</v>
+        <v>-4.783721505017994</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.956594413699136</v>
+        <v>2.977738718575351</v>
       </c>
       <c r="F2091" t="n">
         <v>1.145879320756531</v>
@@ -49661,16 +49661,16 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103565</v>
+        <v>3.835202441103569</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.784365957412188</v>
+        <v>-4.731505195221652</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.027310878941201</v>
+        <v>3.048455183817415</v>
       </c>
       <c r="F2092" t="n">
         <v>1.145879320756531</v>
@@ -49684,16 +49684,16 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047747</v>
+        <v>3.821827147047751</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.752468440326942</v>
+        <v>-4.699607678136407</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.04888385598531</v>
+        <v>3.070028160861524</v>
       </c>
       <c r="F2093" t="n">
         <v>1.177776837841776</v>
@@ -49707,16 +49707,16 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650756</v>
+        <v>3.82526841665076</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.767223764527083</v>
+        <v>-4.714363002336547</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.03861931034445</v>
+        <v>3.059763615220665</v>
       </c>
       <c r="F2094" t="n">
         <v>1.177776837841776</v>
@@ -49730,16 +49730,16 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135751</v>
+        <v>3.845044666135755</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.717759141157171</v>
+        <v>-4.664898378966636</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.049329663108695</v>
+        <v>3.070473967984909</v>
       </c>
       <c r="F2095" t="n">
         <v>1.227241461211688</v>
@@ -49753,16 +49753,16 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479224</v>
+        <v>3.825931790479229</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.554651149003556</v>
+        <v>-4.50179038681302</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.110980527685076</v>
+        <v>3.13212483256129</v>
       </c>
       <c r="F2096" t="n">
         <v>1.390349453365303</v>
@@ -49776,16 +49776,16 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844248</v>
+        <v>3.847096478844247</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.421843523506389</v>
+        <v>-4.368982761315854</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.173150614575071</v>
+        <v>3.194294919451285</v>
       </c>
       <c r="F2097" t="n">
         <v>1.390349453365303</v>
@@ -49799,16 +49799,16 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790952</v>
+        <v>3.83242598779095</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.484551439980947</v>
+        <v>-4.431690677790412</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.148924912971369</v>
+        <v>3.170069217847583</v>
       </c>
       <c r="F2098" t="n">
         <v>1.327641536890745</v>
@@ -49822,16 +49822,16 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578998</v>
+        <v>3.861579399578996</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.436543316137255</v>
+        <v>-4.383682553946719</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.131037579299198</v>
+        <v>3.152181884175413</v>
       </c>
       <c r="F2099" t="n">
         <v>1.327641536890745</v>
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.836459310407269</v>
+        <v>3.92616954360033</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.352503709059398</v>
+        <v>-4.304856896763129</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.168585675688291</v>
+        <v>3.187644400606799</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.411681143968602</v>
+        <v>1.406467194074336</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.75695227000696</v>
+        <v>5.7538239000704</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240928.xlsx
+++ b/tame_output/ON/bt/strategyON_20240928.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.5%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-592.1%</t>
+          <t>-594.6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-58.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-295.7%</t>
+          <t>-295.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>117.5%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.540125988402941</v>
+        <v>-8.512869468283869</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2496113108094913</v>
+        <v>-0.2387087027618624</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.524748936544829</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.442218949726451</v>
+        <v>-8.414962429607378</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.210748810312356</v>
+        <v>-0.1998462022647267</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.456763186684273</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.418265408750493</v>
+        <v>-8.39100888863142</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2004988877764791</v>
+        <v>-0.1895962797288502</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.432809645708315</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.154205470427696</v>
+        <v>-8.126948950308623</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1081352286091124</v>
+        <v>-0.09723262056148352</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.168749707385519</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.447125846922858</v>
+        <v>-7.419869326803785</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.171909587132522</v>
+        <v>0.1828121951801509</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.168749707385519</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.406941548556667</v>
+        <v>-7.379685028437595</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1883269303668396</v>
+        <v>0.1992295384144684</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.128565409019328</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.243541677617305</v>
+        <v>-7.216285157498232</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2530536999633415</v>
+        <v>0.2639563080109704</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9651655380799653</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.08542429823853</v>
+        <v>-7.058167778119457</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3242250805527038</v>
+        <v>0.3351276886003332</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8070481587011898</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.935757907231014</v>
+        <v>-6.908501387111942</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.381199426642751</v>
+        <v>0.3921020346903799</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7141446674586539</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.803482433600128</v>
+        <v>-6.776225913481055</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3353704021022601</v>
+        <v>0.346273010149889</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.5818691938277673</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631621218035225</v>
+        <v>-6.604364697916153</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4069299490158578</v>
+        <v>0.4178325570634867</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4100079782628644</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.546656551305906</v>
+        <v>-6.519400031186834</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4538221569312442</v>
+        <v>0.4647247649788731</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.3250433115335448</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.652246541079011</v>
+        <v>-6.624990020959938</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2836102314227835</v>
+        <v>0.2945128394704128</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.4306333013066492</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.584011956453583</v>
+        <v>-6.556755436334511</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3594484071500412</v>
+        <v>0.3703510151976701</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.4122179784341132</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.436071915045984</v>
+        <v>-6.408815394926911</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3020036150746739</v>
+        <v>0.3129062231223028</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3918970625255556</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.383102392791995</v>
+        <v>-6.355845872672923</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.314477437722791</v>
+        <v>0.3253800457704199</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.3389275402715667</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217314196831705</v>
+        <v>-6.190057676712632</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.373832104011814</v>
+        <v>0.3847347120594433</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.3389275402715667</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183950990352936</v>
+        <v>-6.156694470233863</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4016397409844648</v>
+        <v>0.4125423490320936</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.3389275402715667</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075691853230414</v>
+        <v>-6.048435333111342</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4394755162926685</v>
+        <v>0.4503781243402973</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.3389275402715667</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952400718413283</v>
+        <v>-5.925144198294211</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4862900642300976</v>
+        <v>0.4971926722777269</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.2156364054544362</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.899703851281992</v>
+        <v>-5.87244733116292</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5150697893199392</v>
+        <v>0.5259723973675685</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1629395383231451</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.655938409298548</v>
+        <v>-5.628681889179475</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6083566744603677</v>
+        <v>0.619259282507997</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1629395383231451</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.566162736922076</v>
+        <v>-5.538906216803003</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6463912573309725</v>
+        <v>0.6572938653786018</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.101340093408835</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.316312342973001</v>
+        <v>-5.289055822853928</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7390734898943045</v>
+        <v>0.7499760979419339</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.101340093408835</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.140420250505569</v>
+        <v>-5.113163730386496</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8130294504019262</v>
+        <v>0.8239320584495551</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.101340093408835</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.968973787483105</v>
+        <v>-4.941717267364033</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8949355416654652</v>
+        <v>0.9058381497130943</v>
       </c>
       <c r="F1921" t="n">
         <v>0.07010636961362809</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.888951500373985</v>
+        <v>-4.861694980254912</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9259649341254106</v>
+        <v>0.9368675421730397</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1501286567227491</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.82531575814005</v>
+        <v>-4.798059238020977</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9561140320733017</v>
+        <v>0.9670166401209308</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2137643989566836</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.731618439923655</v>
+        <v>-4.704361919804582</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9747872181436554</v>
+        <v>0.9856898261912845</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2137643989566836</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.742121062988944</v>
+        <v>-4.714864542869871</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9723292455424173</v>
+        <v>0.9832318535900462</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2032617758913947</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629634802320069</v>
+        <v>-4.602378282200997</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.021253063644787</v>
+        <v>1.032155671692416</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2032617758913947</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611921115442204</v>
+        <v>-4.584664595323131</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.029017122313273</v>
+        <v>1.039919730360902</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2064431047883115</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.488446844129186</v>
+        <v>-4.461190324010113</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075404902058474</v>
+        <v>1.086307510106103</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2064431047883115</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.268426046092175</v>
+        <v>-4.241169525973103</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.164992258283893</v>
+        <v>1.175894866331522</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3476629498562918</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.135558357028898</v>
+        <v>-4.108301836909825</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.234033516711027</v>
+        <v>1.244936124758656</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3476629498562918</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.015385273664399</v>
+        <v>-3.988128753545326</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.283248594497128</v>
+        <v>1.294151202544757</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4678360332207907</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.880131912334422</v>
+        <v>-3.852875392215349</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.347438041590559</v>
+        <v>1.358340649638188</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6030893945507678</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.940006739692114</v>
+        <v>-3.912750219573041</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.309525602048908</v>
+        <v>1.320428210096537</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5432145671930757</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.820186508781277</v>
+        <v>-3.792929988662204</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.372742863647451</v>
+        <v>1.38364547169508</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5432145671930757</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.822656215243083</v>
+        <v>-3.79539969512401</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.279399180385171</v>
+        <v>1.290301788432799</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5407448607312695</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.891026401567093</v>
+        <v>-3.86376988144802</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.171312967340868</v>
+        <v>1.182215575388497</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5500205597674844</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.002898681193243</v>
+        <v>-3.975642161074171</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.117000764122299</v>
+        <v>1.127903372169928</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5500205597674844</v>
@@ -46125,10 +46125,10 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.986924015706975</v>
+        <v>-3.959667495587903</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.089965155240833</v>
+        <v>1.100867763288462</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5500205597674844</v>
@@ -46148,10 +46148,10 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.811449755914506</v>
+        <v>-3.784193235795434</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.164722091149609</v>
+        <v>1.175624699197238</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5500205597674844</v>
@@ -46171,10 +46171,10 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.803525381329592</v>
+        <v>-3.776268861210519</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.143633869744782</v>
+        <v>1.154536477792411</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5500205597674844</v>
@@ -46194,10 +46194,10 @@
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.797247178759743</v>
+        <v>-3.76999065864067</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.074683464174171</v>
+        <v>1.0855860722218</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5562987623373334</v>
@@ -46217,10 +46217,10 @@
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.73739455955602</v>
+        <v>-3.710138039436947</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.108796898287793</v>
+        <v>1.119699506335422</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5562987623373334</v>
@@ -46240,10 +46240,10 @@
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.651151096529643</v>
+        <v>-3.62389457641057</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.138240554072204</v>
+        <v>1.149143162119833</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5562987623373334</v>
@@ -46263,10 +46263,10 @@
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.696457915928622</v>
+        <v>-3.66920139580955</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.111893601757137</v>
+        <v>1.122796209804767</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5154885993281026</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.725491020630924</v>
+        <v>-3.698234500511851</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.100832232909319</v>
+        <v>1.111734840956947</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5154885993281026</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.632680539180065</v>
+        <v>-3.605424019060992</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.067229117381028</v>
+        <v>1.078131725428657</v>
       </c>
       <c r="F1946" t="n">
         <v>0.608299080778962</v>
@@ -46332,10 +46332,10 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.677070008509492</v>
+        <v>-3.64981348839042</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.051346805573858</v>
+        <v>1.062249413621487</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5639096114495343</v>
@@ -46355,10 +46355,10 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.656566314623995</v>
+        <v>-3.629309794504922</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.054623991639779</v>
+        <v>1.065526599687409</v>
       </c>
       <c r="F1948" t="n">
         <v>0.5844133053350317</v>
@@ -46378,10 +46378,10 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.740238411336327</v>
+        <v>-3.712981891217254</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.026646448785514</v>
+        <v>1.037549056833143</v>
       </c>
       <c r="F1949" t="n">
         <v>0.5844133053350317</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.76801880923768</v>
+        <v>-3.740762289118607</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.027031491393512</v>
+        <v>1.037934099441141</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5566329074336787</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.886399481967818</v>
+        <v>-3.859142961848746</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8180349423021096</v>
+        <v>0.8289375503497387</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4894150552827025</v>
@@ -46447,10 +46447,10 @@
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.99501356041115</v>
+        <v>-3.967757040292077</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8947389716439829</v>
+        <v>0.905641579691612</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4894150552827025</v>
@@ -46470,10 +46470,10 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.959604522163007</v>
+        <v>-3.932348002043934</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9234156130455631</v>
+        <v>0.934318221093192</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4894150552827025</v>
@@ -46493,10 +46493,10 @@
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.968065690818468</v>
+        <v>-3.940809170699395</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9174505869257472</v>
+        <v>0.9283531949733763</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4809538866272414</v>
@@ -46516,10 +46516,10 @@
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.790949360783302</v>
+        <v>-3.763692840664229</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9850261477851161</v>
+        <v>0.995928755832745</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4809538866272414</v>
@@ -46539,10 +46539,10 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.836041605616847</v>
+        <v>-3.808785085497775</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.967672641613611</v>
+        <v>0.9785752496612401</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4190578434578516</v>
@@ -46562,10 +46562,10 @@
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.656666184378079</v>
+        <v>-3.629409664259007</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.033209785415532</v>
+        <v>1.044112393463162</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5758346016285703</v>
@@ -46585,10 +46585,10 @@
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.701680397898686</v>
+        <v>-3.674423877779613</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9960115553388798</v>
+        <v>1.006914163386509</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5454857063139656</v>
@@ -46608,10 +46608,10 @@
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.968684908171121</v>
+        <v>-3.941428388052048</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8949013135688513</v>
+        <v>0.9058039216164804</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3511226682710171</v>
@@ -46631,10 +46631,10 @@
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.069882689608294</v>
+        <v>-4.042626169489221</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8536261228904836</v>
+        <v>0.8645287309381127</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2827138547256979</v>
@@ -46654,10 +46654,10 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.063371722993981</v>
+        <v>-4.036115202874909</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8538304710905253</v>
+        <v>0.8647330791381544</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2827138547256979</v>
@@ -46677,10 +46677,10 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.044333595286684</v>
+        <v>-4.017077075167611</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8579704413816893</v>
+        <v>0.8688730494293182</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2245302433945033</v>
@@ -46700,10 +46700,10 @@
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.096849397561504</v>
+        <v>-4.069592877442432</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9562585221059514</v>
+        <v>0.9671611301535805</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2245302433945033</v>
@@ -46723,10 +46723,10 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.100257708996084</v>
+        <v>-4.073001188877011</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9557285265182531</v>
+        <v>0.966631134565882</v>
       </c>
       <c r="F1964" t="n">
         <v>0.2570468124038807</v>
@@ -46746,10 +46746,10 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.080901573102237</v>
+        <v>-4.053645052983164</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9694795112727179</v>
+        <v>0.980382119320347</v>
       </c>
       <c r="F1965" t="n">
         <v>0.2570468124038807</v>
@@ -46769,10 +46769,10 @@
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.154231101840329</v>
+        <v>-4.126974581721257</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8380979210546804</v>
+        <v>0.8490005291023095</v>
       </c>
       <c r="F1966" t="n">
         <v>0.2574414748235027</v>
@@ -46792,10 +46792,10 @@
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.238052323115028</v>
+        <v>-4.210795802995955</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8073630540762819</v>
+        <v>0.8182656621239111</v>
       </c>
       <c r="F1967" t="n">
         <v>0.2574414748235027</v>
@@ -46815,10 +46815,10 @@
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.231899617062243</v>
+        <v>-4.204643096943171</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8104864848890541</v>
+        <v>0.8213890929366832</v>
       </c>
       <c r="F1968" t="n">
         <v>0.2635941808762869</v>
@@ -46838,10 +46838,10 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.248708915212745</v>
+        <v>-4.221452395093673</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8028432423689635</v>
+        <v>0.8137458504165926</v>
       </c>
       <c r="F1969" t="n">
         <v>0.2467848827257853</v>
@@ -46861,10 +46861,10 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.186410916436623</v>
+        <v>-4.15915439631755</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8940979956762334</v>
+        <v>0.9050006037238625</v>
       </c>
       <c r="F1970" t="n">
         <v>0.2920791470002274</v>
@@ -46884,10 +46884,10 @@
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.984620718771465</v>
+        <v>-3.957364198652392</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7771060764564237</v>
+        <v>0.7880086845040526</v>
       </c>
       <c r="F1971" t="n">
         <v>0.4900973391693817</v>
@@ -46907,10 +46907,10 @@
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.03550743145766</v>
+        <v>-4.008250911338587</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8270416237041209</v>
+        <v>0.83794423175175</v>
       </c>
       <c r="F1972" t="n">
         <v>0.4392106264831871</v>
@@ -46930,10 +46930,10 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.948896688807852</v>
+        <v>-3.92164016868878</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8763136568800876</v>
+        <v>0.8872162649277167</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5178363576883454</v>
@@ -46953,10 +46953,10 @@
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.009105986813137</v>
+        <v>-3.981849466694064</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8507659185026455</v>
+        <v>0.8616685265502744</v>
       </c>
       <c r="F1974" t="n">
         <v>0.4576270596830608</v>
@@ -46976,10 +46976,10 @@
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.959919338128786</v>
+        <v>-3.932662818009713</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8689321960163146</v>
+        <v>0.8798348040639437</v>
       </c>
       <c r="F1975" t="n">
         <v>0.4576270596830608</v>
@@ -46999,10 +46999,10 @@
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.915546206490217</v>
+        <v>-3.888289686371144</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8865443161071782</v>
+        <v>0.8974469241548073</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5020001913216294</v>
@@ -47022,10 +47022,10 @@
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.880814885171716</v>
+        <v>-3.853558365052643</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.894830638773169</v>
+        <v>0.9057332468207981</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5020001913216294</v>
@@ -47045,10 +47045,10 @@
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.83315915461066</v>
+        <v>-3.805902634491588</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9202746880253958</v>
+        <v>0.9311772960730249</v>
       </c>
       <c r="F1978" t="n">
         <v>0.5496559218826851</v>
@@ -47068,10 +47068,10 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.732640996111906</v>
+        <v>-3.705384475992833</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9653743247996225</v>
+        <v>0.9762769328472516</v>
       </c>
       <c r="F1979" t="n">
         <v>0.6501740803814396</v>
@@ -47091,10 +47091,10 @@
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.716735666679553</v>
+        <v>-3.689479146560481</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9584911290484359</v>
+        <v>0.9693937370960648</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5710614196722008</v>
@@ -47114,10 +47114,10 @@
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.671897265071155</v>
+        <v>-3.644640744952083</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9805241923024237</v>
+        <v>0.9914268003500526</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5756048526170703</v>
@@ -47137,10 +47137,10 @@
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.691395721313163</v>
+        <v>-3.664139201194091</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9768857494366983</v>
+        <v>0.9877883574843274</v>
       </c>
       <c r="F1982" t="n">
         <v>0.527520211337166</v>
@@ -47160,10 +47160,10 @@
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.647192884227263</v>
+        <v>-3.61993636410819</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.000446486798896</v>
+        <v>1.011349094846525</v>
       </c>
       <c r="F1983" t="n">
         <v>0.5717230484230664</v>
@@ -47183,10 +47183,10 @@
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.65475255006431</v>
+        <v>-3.627496029945237</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9958326209333244</v>
+        <v>1.006735228980953</v>
       </c>
       <c r="F1984" t="n">
         <v>0.6265264524328857</v>
@@ -47206,10 +47206,10 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.496461132525038</v>
+        <v>-3.469204612405965</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.110396953132073</v>
+        <v>1.121299561179702</v>
       </c>
       <c r="F1985" t="n">
         <v>0.6265264524328857</v>
@@ -47229,10 +47229,10 @@
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.288819128890561</v>
+        <v>-3.261562608771489</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.191894459180117</v>
+        <v>1.202797067227746</v>
       </c>
       <c r="F1986" t="n">
         <v>0.8341684560673619</v>
@@ -47252,10 +47252,10 @@
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.237787036168033</v>
+        <v>-3.210530516048961</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.207255524507398</v>
+        <v>1.218158132555027</v>
       </c>
       <c r="F1987" t="n">
         <v>0.8852005487898899</v>
@@ -47275,10 +47275,10 @@
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.172562855040828</v>
+        <v>-3.145306334921755</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.250532601050985</v>
+        <v>1.261435209098614</v>
       </c>
       <c r="F1988" t="n">
         <v>0.9504247299170955</v>
@@ -47298,10 +47298,10 @@
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.135135834969694</v>
+        <v>-3.107879314850621</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.261464381378719</v>
+        <v>1.272366989426348</v>
       </c>
       <c r="F1989" t="n">
         <v>0.9556762679462771</v>
@@ -47321,10 +47321,10 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.133777849996148</v>
+        <v>-3.106521329877076</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.263264367699378</v>
+        <v>1.274166975747006</v>
       </c>
       <c r="F1990" t="n">
         <v>1.030014393484096</v>
@@ -47344,10 +47344,10 @@
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.105364586896265</v>
+        <v>-3.078108066777192</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.435187443960542</v>
+        <v>1.446090052008171</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9710388307376669</v>
@@ -47367,10 +47367,10 @@
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.030582325871252</v>
+        <v>-3.003325805752179</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.585213257588364</v>
+        <v>1.596115865635993</v>
       </c>
       <c r="F1992" t="n">
         <v>1.04582109176268</v>
@@ -47390,10 +47390,10 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.004498241607444</v>
+        <v>-2.977241721488372</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.587354867307746</v>
+        <v>1.598257475355375</v>
       </c>
       <c r="F1993" t="n">
         <v>1.04582109176268</v>
@@ -47413,10 +47413,10 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.916620328498324</v>
+        <v>-2.889363808379251</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.620699228135174</v>
+        <v>1.631601836182803</v>
       </c>
       <c r="F1994" t="n">
         <v>1.161746734186031</v>
@@ -47436,10 +47436,10 @@
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.907727867105041</v>
+        <v>-2.880471346985968</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.641810618419278</v>
+        <v>1.652713226466908</v>
       </c>
       <c r="F1995" t="n">
         <v>1.161746734186031</v>
@@ -47459,10 +47459,10 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.076203984074918</v>
+        <v>-3.048947463955846</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.566275219035911</v>
+        <v>1.57717782708354</v>
       </c>
       <c r="F1996" t="n">
         <v>1.13379889846945</v>
@@ -47482,10 +47482,10 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.629947791445479</v>
+        <v>-2.602691271326406</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.726047393275549</v>
+        <v>1.736950001323178</v>
       </c>
       <c r="F1997" t="n">
         <v>1.039080228799817</v>
@@ -47505,10 +47505,10 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.607226687762326</v>
+        <v>-2.579970167643253</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.725799857245714</v>
+        <v>1.736702465293344</v>
       </c>
       <c r="F1998" t="n">
         <v>1.039080228799817</v>
@@ -47528,10 +47528,10 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.736428501056368</v>
+        <v>-2.709171980937296</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.833025257779267</v>
+        <v>1.843927865826896</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9098784155057749</v>
@@ -47551,10 +47551,10 @@
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.762302899530394</v>
+        <v>-2.735046379411322</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.859753320883303</v>
+        <v>1.870655928930932</v>
       </c>
       <c r="F2000" t="n">
         <v>0.954790024217516</v>
@@ -47574,10 +47574,10 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.755248209315221</v>
+        <v>-2.727991689196148</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.859250552958917</v>
+        <v>1.870153161006546</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9618447144326898</v>
@@ -47597,10 +47597,10 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.728296984988733</v>
+        <v>-2.70104046486966</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.880037196334254</v>
+        <v>1.890939804381883</v>
       </c>
       <c r="F2002" t="n">
         <v>0.976725060460409</v>
@@ -47620,10 +47620,10 @@
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.74984121281952</v>
+        <v>-2.722584692700447</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.055522637346899</v>
+        <v>2.066425245394528</v>
       </c>
       <c r="F2003" t="n">
         <v>0.976725060460409</v>
@@ -47643,10 +47643,10 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.772249330624392</v>
+        <v>-2.744992810505319</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.038676085127944</v>
+        <v>2.049578693175572</v>
       </c>
       <c r="F2004" t="n">
         <v>0.976725060460409</v>
@@ -47666,10 +47666,10 @@
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.800473566201992</v>
+        <v>-2.77321704608292</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.029440390446541</v>
+        <v>2.04034299849417</v>
       </c>
       <c r="F2005" t="n">
         <v>0.9947018129117176</v>
@@ -47689,10 +47689,10 @@
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.809914492090522</v>
+        <v>-2.782657971971449</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.081917737812976</v>
+        <v>2.092820345860605</v>
       </c>
       <c r="F2006" t="n">
         <v>1.117128930455109</v>
@@ -47712,10 +47712,10 @@
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.898791123258996</v>
+        <v>-2.871534603139923</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.049258179890887</v>
+        <v>2.060160787938516</v>
       </c>
       <c r="F2007" t="n">
         <v>1.028252299286635</v>
@@ -47735,10 +47735,10 @@
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.975121100859902</v>
+        <v>-2.947864580740829</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.0168380017443</v>
+        <v>2.027740609791929</v>
       </c>
       <c r="F2008" t="n">
         <v>1.028252299286635</v>
@@ -47758,10 +47758,10 @@
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.130077886260031</v>
+        <v>-3.102821366140958</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.949675517187111</v>
+        <v>1.96057812523474</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8732955138865059</v>
@@ -47781,10 +47781,10 @@
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.291646311787286</v>
+        <v>-3.264389791668214</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.883482157186361</v>
+        <v>1.89438476523399</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7465125900886266</v>
@@ -47804,10 +47804,10 @@
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.399946973657406</v>
+        <v>-3.372690453538333</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.853235299304232</v>
+        <v>1.864137907351861</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7465125900886266</v>
@@ -47827,10 +47827,10 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.41775094537815</v>
+        <v>-3.390494425259077</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.838118907398874</v>
+        <v>1.849021515446503</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6759779671834254</v>
@@ -47850,10 +47850,10 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.445651732487623</v>
+        <v>-3.41839521236855</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.825482633682087</v>
+        <v>1.836385241729716</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6413810430404906</v>
@@ -47873,10 +47873,10 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.568177835190517</v>
+        <v>-3.540921315071444</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.773236636578128</v>
+        <v>1.784139244625757</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5188549403375967</v>
@@ -47896,10 +47896,10 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.798692331376105</v>
+        <v>-3.771435811257033</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.747736797694396</v>
+        <v>1.758639405742025</v>
       </c>
       <c r="F2015" t="n">
         <v>0.288340444152008</v>
@@ -47919,10 +47919,10 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.147437416600549</v>
+        <v>-4.120180896481476</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.748550482606466</v>
+        <v>1.759453090654095</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1795924902331102</v>
@@ -47942,10 +47942,10 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.301423834376689</v>
+        <v>-4.274167314257617</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.75593618464165</v>
+        <v>1.766838792689279</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1795924902331102</v>
@@ -47965,10 +47965,10 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.506023269239698</v>
+        <v>-4.478766749120625</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.660147612816567</v>
+        <v>1.671050220864196</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1795924902331102</v>
@@ -47988,10 +47988,10 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.758498423247422</v>
+        <v>-4.73124190312835</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.571028040268891</v>
+        <v>1.58193064831652</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1795924902331102</v>
@@ -48011,10 +48011,10 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.9985334175363</v>
+        <v>-5.024137659607762</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.476224577072284</v>
+        <v>1.465982880243699</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1795924902331102</v>
@@ -48034,10 +48034,10 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.185197545671108</v>
+        <v>-5.21080178774257</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.405680668045682</v>
+        <v>1.395438971217097</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1528535194085503</v>
@@ -48057,10 +48057,10 @@
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.33121823258507</v>
+        <v>-5.356822474656532</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.342350246016287</v>
+        <v>1.332108549187702</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1437704276146933</v>
@@ -48080,10 +48080,10 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.422932241694655</v>
+        <v>-5.448536483766118</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.467868699071497</v>
+        <v>1.457627002242912</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1437704276146933</v>
@@ -48103,10 +48103,10 @@
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.454583900754624</v>
+        <v>-5.480188142826087</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.450054673411323</v>
+        <v>1.439812976582738</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1386019703702531</v>
@@ -48126,10 +48126,10 @@
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.523649955327561</v>
+        <v>-5.549254197399024</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.43265766915064</v>
+        <v>1.422415972322055</v>
       </c>
       <c r="F2025" t="n">
         <v>0.07623109287664309</v>
@@ -48149,10 +48149,10 @@
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.625626077575968</v>
+        <v>-5.651230319647431</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.400792858707179</v>
+        <v>1.390551161878594</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.02574502937176448</v>
@@ -48172,10 +48172,10 @@
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.515619794098747</v>
+        <v>-5.54122403617021</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.436948259342243</v>
+        <v>1.426706562513658</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.002540457454489276</v>
@@ -48195,10 +48195,10 @@
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.372560218357821</v>
+        <v>-5.398164460429284</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.498422100360588</v>
+        <v>1.488180403532003</v>
       </c>
       <c r="F2028" t="n">
         <v>0.005472969135490002</v>
@@ -48218,10 +48218,10 @@
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.071113492885983</v>
+        <v>-5.096717734957446</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.626261673431859</v>
+        <v>1.616019976603274</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3069196946073273</v>
@@ -48241,10 +48241,10 @@
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.095703737121167</v>
+        <v>-5.12130797919263</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.617396753490496</v>
+        <v>1.607155056661911</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3069196946073273</v>
@@ -48264,10 +48264,10 @@
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.044665361114647</v>
+        <v>-5.07026960318611</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.63865500827286</v>
+        <v>1.628413311444274</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3069196946073273</v>
@@ -48287,10 +48287,10 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.015816684291186</v>
+        <v>-5.041420926362649</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.669232577876389</v>
+        <v>1.658990881047804</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3357683714307875</v>
@@ -48310,10 +48310,10 @@
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.919181772272546</v>
+        <v>-4.944786014344009</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.52407053880778</v>
+        <v>1.513828841979195</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4324032834494275</v>
@@ -48333,10 +48333,10 @@
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.850143761324079</v>
+        <v>-4.875748003395541</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.555187787261131</v>
+        <v>1.544946090432546</v>
       </c>
       <c r="F2034" t="n">
         <v>0.5014412943978955</v>
@@ -48356,10 +48356,10 @@
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.685647427133117</v>
+        <v>-4.71125166920458</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.605413140013598</v>
+        <v>1.595171443185013</v>
       </c>
       <c r="F2035" t="n">
         <v>0.6659376285888574</v>
@@ -48379,10 +48379,10 @@
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.608548825591244</v>
+        <v>-4.634153067662707</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.635440291066777</v>
+        <v>1.625198594238192</v>
       </c>
       <c r="F2036" t="n">
         <v>0.6659376285888574</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147911</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.618934020481134</v>
+        <v>-4.644538262552596</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.641154992235894</v>
+        <v>1.630913295407309</v>
       </c>
       <c r="F2037" t="n">
         <v>0.6555524336989681</v>
@@ -48425,10 +48425,10 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.637522179203359</v>
+        <v>-4.663126421274821</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.704556734523429</v>
+        <v>1.694315037694844</v>
       </c>
       <c r="F2038" t="n">
         <v>0.6369642749767428</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496556</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.637820725899394</v>
+        <v>-4.663424967970857</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.701306326663313</v>
+        <v>1.691064629834728</v>
       </c>
       <c r="F2039" t="n">
         <v>0.6366657282807069</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108861</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.536997592208967</v>
+        <v>-4.56260183428043</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.746166475078876</v>
+        <v>1.73592477825029</v>
       </c>
       <c r="F2040" t="n">
         <v>0.6491299437650607</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121472</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.346216231456559</v>
+        <v>-4.371820473528022</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.822608272858382</v>
+        <v>1.812366576029797</v>
       </c>
       <c r="F2041" t="n">
         <v>0.8399113045174681</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906085</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.239252873607137</v>
+        <v>-4.2648571156786</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.845230461735747</v>
+        <v>1.834988764907162</v>
       </c>
       <c r="F2042" t="n">
         <v>0.8983759124772696</v>
@@ -48540,10 +48540,10 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.183922285705375</v>
+        <v>-4.209526527776838</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.902329633508511</v>
+        <v>1.892087936679925</v>
       </c>
       <c r="F2043" t="n">
         <v>0.9537065003790317</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539899</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.171868158792412</v>
+        <v>-4.197472400863875</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.900837852175133</v>
+        <v>1.890596155346548</v>
       </c>
       <c r="F2044" t="n">
         <v>0.9657606272919945</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.725010844811014</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.213023278360633</v>
+        <v>-4.238627520432096</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.886256434531981</v>
+        <v>1.876014737703396</v>
       </c>
       <c r="F2045" t="n">
         <v>0.9246055077237736</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.612322444382925</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.144974715669103</v>
+        <v>-4.170578957740566</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.926326885486476</v>
+        <v>1.91608518865789</v>
       </c>
       <c r="F2046" t="n">
         <v>0.9926540704153033</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.645256780013432</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.376575108838604</v>
+        <v>-4.402179350910067</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.853889398392269</v>
+        <v>1.843647701563684</v>
       </c>
       <c r="F2047" t="n">
         <v>0.9926540704153033</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.66674720149897</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.426626654367823</v>
+        <v>-4.452230896439286</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.817475016247464</v>
+        <v>1.807233319418879</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9926540704153033</v>
@@ -48678,10 +48678,10 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.601733486944267</v>
+        <v>-4.62733772901573</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.707684196810352</v>
+        <v>1.697442499981767</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9926540704153033</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.405633333513745</v>
+        <v>-4.431237575585207</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.793146877179502</v>
+        <v>1.782905180350917</v>
       </c>
       <c r="F2050" t="n">
         <v>1.188754223845826</v>
@@ -48724,10 +48724,10 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.25260794140046</v>
+        <v>-4.278212183471923</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.95352803359772</v>
+        <v>1.943286336769135</v>
       </c>
       <c r="F2051" t="n">
         <v>1.34177961595911</v>
@@ -48747,10 +48747,10 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.28091525527373</v>
+        <v>-4.306519497345193</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.129671332956704</v>
+        <v>2.119429636128119</v>
       </c>
       <c r="F2052" t="n">
         <v>1.34177961595911</v>
@@ -48770,10 +48770,10 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.447508480387253</v>
+        <v>-4.473112722458715</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.032436994265378</v>
+        <v>2.022195297436793</v>
       </c>
       <c r="F2053" t="n">
         <v>1.175186390845588</v>
@@ -48793,10 +48793,10 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.424472687025687</v>
+        <v>-4.45007692909715</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.045327714271722</v>
+        <v>2.035086017443137</v>
       </c>
       <c r="F2054" t="n">
         <v>1.175186390845588</v>
@@ -48816,10 +48816,10 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.39522670656999</v>
+        <v>-4.420830948641453</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.054644161577496</v>
+        <v>2.044402464748911</v>
       </c>
       <c r="F2055" t="n">
         <v>1.175186390845588</v>
@@ -48839,10 +48839,10 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.502152254447841</v>
+        <v>-4.527756496519304</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.009167181583991</v>
+        <v>1.998925484755405</v>
       </c>
       <c r="F2056" t="n">
         <v>1.068260842967736</v>
@@ -48862,10 +48862,10 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.64717081295509</v>
+        <v>-4.672775055026553</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.952588560324326</v>
+        <v>1.94234686349574</v>
       </c>
       <c r="F2057" t="n">
         <v>0.9232422844604879</v>
@@ -48885,10 +48885,10 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.765512578739807</v>
+        <v>-4.79111682081127</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.005183093268192</v>
+        <v>1.994941396439606</v>
       </c>
       <c r="F2058" t="n">
         <v>0.933928323023378</v>
@@ -48908,10 +48908,10 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.816923001060515</v>
+        <v>-4.842527243131978</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.982404621465848</v>
+        <v>1.972162924637262</v>
       </c>
       <c r="F2059" t="n">
         <v>0.933928323023378</v>
@@ -48931,10 +48931,10 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.896342452268267</v>
+        <v>-4.92194669433973</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.950539969057036</v>
+        <v>1.940298272228451</v>
       </c>
       <c r="F2060" t="n">
         <v>0.933928323023378</v>
@@ -48954,10 +48954,10 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.991805450185485</v>
+        <v>-5.017409692256948</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.912348663448192</v>
+        <v>1.902106966619607</v>
       </c>
       <c r="F2061" t="n">
         <v>0.933928323023378</v>
@@ -48977,10 +48977,10 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.92742953933477</v>
+        <v>-4.953033781406233</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.936195424351088</v>
+        <v>1.925953727522503</v>
       </c>
       <c r="F2062" t="n">
         <v>0.9983042338740931</v>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.982798701466963</v>
+        <v>-5.008402943538426</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.919781577245938</v>
+        <v>1.909539880417352</v>
       </c>
       <c r="F2063" t="n">
         <v>0.9983042338740931</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.001017168464572</v>
+        <v>-5.026621410536035</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.912032553789827</v>
+        <v>1.901790856961242</v>
       </c>
       <c r="F2064" t="n">
         <v>0.9731977966182509</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.912810334316994</v>
+        <v>-4.938414576388457</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.967189680299176</v>
+        <v>1.956947983470592</v>
       </c>
       <c r="F2065" t="n">
         <v>0.9731977966182509</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.806775339111685</v>
+        <v>-4.832379581183147</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.993304378906028</v>
+        <v>1.983062682077443</v>
       </c>
       <c r="F2066" t="n">
         <v>0.9731977966182509</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.623563675978589</v>
+        <v>-4.649167918050052</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.069019993623312</v>
+        <v>2.058778296794727</v>
       </c>
       <c r="F2067" t="n">
         <v>0.9731977966182509</v>
@@ -49115,10 +49115,10 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.551842228964738</v>
+        <v>-4.577446471036201</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.080652978508229</v>
+        <v>2.070411281679644</v>
       </c>
       <c r="F2068" t="n">
         <v>1.044919243632102</v>
@@ -49138,10 +49138,10 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.529469203357032</v>
+        <v>-4.555073445428495</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.036517934672483</v>
+        <v>2.026276237843898</v>
       </c>
       <c r="F2069" t="n">
         <v>1.056174994745003</v>
@@ -49161,10 +49161,10 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.562485499267777</v>
+        <v>-4.58808974133924</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.208509621193541</v>
+        <v>2.198267924364956</v>
       </c>
       <c r="F2070" t="n">
         <v>0.9867376180782517</v>
@@ -49184,10 +49184,10 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.550957863618168</v>
+        <v>-4.576562105689631</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.205041901281633</v>
+        <v>2.194800204453048</v>
       </c>
       <c r="F2071" t="n">
         <v>1.045738276279614</v>
@@ -49207,10 +49207,10 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.648299364960537</v>
+        <v>-4.673903607032</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.169773413266475</v>
+        <v>2.159531716437889</v>
       </c>
       <c r="F2072" t="n">
         <v>1.001318094114126</v>
@@ -49230,10 +49230,10 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.734155394300504</v>
+        <v>-4.759759636371967</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.136682083723326</v>
+        <v>2.126440386894741</v>
       </c>
       <c r="F2073" t="n">
         <v>0.9589420248879907</v>
@@ -49253,10 +49253,10 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.742992191716623</v>
+        <v>-4.768596433788086</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.11556656657738</v>
+        <v>2.105324869748795</v>
       </c>
       <c r="F2074" t="n">
         <v>0.95149985224664</v>
@@ -49276,10 +49276,10 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.834374754282082</v>
+        <v>-4.859978996353544</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.089178052596246</v>
+        <v>2.078936355767661</v>
       </c>
       <c r="F2075" t="n">
         <v>0.9149349675272953</v>
@@ -49299,10 +49299,10 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.822668036295076</v>
+        <v>-4.848272278366538</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.195988997615316</v>
+        <v>2.185747300786732</v>
       </c>
       <c r="F2076" t="n">
         <v>0.9266416855143017</v>
@@ -49322,10 +49322,10 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.893580110037353</v>
+        <v>-4.919184352108816</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.17065650684981</v>
+        <v>2.160414810021225</v>
       </c>
       <c r="F2077" t="n">
         <v>0.9266416855143017</v>
@@ -49345,10 +49345,10 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.903896208203705</v>
+        <v>-4.929500450275168</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.379434900861328</v>
+        <v>2.369193204032743</v>
       </c>
       <c r="F2078" t="n">
         <v>0.9266416855143017</v>
@@ -49368,10 +49368,10 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.903802240186333</v>
+        <v>-4.929406482257796</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.378651154980366</v>
+        <v>2.368409458151781</v>
       </c>
       <c r="F2079" t="n">
         <v>0.9270115468616197</v>
@@ -49391,10 +49391,10 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.052168467842478</v>
+        <v>-5.07777270991394</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.313536649862262</v>
+        <v>2.303294953033677</v>
       </c>
       <c r="F2080" t="n">
         <v>0.9270115468616197</v>
@@ -49414,10 +49414,10 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.051220044724439</v>
+        <v>-5.076824286795902</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.313916019109478</v>
+        <v>2.303674322280893</v>
       </c>
       <c r="F2081" t="n">
         <v>0.9270115468616197</v>
@@ -49437,10 +49437,10 @@
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.15148986268346</v>
+        <v>-5.177094104754923</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.286535699906961</v>
+        <v>2.276294003078376</v>
       </c>
       <c r="F2082" t="n">
         <v>0.9270115468616197</v>
@@ -49460,10 +49460,10 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.145497615894649</v>
+        <v>-5.171101857966112</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.290878597046873</v>
+        <v>2.280636900218288</v>
       </c>
       <c r="F2083" t="n">
         <v>0.9270115468616197</v>
@@ -49483,10 +49483,10 @@
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.056939654763881</v>
+        <v>-5.082543896835344</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.319955917516949</v>
+        <v>2.309714220688365</v>
       </c>
       <c r="F2084" t="n">
         <v>0.9270115468616197</v>
@@ -49506,10 +49506,10 @@
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.039180577260807</v>
+        <v>-5.06478481933227</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.326368225957175</v>
+        <v>2.31612652912859</v>
       </c>
       <c r="F2085" t="n">
         <v>0.9270115468616197</v>
@@ -49529,10 +49529,10 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.939550426211739</v>
+        <v>-4.965154668283202</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.379002472285388</v>
+        <v>2.368760775456804</v>
       </c>
       <c r="F2086" t="n">
         <v>1.026641697910687</v>
@@ -49552,10 +49552,10 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.98894993490075</v>
+        <v>-5.014554176972213</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.548396934308511</v>
+        <v>2.538155237479926</v>
       </c>
       <c r="F2087" t="n">
         <v>1.036900531342432</v>
@@ -49575,10 +49575,10 @@
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.782265461258374</v>
+        <v>-4.807869703329837</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.618259396868323</v>
+        <v>2.608017700039738</v>
       </c>
       <c r="F2088" t="n">
         <v>1.243585004984808</v>
@@ -49598,10 +49598,10 @@
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.816422356255901</v>
+        <v>-4.842026598327363</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.606598152523418</v>
+        <v>2.596356455694832</v>
       </c>
       <c r="F2089" t="n">
         <v>1.160001235443995</v>
@@ -49621,10 +49621,10 @@
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.723832877194444</v>
+        <v>-4.749437119265907</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.997131058137668</v>
+        <v>2.986889361309083</v>
       </c>
       <c r="F2090" t="n">
         <v>1.160001235443995</v>
@@ -49644,10 +49644,10 @@
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.783721505017994</v>
+        <v>-4.809325747089457</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.977738718575351</v>
+        <v>2.967497021746766</v>
       </c>
       <c r="F2091" t="n">
         <v>1.145879320756531</v>
@@ -49667,10 +49667,10 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.731505195221652</v>
+        <v>-4.757109437293115</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.048455183817415</v>
+        <v>3.03821348698883</v>
       </c>
       <c r="F2092" t="n">
         <v>1.145879320756531</v>
@@ -49690,10 +49690,10 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.699607678136407</v>
+        <v>-4.72521192020787</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.070028160861524</v>
+        <v>3.059786464032939</v>
       </c>
       <c r="F2093" t="n">
         <v>1.177776837841776</v>
@@ -49713,10 +49713,10 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.714363002336547</v>
+        <v>-4.73996724440801</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.059763615220665</v>
+        <v>3.04952191839208</v>
       </c>
       <c r="F2094" t="n">
         <v>1.177776837841776</v>
@@ -49736,10 +49736,10 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.664898378966636</v>
+        <v>-4.690502621038099</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.070473967984909</v>
+        <v>3.060232271156324</v>
       </c>
       <c r="F2095" t="n">
         <v>1.227241461211688</v>
@@ -49759,10 +49759,10 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.50179038681302</v>
+        <v>-4.527394628884483</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.13212483256129</v>
+        <v>3.121883135732705</v>
       </c>
       <c r="F2096" t="n">
         <v>1.390349453365303</v>
@@ -49782,10 +49782,10 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.368982761315854</v>
+        <v>-4.394587003387317</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.194294919451285</v>
+        <v>3.184053222622699</v>
       </c>
       <c r="F2097" t="n">
         <v>1.390349453365303</v>
@@ -49805,10 +49805,10 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.431690677790412</v>
+        <v>-4.457294919861875</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.170069217847583</v>
+        <v>3.159827521018998</v>
       </c>
       <c r="F2098" t="n">
         <v>1.327641536890745</v>
@@ -49828,10 +49828,10 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.383682553946719</v>
+        <v>-4.409286796018182</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.152181884175413</v>
+        <v>3.141940187346827</v>
       </c>
       <c r="F2099" t="n">
         <v>1.327641536890745</v>
@@ -49845,16 +49845,16 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.92616954360033</v>
+        <v>3.900467959550761</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.304856896763129</v>
+        <v>-4.330461138834591</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.187644400606799</v>
+        <v>3.177402703778214</v>
       </c>
       <c r="F2100" t="n">
         <v>1.406467194074336</v>

--- a/tame_output/ON/bt/strategyON_20240928.xlsx
+++ b/tame_output/ON/bt/strategyON_20240928.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>179.4%</t>
+          <t>186.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.4%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.6%</t>
+          <t>-593.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-58.5%</t>
+          <t>-58.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-295.8%</t>
+          <t>-298.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-83.3%</t>
+          <t>-80.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.2%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>129.4%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2100"/>
+  <dimension ref="A1:G2101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.236166003327313</v>
+        <v>-5.200279286611126</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.02185615028424</v>
+        <v>1.036210836970715</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4017410483150389</v>
+        <v>-0.3701661656154544</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.87563434693989</v>
+        <v>2.89457927655964</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.644754780507992</v>
+        <v>-5.608868063791804</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.857182183426727</v>
+        <v>0.8715368701132022</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7787549427961329</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.629242624646241</v>
+        <v>2.648187554265992</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.758515192530857</v>
+        <v>-5.722628475814669</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.806863451089042</v>
+        <v>0.8212181377755172</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7787549427961329</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.624428057117702</v>
+        <v>2.643372986737453</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.174907066817855</v>
+        <v>-6.139020350101666</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6383007519831203</v>
+        <v>0.6526554386695955</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7787549427961329</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.622422107726579</v>
+        <v>2.64136703734633</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.536080696634842</v>
+        <v>-6.500193979918654</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5040899907250038</v>
+        <v>0.5184446774114795</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7787549427961329</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.632680798395258</v>
+        <v>2.651625728015009</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.843452499561673</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.3772408346999669</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7787549427961329</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.628780363540954</v>
+        <v>2.647725293160704</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-6.891655316804017</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.3563646278580301</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.7787549427961329</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.627185283595955</v>
+        <v>2.646130213215705</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-7.058463976778379</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.2934201397974938</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8210382665092695</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.605594265297281</v>
+        <v>2.624539194917031</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.245183685087682</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.2147059519393695</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8210382665092695</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.601567960762878</v>
+        <v>2.620512890382629</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.628185073830313</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.06140329512073306</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8210382665092695</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.601465859441294</v>
+        <v>2.620410789061045</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.632671519031701</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.06218023301160747</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.8255247117106581</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.601345508291891</v>
+        <v>2.620290437911641</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-7.992201841535703</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>-0.0762815926919429</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.8255247117106581</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.606695811589941</v>
+        <v>2.625640741209692</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-8.042550904989923</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>-0.08850519811645396</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9074486578644647</v>
+        <v>-0.8758737751648802</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.584402393474585</v>
+        <v>2.603347323094336</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.140170182411319</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.1245111584632435</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.005067935285861</v>
+        <v>-0.9734930525862768</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.547817507263267</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.194241681919678</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1432462019450145</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.059139434794221</v>
+        <v>-1.027564552094636</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.518268163879823</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.197817468011426</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1391633192630715</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.084668356710713</v>
+        <v>-1.053093474011129</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.50846400784857</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.231470306519899</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1481419001820248</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.185081724627751</v>
+        <v>-1.153506841928166</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.452698541582784</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.370556421138756</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.1884046445361465</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.292592956547023</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.384618574304891</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.5456808385253</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2438991907432468</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.467717373933567</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.294099144620481</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.780132932539789</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3448991932506389</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.467717373933567</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.286879979718885</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.884507663566236</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.3933212764351937</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.572092104960013</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.217582950329041</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-9.04702112926482</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.4572108728760709</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.669725535378699</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.160118681916386</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.173057922633109</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.5049318615942719</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.644473912568957</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.177963384231346</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.115986150737179</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.478112817149499</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.644473912568957</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.181953719917747</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.257657992461299</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.5362567807378888</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.644473912568957</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.180478493019005</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.208067148036465</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.5013670328030826</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.594883068144123</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.225286409838778</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.059148813564608</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.4548508326610232</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.56363347740895</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.230985030633199</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.833303660845198</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.3549336985370504</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.521706801821786</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.265720109021705</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.708725004507606</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.3039630914459548</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.521706801821786</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.266859253577764</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.683688322939096</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.2913146446564432</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.496377714271051</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.284690480270313</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.611555147651215</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.256727670302654</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.496377714271051</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.29042418450895</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.644238203941597</v>
+        <v>-8.608351487225409</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2795381552126726</v>
+        <v>-0.2651834685261969</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.493174053845244</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.263664188750818</v>
+        <v>2.282609118370568</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.550779169956373</v>
+        <v>-8.514892453240185</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2520380229314902</v>
+        <v>-0.237683336245015</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.493174053845244</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.25378070743791</v>
+        <v>2.272725637057661</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.512869468283869</v>
+        <v>-8.504239271686753</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2387087027618624</v>
+        <v>-0.2352566241230161</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.493174053845244</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.251946146938536</v>
+        <v>2.270891076558287</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.414962429607378</v>
+        <v>-8.406332233010263</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1998462022647267</v>
+        <v>-0.1963941236258804</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.456763186684273</v>
+        <v>-1.425188303984688</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.292437281881409</v>
+        <v>2.31138221150116</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097246</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.39100888863142</v>
+        <v>-8.382378692034305</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1895962797288502</v>
+        <v>-0.1861442010900038</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.432809645708315</v>
+        <v>-1.40123476300873</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.307477912612478</v>
+        <v>2.326422842232228</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.126948950308623</v>
+        <v>-8.118318753711508</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.09723262056148352</v>
+        <v>-0.09378054192263718</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.137174824685934</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.452653559444403</v>
+        <v>2.471598489064154</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.419869326803785</v>
+        <v>-7.41123913020667</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1828121951801509</v>
+        <v>0.1862642738189972</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.137174824685934</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.449866525784102</v>
+        <v>2.468811455403853</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.379685028437595</v>
+        <v>-7.371054831840479</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1992295384144684</v>
+        <v>0.2026816170533148</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.128565409019328</v>
+        <v>-1.096990526319743</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.474320728691658</v>
+        <v>2.493265658311409</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.216285157498232</v>
+        <v>-7.207654960901117</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2639563080109704</v>
+        <v>0.2674083866498167</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9651655380799653</v>
+        <v>-0.9335906553803808</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.571727472476033</v>
+        <v>2.590672402095783</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.058167778119457</v>
+        <v>-7.049537581522341</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3351276886003332</v>
+        <v>0.338579767239179</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8070481587011898</v>
+        <v>-0.7754732760016053</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.67452232894115</v>
+        <v>2.693467258560901</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.908501387111942</v>
+        <v>-6.899871190514826</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3921020346903799</v>
+        <v>0.3955541133292262</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7141446674586539</v>
+        <v>-0.6825697847590694</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.727372213373712</v>
+        <v>2.746317142993463</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.776225913481055</v>
+        <v>-6.76759571688394</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.346273010149889</v>
+        <v>0.3497250887887353</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5818691938277673</v>
+        <v>-0.5502943111281827</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.707998283559399</v>
+        <v>2.72694321317915</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.604364697916153</v>
+        <v>-6.595734501319037</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4178325570634867</v>
+        <v>0.421284635702333</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4100079782628644</v>
+        <v>-0.3784330955632799</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.813930073585978</v>
+        <v>2.832875003205728</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.519400031186834</v>
+        <v>-6.510769834589718</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4647247649788731</v>
+        <v>0.4681768436177194</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3250433115335448</v>
+        <v>-0.2934684288339603</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.877815214847228</v>
+        <v>2.896760144466979</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.624990020959938</v>
+        <v>-6.616359824362823</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2945128394704128</v>
+        <v>0.2979649181092592</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4306333013066492</v>
+        <v>-0.3990584186070646</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.686485291384147</v>
+        <v>2.705430221003898</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.556755436334511</v>
+        <v>-6.548125239737395</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3703510151976701</v>
+        <v>0.3738030938365164</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4122179784341132</v>
+        <v>-0.3806430957345286</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.746078826984755</v>
+        <v>2.765023756604506</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.408815394926911</v>
+        <v>-6.400185198329796</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3129062231223028</v>
+        <v>0.3163583017611491</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3918970625255556</v>
+        <v>-0.3603221798259711</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.641650567891482</v>
+        <v>2.660595497511233</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.355845872672923</v>
+        <v>-6.347215676075807</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3253800457704199</v>
+        <v>0.3288321244092662</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3073526575719822</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.664718294990398</v>
+        <v>2.683663224610148</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.190057676712632</v>
+        <v>-6.181427480115516</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3847347120594433</v>
+        <v>0.3881867906982892</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3073526575719822</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.657757682895304</v>
+        <v>2.676702612515055</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.156694470233863</v>
+        <v>-6.148064273636748</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4125423490320936</v>
+        <v>0.41599442767094</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3073526575719822</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.672220037276448</v>
+        <v>2.691164966896198</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.048435333111342</v>
+        <v>-6.039805136514226</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4503781243402973</v>
+        <v>0.4538302029791437</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3073526575719822</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.666752157735643</v>
+        <v>2.685697087355393</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.925144198294211</v>
+        <v>-5.916514001697095</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4971926722777269</v>
+        <v>0.5006447509165728</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2156364054544362</v>
+        <v>-0.1840615227548517</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.738224932636498</v>
+        <v>2.757169862256248</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.87244733116292</v>
+        <v>-5.863817134565804</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5259723973675685</v>
+        <v>0.5294244760064148</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1313646556235605</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.777544031152598</v>
+        <v>2.796488960772348</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.628681889179475</v>
+        <v>-5.62005169258236</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.619259282507997</v>
+        <v>0.6227113611468429</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1313646556235605</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.773324739499648</v>
+        <v>2.792269669119399</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.538906216803003</v>
+        <v>-5.530276020205887</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6572938653786018</v>
+        <v>0.6607459440174481</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.06976521070925051</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.81240872036825</v>
+        <v>2.831353649988001</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.289055822853928</v>
+        <v>-5.280425626256813</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7499760979419339</v>
+        <v>0.7534281765807798</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.06976521070925051</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.805150795351952</v>
+        <v>2.824095724971703</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.113163730386496</v>
+        <v>-5.104533533789381</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8239320584495551</v>
+        <v>0.8273841370884014</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.06976521070925051</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.808749918872601</v>
+        <v>2.827694848492352</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.941717267364033</v>
+        <v>-4.933087070766917</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9058381497130943</v>
+        <v>0.9092902283519406</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.07010636961362809</v>
+        <v>0.1016812523132126</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.924945302740633</v>
+        <v>2.943890232360383</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.861694980254912</v>
+        <v>-4.853064783657796</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9368675421730397</v>
+        <v>0.940319620811886</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1501286567227491</v>
+        <v>0.1817035394223336</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.971979152622402</v>
+        <v>2.990924082242153</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.798059238020977</v>
+        <v>-4.789429041423862</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9670166401209308</v>
+        <v>0.9704687187597769</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.2453392816562681</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.01485539901708</v>
+        <v>3.033800328636831</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.704361919804582</v>
+        <v>-4.695731723207467</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9856898261912845</v>
+        <v>0.9891419048301306</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.2453392816562681</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.996049657800876</v>
+        <v>3.014994587420627</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.714864542869871</v>
+        <v>-4.706781117711595</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9832318535900462</v>
+        <v>0.9864652236533569</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.2342898871521405</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.99149116058658</v>
+        <v>3.010108027343027</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.602378282200997</v>
+        <v>-4.594294857042719</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.032155671692416</v>
+        <v>1.035389041755727</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.2342898871521405</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.9954204744214</v>
+        <v>3.014037341177847</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.584664595323131</v>
+        <v>-4.576581170164854</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.039919730360902</v>
+        <v>1.043153100424213</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2374712160490573</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>3.016624722433337</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.461190324010113</v>
+        <v>-4.453106898851836</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.086307510106103</v>
+        <v>1.089540880169414</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.2374712160490573</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>3.013622793653331</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.241169525973103</v>
+        <v>-4.233086100814825</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.175894866331522</v>
+        <v>1.179128236394833</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3476629498562918</v>
+        <v>0.3786910611170375</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.081316870948286</v>
+        <v>3.099933737704733</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.108301836909825</v>
+        <v>-4.100218411751547</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.244936124758656</v>
+        <v>1.248169494821967</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3476629498562918</v>
+        <v>0.3786910611170375</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.097211053750109</v>
+        <v>3.115827920506557</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.988128753545326</v>
+        <v>-3.980045328387049</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.294151202544757</v>
+        <v>1.297384572608068</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4678360332207907</v>
+        <v>0.4988641444815365</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.170460748209111</v>
+        <v>3.189077614965558</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576999</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.852875392215349</v>
+        <v>-3.844791967057072</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.358340649638188</v>
+        <v>1.361574019701499</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6030893945507678</v>
+        <v>0.6341175058115136</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.261700867568536</v>
+        <v>3.280317734324984</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942105</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.912750219573041</v>
+        <v>-3.904666794414764</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.320428210096537</v>
+        <v>1.323661580159848</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5432145671930757</v>
+        <v>0.5742426784538215</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.211813462555347</v>
+        <v>3.230430329311794</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.792929988662204</v>
+        <v>-3.784846563503927</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.38364547169508</v>
+        <v>1.386878841758391</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5432145671930757</v>
+        <v>0.5742426784538215</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.227102631789556</v>
+        <v>3.245719498546003</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.79539969512401</v>
+        <v>-3.787316269965733</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.290301788432799</v>
+        <v>1.293535158496111</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5407448607312695</v>
+        <v>0.5717729719920153</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.133265007234913</v>
+        <v>3.151881873991361</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003603</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.86376988144802</v>
+        <v>-3.855686456289742</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.182215575388497</v>
+        <v>1.185448945451808</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5810486710282302</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.058092288141944</v>
+        <v>3.076709154898391</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508371</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.975642161074171</v>
+        <v>-3.967558735915893</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.127903372169928</v>
+        <v>1.131136742233239</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5810486710282302</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.048528996773835</v>
+        <v>3.067145863530282</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.959667495587903</v>
+        <v>-3.951584070429625</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.100867763288462</v>
+        <v>1.104101133351774</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5810486710282302</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.015103521697863</v>
+        <v>3.03372038845431</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.784193235795434</v>
+        <v>-3.776109810637156</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.175624699197238</v>
+        <v>1.178858069260549</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5810486710282302</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.01967075368965</v>
+        <v>3.038287620446098</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.776268861210519</v>
+        <v>-3.768185436052242</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.154536477792411</v>
+        <v>1.157769847855722</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5810486710282302</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.995412782450857</v>
+        <v>3.014029649207305</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111296</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.76999065864067</v>
+        <v>-3.761907233482393</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.0855860722218</v>
+        <v>1.088819442285111</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5562987623373334</v>
+        <v>0.5873268735980792</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.927718017394216</v>
+        <v>2.946334884150664</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.710138039436947</v>
+        <v>-3.70205461427867</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.119699506335422</v>
+        <v>1.122932876398733</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5562987623373334</v>
+        <v>0.5873268735980792</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.937890403826349</v>
+        <v>2.956507270582796</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.62389457641057</v>
+        <v>-3.615811151252292</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.149143162119833</v>
+        <v>1.152376532183144</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5562987623373334</v>
+        <v>0.5873268735980792</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.932836674400209</v>
+        <v>2.951453541156657</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.66920139580955</v>
+        <v>-3.661117970651272</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.122796209804767</v>
+        <v>1.126029579868078</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5154885993281026</v>
+        <v>0.5465167105888484</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.900126352039196</v>
+        <v>2.918743218795644</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.698234500511851</v>
+        <v>-3.690151075353574</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.111734840956947</v>
+        <v>1.114968211020259</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5154885993281026</v>
+        <v>0.5465167105888484</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.900678225072298</v>
+        <v>2.919295091828745</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.605424019060992</v>
+        <v>-3.597340593902715</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.078131725428657</v>
+        <v>1.081365095491968</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.608299080778962</v>
+        <v>0.6393271920397078</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.885637205834179</v>
+        <v>2.904254072590627</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.64981348839042</v>
+        <v>-3.641730063232142</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.062249413621487</v>
+        <v>1.065482783684798</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5639096114495343</v>
+        <v>0.5949377227102801</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.860877000161123</v>
+        <v>2.879493866917571</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.629309794504922</v>
+        <v>-3.621226369346645</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.065526599687409</v>
+        <v>1.06875996975072</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5844133053350317</v>
+        <v>0.6154414165957774</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.868254925004145</v>
+        <v>2.886871791760592</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.712981891217254</v>
+        <v>-3.704898466058977</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.037549056833143</v>
+        <v>1.040782426896454</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5844133053350317</v>
+        <v>0.6154414165957774</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.873746220834812</v>
+        <v>2.89236308759126</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.740762289118607</v>
+        <v>-3.73267886396033</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.037934099441141</v>
+        <v>1.041167469504452</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5566329074336787</v>
+        <v>0.5876610186944244</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.868575183862539</v>
+        <v>2.887192050618987</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.859142961848746</v>
+        <v>-3.851059536690468</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8289375503497387</v>
+        <v>0.8321709204130499</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4894150552827025</v>
+        <v>0.5204431665434482</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.666600192572607</v>
+        <v>2.685217059329054</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.967757040292077</v>
+        <v>-3.959673615133799</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.905641579691612</v>
+        <v>0.9088749497549229</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4894150552827025</v>
+        <v>0.5204431665434482</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.786749853291812</v>
+        <v>2.80536672004826</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.932348002043934</v>
+        <v>-3.924264576885657</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.934318221093192</v>
+        <v>0.9375515911565031</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4894150552827025</v>
+        <v>0.5204431665434482</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.801262879394135</v>
+        <v>2.819879746150583</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.940809170699395</v>
+        <v>-3.932725745541118</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9283531949733763</v>
+        <v>0.9315865650366872</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4809538866272414</v>
+        <v>0.5119819978879872</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.793605619543228</v>
+        <v>2.812222486299675</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532489</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.763692840664229</v>
+        <v>-3.755609415505952</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.995928755832745</v>
+        <v>0.9991621258960561</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4809538866272414</v>
+        <v>0.5119819978879872</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.79033464838853</v>
+        <v>2.808951515144977</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793905</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.808785085497775</v>
+        <v>-3.800701660339497</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9785752496612401</v>
+        <v>0.981808619724551</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4190578434578516</v>
+        <v>0.4500859547185974</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.753880414248809</v>
+        <v>2.772497281005256</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.629409664259007</v>
+        <v>-3.621326239100729</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.044112393463162</v>
+        <v>1.047345763526472</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5758346016285703</v>
+        <v>0.606862712889316</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.841733444457655</v>
+        <v>2.860350311214102</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.674423877779613</v>
+        <v>-3.666340452621335</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.006914163386509</v>
+        <v>1.01014753344982</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5454857063139656</v>
+        <v>0.5765138175747114</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.804331562600482</v>
+        <v>2.822948429356929</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.941428388052048</v>
+        <v>-3.933344962893771</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9058039216164804</v>
+        <v>0.9090372916797913</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3511226682710171</v>
+        <v>0.3821507795317629</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.693405302113658</v>
+        <v>2.712022168870106</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.042626169489221</v>
+        <v>-4.034542744330944</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8645287309381127</v>
+        <v>0.8677621010014236</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2827138547256979</v>
+        <v>0.3137419659864437</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.651563935882968</v>
+        <v>2.670180802639416</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.036115202874909</v>
+        <v>-4.028031777716631</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8647330791381544</v>
+        <v>0.8679664492014654</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2827138547256979</v>
+        <v>0.3137419659864437</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.649163897437285</v>
+        <v>2.667780764193732</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.017077075167611</v>
+        <v>-4.008993650009334</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8688730494293182</v>
+        <v>0.8721064194926293</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2245302433945033</v>
+        <v>0.2555583546552491</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.610778449846813</v>
+        <v>2.629395316603261</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.069592877442432</v>
+        <v>-4.061509452284154</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9671611301535805</v>
+        <v>0.9703945002168914</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2245302433945033</v>
+        <v>0.2555583546552491</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.730072851481003</v>
+        <v>2.748689718237451</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.073001188877011</v>
+        <v>-4.064917763718734</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.966631134565882</v>
+        <v>0.9698645046291932</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2570468124038807</v>
+        <v>0.2880749236646265</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.750416121872763</v>
+        <v>2.769032988629211</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.053645052983164</v>
+        <v>-4.045561627824886</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.980382119320347</v>
+        <v>0.9836154893836579</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2570468124038807</v>
+        <v>0.2880749236646265</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.756424652269689</v>
+        <v>2.775041519026137</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.126974581721257</v>
+        <v>-4.118891156562979</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8490005291023095</v>
+        <v>0.8522338991656204</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2574414748235027</v>
+        <v>0.2884695860842484</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.654611670998662</v>
+        <v>2.673228537755109</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.210795802995955</v>
+        <v>-4.202712377837678</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8182656621239111</v>
+        <v>0.821499032187222</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2574414748235027</v>
+        <v>0.2884695860842484</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.657405292530143</v>
+        <v>2.67602215928659</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.204643096943171</v>
+        <v>-4.196559671784893</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8213890929366832</v>
+        <v>0.8246224629999941</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2635941808762869</v>
+        <v>0.2946222921370327</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.661759264553472</v>
+        <v>2.680376131309919</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.221452395093673</v>
+        <v>-4.213368969935395</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8137458504165926</v>
+        <v>0.8169792204799036</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2467848827257853</v>
+        <v>0.2778129939865311</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.650754162403281</v>
+        <v>2.669371029159729</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.15915439631755</v>
+        <v>-4.151070971159273</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9050006037238625</v>
+        <v>0.9082339737871734</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2920791470002274</v>
+        <v>0.3231072582609731</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.744266274764767</v>
+        <v>2.762883141521215</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.957364198652392</v>
+        <v>-3.949280773494115</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7880086845040526</v>
+        <v>0.7912420545673637</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4900973391693817</v>
+        <v>0.5211254504301275</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.665369191780387</v>
+        <v>2.683986058536834</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.008250911338587</v>
+        <v>-4.00016748618031</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.83794423175175</v>
+        <v>0.841177601815061</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4392106264831871</v>
+        <v>0.4702387377439329</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.705127396490846</v>
+        <v>2.723744263247293</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.92164016868878</v>
+        <v>-3.913556743530502</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8872162649277167</v>
+        <v>0.8904496349910276</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5178363576883454</v>
+        <v>0.5488644689490911</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.766930571329984</v>
+        <v>2.785547438086431</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.981849466694064</v>
+        <v>-3.973766041535787</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8616685265502744</v>
+        <v>0.8649018966135855</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4576270596830608</v>
+        <v>0.4886551709438066</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.729340973351485</v>
+        <v>2.747957840107933</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397797</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.932662818009713</v>
+        <v>-3.924579392851435</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8798348040639437</v>
+        <v>0.8830681741272546</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4576270596830608</v>
+        <v>0.4886551709438066</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.727832591391413</v>
+        <v>2.746449458147861</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316252</v>
+        <v>3.833513460316253</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.888289686371144</v>
+        <v>-3.880206261212867</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8974469241548073</v>
+        <v>0.9006802942181182</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5020001913216294</v>
+        <v>0.5330283025823752</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.754319337809991</v>
+        <v>2.772936204566438</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.853558365052643</v>
+        <v>-3.845474939894366</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9057332468207981</v>
+        <v>0.9089666168841091</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5020001913216294</v>
+        <v>0.5330283025823752</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.748713131948581</v>
+        <v>2.767329998705029</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.805902634491588</v>
+        <v>-3.79781920933331</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9311772960730249</v>
+        <v>0.9344106661363361</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5496559218826851</v>
+        <v>0.5806840331434309</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.78368832731302</v>
+        <v>2.802305194069467</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.705384475992833</v>
+        <v>-3.697301050834556</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9762769328472516</v>
+        <v>0.9795103029105627</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6501740803814396</v>
+        <v>0.6812021916421854</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.848891595786997</v>
+        <v>2.867508462543444</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.689479146560481</v>
+        <v>-3.681395721402203</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9693937370960648</v>
+        <v>0.9726271071593759</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5710614196722008</v>
+        <v>0.6020895309329466</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.788178671837326</v>
+        <v>2.806795538593773</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.644640744952083</v>
+        <v>-3.636557319793805</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9914268003500526</v>
+        <v>0.9946601704133637</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5756048526170703</v>
+        <v>0.6066329638778161</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.795002434214876</v>
+        <v>2.813619300971324</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.664139201194091</v>
+        <v>-3.656055776035813</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9877883574843274</v>
+        <v>0.9910217275476385</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.527520211337166</v>
+        <v>0.5585483225979118</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.770312589078011</v>
+        <v>2.788929455834459</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.61993636410819</v>
+        <v>-3.611852938949913</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.011349094846525</v>
+        <v>1.014582464909836</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5717230484230664</v>
+        <v>0.6027511596838122</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.802713893857389</v>
+        <v>2.821330760613836</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.627496029945237</v>
+        <v>-3.61941260478696</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.006735228980953</v>
+        <v>1.009968599044265</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6265264524328857</v>
+        <v>0.6575545636936315</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.834005936732528</v>
+        <v>2.852622803488976</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.469204612405965</v>
+        <v>-3.461121187247687</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.121299561179702</v>
+        <v>1.124532931243013</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6265264524328857</v>
+        <v>0.6575545636936315</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.885253701915568</v>
+        <v>2.903870568672015</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.261562608771489</v>
+        <v>-3.253479183613211</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.202797067227746</v>
+        <v>1.206030437291057</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8341684560673619</v>
+        <v>0.8651965673281077</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.008279608690507</v>
+        <v>3.026896475446954</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.210530516048961</v>
+        <v>-3.202447090890683</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.218158132555027</v>
+        <v>1.221391502618338</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8852005487898899</v>
+        <v>0.9162286600506356</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.033847092562294</v>
+        <v>3.052463959318741</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.145306334921755</v>
+        <v>-3.137222909763477</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.261435209098614</v>
+        <v>1.264668579161925</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9504247299170955</v>
+        <v>0.9814528411778413</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.090169005331322</v>
+        <v>3.108785872087769</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.107879314850621</v>
+        <v>-3.099795889692344</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.272366989426348</v>
+        <v>1.275600359489659</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9556762679462771</v>
+        <v>0.9867043792070229</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.089280900448111</v>
+        <v>3.107897767204558</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.106521329877076</v>
+        <v>-3.098437904718798</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.274166975747006</v>
+        <v>1.277400345810318</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.030014393484096</v>
+        <v>1.061042504744842</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.135140568102043</v>
+        <v>3.15375743485849</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636289</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.078108066777192</v>
+        <v>-3.070024641618915</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.446090052008171</v>
+        <v>1.449323422071482</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9710388307376669</v>
+        <v>1.002066941998413</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.260313001475396</v>
+        <v>3.278929868231844</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957628</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.003325805752179</v>
+        <v>-2.995242380593902</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.596115865635993</v>
+        <v>1.599349235699304</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.04582109176268</v>
+        <v>1.076849203023425</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.425295267308221</v>
+        <v>3.443912134064668</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.977241721488372</v>
+        <v>-2.969158296330094</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.598257475355375</v>
+        <v>1.601490845418686</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.04582109176268</v>
+        <v>1.076849203023425</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.41700324332208</v>
+        <v>3.435620110078527</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.889363808379251</v>
+        <v>-2.881280383220973</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.631601836182803</v>
+        <v>1.634835206246114</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.161746734186031</v>
+        <v>1.192774845446777</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.48475182435987</v>
+        <v>3.503368691116318</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.880471346985968</v>
+        <v>-2.87238792182769</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.652713226466908</v>
+        <v>1.655946596530218</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.161746734186031</v>
+        <v>1.192774845446777</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.502306230086661</v>
+        <v>3.520923096843109</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.048947463955846</v>
+        <v>-3.040864038797568</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.57717782708354</v>
+        <v>1.580411197146851</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.13379889846945</v>
+        <v>1.164827009730196</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.477392576061296</v>
+        <v>3.496009442817744</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.602691271326406</v>
+        <v>-2.594607846168128</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.736950001323178</v>
+        <v>1.740183371386489</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.039080228799817</v>
+        <v>1.070108340060563</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.401831071447379</v>
+        <v>3.420447938203826</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.579970167643253</v>
+        <v>-2.571886742484976</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.736702465293344</v>
+        <v>1.739935835356655</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.039080228799817</v>
+        <v>1.070108340060563</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.392495093944283</v>
+        <v>3.411111960700731</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.709171980937296</v>
+        <v>-2.701088555779018</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.843927865826896</v>
+        <v>1.847161235890207</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9098784155057749</v>
+        <v>0.9409065267665209</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.473880131819027</v>
+        <v>3.492496998575475</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.735046379411322</v>
+        <v>-2.726962954253044</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.870655928930932</v>
+        <v>1.873889298994243</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.954790024217516</v>
+        <v>0.985818135478262</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.537904919539718</v>
+        <v>3.556521786296166</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.727991689196148</v>
+        <v>-2.71990826403787</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.870153161006546</v>
+        <v>1.873386531069858</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9618447144326898</v>
+        <v>0.9928728256934358</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.538813089658368</v>
+        <v>3.557429956414815</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.70104046486966</v>
+        <v>-2.692957039711382</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.890939804381883</v>
+        <v>1.894173174445194</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.976725060460409</v>
+        <v>1.007753171721155</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.557747450919741</v>
+        <v>3.576364317676188</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.722584692700447</v>
+        <v>-2.71450126754217</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.066425245394528</v>
+        <v>2.069658615457839</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.976725060460409</v>
+        <v>1.007753171721155</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.741850583064701</v>
+        <v>3.760467449821148</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.744992810505319</v>
+        <v>-2.736909385347042</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.049578693175572</v>
+        <v>2.052812063238884</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.976725060460409</v>
+        <v>1.007753171721155</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.733967277967694</v>
+        <v>3.752584144724141</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.77321704608292</v>
+        <v>-2.765133620924642</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.04034299849417</v>
+        <v>2.043576368557481</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9947018129117176</v>
+        <v>1.025729924172464</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.746807328988116</v>
+        <v>3.765424195744564</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.782657971971449</v>
+        <v>-2.774574546813172</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.092820345860605</v>
+        <v>2.096053715923916</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.117128930455109</v>
+        <v>1.148157041715855</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.876517317235998</v>
+        <v>3.895134183992446</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.871534603139923</v>
+        <v>-2.863451177981646</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.060160787938516</v>
+        <v>2.063394158001827</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.028252299286635</v>
+        <v>1.059280410547381</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.826082433080215</v>
+        <v>3.844699299836662</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347707</v>
+        <v>3.727898186347709</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.947864580740829</v>
+        <v>-2.939781155582552</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.027740609791929</v>
+        <v>2.03097397985524</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.028252299286635</v>
+        <v>1.059280410547381</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.82419424597399</v>
+        <v>3.842811112730438</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.102821366140958</v>
+        <v>-3.094737940982681</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.96057812523474</v>
+        <v>1.963811495298051</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8732955138865059</v>
+        <v>0.904323625147252</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.726040404336775</v>
+        <v>3.744657271093223</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234307</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.264389791668214</v>
+        <v>-3.256306366509936</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.89438476523399</v>
+        <v>1.897618135297301</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7465125900886266</v>
+        <v>0.7775407013493726</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.648404660268199</v>
+        <v>3.667021527024647</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389353</v>
+        <v>3.754596135389356</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.372690453538333</v>
+        <v>-3.364607028380056</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.864137907351861</v>
+        <v>1.867371277415172</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7465125900886266</v>
+        <v>0.7775407013493726</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.661478067134118</v>
+        <v>3.680094933890566</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.390494425259077</v>
+        <v>-3.3824110001008</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.849021515446503</v>
+        <v>1.852254885509814</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6759779671834254</v>
+        <v>0.7070060784441714</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.611162490173938</v>
+        <v>3.629779356930385</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.41839521236855</v>
+        <v>-3.410311787210273</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.836385241729716</v>
+        <v>1.839618611793027</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6413810430404906</v>
+        <v>0.6724091543012366</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.588928376815179</v>
+        <v>3.607545243571626</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.540921315071444</v>
+        <v>-3.532837889913166</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.784139244625757</v>
+        <v>1.787372614689068</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5188549403375967</v>
+        <v>0.5498830515983427</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.512177159170641</v>
+        <v>3.530794025927089</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.771435811257033</v>
+        <v>-3.763352386098755</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.758639405742025</v>
+        <v>1.761872775805337</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.288340444152008</v>
+        <v>0.319368555412754</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.440574421049792</v>
+        <v>3.459191287806239</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.120180896481476</v>
+        <v>-4.112097471323199</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.759453090654095</v>
+        <v>1.762686460717406</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1795924902331102</v>
+        <v>0.2106206014938562</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.5156373677003</v>
+        <v>3.534254234456748</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.274167314257617</v>
+        <v>-4.266083889099339</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.766838792689279</v>
+        <v>1.77007216275259</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1795924902331102</v>
+        <v>0.2106206014938562</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.58461763684594</v>
+        <v>3.603234503602387</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.478766749120625</v>
+        <v>-4.470683323962348</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.671050220864196</v>
+        <v>1.674283590927507</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1795924902331102</v>
+        <v>0.2106206014938562</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.570668838966061</v>
+        <v>3.589285705722508</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.73124190312835</v>
+        <v>-4.723158477970072</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.58193064831652</v>
+        <v>1.585164018379831</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1795924902331102</v>
+        <v>0.2106206014938562</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.582539328021475</v>
+        <v>3.601156194777922</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.024137659607762</v>
+        <v>-5.016054234449484</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.465982880243699</v>
+        <v>1.46921625030701</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1795924902331102</v>
+        <v>0.2106206014938562</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.583749862540418</v>
+        <v>3.602366729296866</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.21080178774257</v>
+        <v>-5.202718362584292</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.395438971217097</v>
+        <v>1.398672341280408</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1528535194085503</v>
+        <v>0.1838816306692963</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.571828222273004</v>
+        <v>3.590445089029451</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.356822474656532</v>
+        <v>-5.348739049498255</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.332108549187702</v>
+        <v>1.335341919251013</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1437704276146933</v>
+        <v>0.1747985388754393</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.561456219932879</v>
+        <v>3.580073086689326</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830332</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.448536483766118</v>
+        <v>-5.44045305860784</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.457627002242912</v>
+        <v>1.460860372306223</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1437704276146933</v>
+        <v>0.1747985388754393</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.723660276631923</v>
+        <v>3.742277143388371</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071555</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.480188142826087</v>
+        <v>-5.472104717667809</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.439812976582738</v>
+        <v>1.443046346646049</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1386019703702531</v>
+        <v>0.1696300816309991</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.715405840249073</v>
+        <v>3.734022707005521</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868151</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.549254197399024</v>
+        <v>-5.541170772240746</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.422415972322055</v>
+        <v>1.425649342385366</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07623109287664309</v>
+        <v>0.1072592041373891</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.688212731321398</v>
+        <v>3.706829598077846</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332697</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.651230319647431</v>
+        <v>-5.643146894489154</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.390551161878594</v>
+        <v>1.393784531941905</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.02574502937176448</v>
+        <v>0.005283081888981522</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.635952696428256</v>
+        <v>3.654569563184704</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231814</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.54122403617021</v>
+        <v>-5.533140611011932</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.426706562513658</v>
+        <v>1.429939932576969</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.002540457454489276</v>
+        <v>0.02848765380625673</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.642028326822797</v>
+        <v>3.660645193579244</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.398164460429284</v>
+        <v>-5.390081035271006</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.488180403532003</v>
+        <v>1.491413773595314</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.005472969135490002</v>
+        <v>0.03650108039623601</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.651086393498758</v>
+        <v>3.669703260255206</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.096717734957446</v>
+        <v>-5.088634309799168</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.616019976603274</v>
+        <v>1.619253346666585</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3069196946073273</v>
+        <v>0.3379478058680733</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.839215311664397</v>
+        <v>3.857832178420844</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.12130797919263</v>
+        <v>-5.113224554034352</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.607155056661911</v>
+        <v>1.610388426725222</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3069196946073273</v>
+        <v>0.3379478058680733</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.840186489417107</v>
+        <v>3.858803356173555</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.07026960318611</v>
+        <v>-5.062186178027832</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.628413311444274</v>
+        <v>1.631646681507585</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3069196946073273</v>
+        <v>0.3379478058680733</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.841029393796863</v>
+        <v>3.859646260553311</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.041420926362649</v>
+        <v>-5.033337501204372</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.658990881047804</v>
+        <v>1.662224251111115</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3357683714307875</v>
+        <v>0.3667964826915335</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.877376698765085</v>
+        <v>3.895993565521532</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.944786014344009</v>
+        <v>-4.936702589185732</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.513828841979195</v>
+        <v>1.517062212042506</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4324032834494275</v>
+        <v>0.4634313947101735</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.751541642100203</v>
+        <v>3.77015850885665</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077644</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.875748003395541</v>
+        <v>-4.867664578237264</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.544946090432546</v>
+        <v>1.548179460495857</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5014412943978955</v>
+        <v>0.5324694056586415</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.796466492743248</v>
+        <v>3.815083359499696</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.775028860833463</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.71125166920458</v>
+        <v>-4.703168244046302</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.595171443185013</v>
+        <v>1.598404813248324</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6659376285888574</v>
+        <v>0.6969657398496034</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.879591112333908</v>
+        <v>3.898207979090355</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.634153067662707</v>
+        <v>-4.626069642504429</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.625198594238192</v>
+        <v>1.628431964301503</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6659376285888574</v>
+        <v>0.6969657398496034</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.878778822770338</v>
+        <v>3.897395689526785</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147911</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.644538262552596</v>
+        <v>-4.636454837394319</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.630913295407309</v>
+        <v>1.63414666547062</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6555524336989681</v>
+        <v>0.6865805449597141</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.882416484961476</v>
+        <v>3.901033351717924</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.663126421274821</v>
+        <v>-4.655042996116544</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.694315037694844</v>
+        <v>1.697548407758155</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6369642749767428</v>
+        <v>0.6679923862374888</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.942100595504566</v>
+        <v>3.960717462261014</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496556</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.663424967970857</v>
+        <v>-4.65534154281258</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.691064629834728</v>
+        <v>1.694297999898039</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6366657282807069</v>
+        <v>0.6676938395414529</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.938790478305243</v>
+        <v>3.957407345061691</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108861</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.56260183428043</v>
+        <v>-4.554518409122152</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.73592477825029</v>
+        <v>1.739158148313602</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6491299437650607</v>
+        <v>0.6801580550258067</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.950799902535247</v>
+        <v>3.969416769291694</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121472</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.371820473528022</v>
+        <v>-4.363737048369744</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.812366576029797</v>
+        <v>1.815599946093108</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8399113045174681</v>
+        <v>0.8709394157782141</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.065397972465234</v>
+        <v>4.084014839221682</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906085</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.2648571156786</v>
+        <v>-4.256773690520323</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.834988764907162</v>
+        <v>1.838222134970473</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8983759124772696</v>
+        <v>0.9294040237380156</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.080313582978712</v>
+        <v>4.09893044973516</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.209526527776838</v>
+        <v>-4.20144310261856</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.892087936679925</v>
+        <v>1.895321306743237</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9537065003790317</v>
+        <v>0.9847346116397777</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.148478872331828</v>
+        <v>4.167095739088276</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539899</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.197472400863875</v>
+        <v>-4.189388975705597</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.890596155346548</v>
+        <v>1.893829525409859</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9657606272919945</v>
+        <v>0.9967887385527405</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.149397916381043</v>
+        <v>4.168014783137491</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811014</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.238627520432096</v>
+        <v>-4.230544095273818</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.876014737703396</v>
+        <v>1.879248107766707</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9246055077237736</v>
+        <v>0.9556336189845196</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.126585474824246</v>
+        <v>4.145202341580694</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382925</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.170578957740566</v>
+        <v>-4.162495532582288</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.91608518865789</v>
+        <v>1.919318558721201</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9926540704153033</v>
+        <v>1.023682181676049</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.180265638317047</v>
+        <v>4.198882505073494</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013432</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.402179350910067</v>
+        <v>-4.394095925751789</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.843647701563684</v>
+        <v>1.846881071626995</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9926540704153033</v>
+        <v>1.023682181676049</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.200468308490641</v>
+        <v>4.219085175247089</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.66674720149897</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.452230896439286</v>
+        <v>-4.444147471281008</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.807233319418879</v>
+        <v>1.81046668948219</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9926540704153033</v>
+        <v>1.023682181676049</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.184074544557523</v>
+        <v>4.202691411313971</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.62733772901573</v>
+        <v>-4.619254303857453</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.697442499981767</v>
+        <v>1.700675870045078</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9926540704153033</v>
+        <v>1.023682181676049</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.14432645815099</v>
+        <v>4.162943324907437</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660852</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.431237575585207</v>
+        <v>-4.42315415042693</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.782905180350917</v>
+        <v>1.786138550414228</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.188754223845826</v>
+        <v>1.219782335106572</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.269009169206243</v>
+        <v>4.287626035962691</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395089</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.278212183471923</v>
+        <v>-4.270128758313645</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.943286336769135</v>
+        <v>1.946519706832446</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.34177961595911</v>
+        <v>1.372807727219856</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.459995404047119</v>
+        <v>4.478612270803566</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.306519497345193</v>
+        <v>-4.298436072186916</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.119429636128119</v>
+        <v>2.12266300619143</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.34177961595911</v>
+        <v>1.372807727219856</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.647461628955411</v>
+        <v>4.666078495711859</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620436</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.473112722458715</v>
+        <v>-4.465029297300438</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.022195297436793</v>
+        <v>2.025428667500104</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.175186390845588</v>
+        <v>1.206214502106334</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.51690864524138</v>
+        <v>4.535525511997828</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285649</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.45007692909715</v>
+        <v>-4.441993503938872</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.035086017443137</v>
+        <v>2.038319387506448</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.175186390845588</v>
+        <v>1.206214502106334</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.520585047903098</v>
+        <v>4.539201914659546</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399472</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.420830948641453</v>
+        <v>-4.412747523483175</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.044402464748911</v>
+        <v>2.047635834812222</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.175186390845588</v>
+        <v>1.206214502106334</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.518203103026593</v>
+        <v>4.536819969783041</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256375</v>
+        <v>3.699404642256373</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.527756496519304</v>
+        <v>-4.519673071361026</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.998925484755405</v>
+        <v>2.002158854818717</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.068260842967736</v>
+        <v>1.099288954228482</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.451341013457517</v>
+        <v>4.469957880213965</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701005</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.672775055026553</v>
+        <v>-4.664691629868275</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.94234686349574</v>
+        <v>1.945580233559051</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9232422844604879</v>
+        <v>0.954270395721234</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.365758680496403</v>
+        <v>4.38437554725285</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.79111682081127</v>
+        <v>-4.783033395652993</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.994941396439606</v>
+        <v>1.998174766502917</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.933928323023378</v>
+        <v>0.964956434284124</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.472101542891889</v>
+        <v>4.490718409648337</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790808</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.842527243131978</v>
+        <v>-4.834443817973701</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.972162924637262</v>
+        <v>1.975396294700573</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.933928323023378</v>
+        <v>0.964956434284124</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.469887240017829</v>
+        <v>4.488504106774276</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437336</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.92194669433973</v>
+        <v>-4.913863269181452</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.940298272228451</v>
+        <v>1.943531642291762</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.933928323023378</v>
+        <v>0.964956434284124</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.469790368092117</v>
+        <v>4.488407234848565</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298404</v>
+        <v>3.736804952298403</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.017409692256948</v>
+        <v>-5.00932626709867</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.902106966619607</v>
+        <v>1.905340336682918</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.933928323023378</v>
+        <v>0.964956434284124</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.469784261650161</v>
+        <v>4.488401128406609</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218006</v>
+        <v>3.715372960218005</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.953033781406233</v>
+        <v>-4.944950356247955</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.925953727522503</v>
+        <v>1.929187097585814</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9983042338740931</v>
+        <v>1.029332345134839</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.5065062047232</v>
+        <v>4.525123071479648</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.008402943538426</v>
+        <v>-5.000319518380149</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.909539880417352</v>
+        <v>1.912773250480663</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9983042338740931</v>
+        <v>1.029332345134839</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.512240022470927</v>
+        <v>4.530856889227374</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113285</v>
+        <v>3.736822870113284</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.026621410536035</v>
+        <v>-5.018537985377757</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.901790856961242</v>
+        <v>1.905024227024553</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9731977966182509</v>
+        <v>1.004225907878997</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.496714523460354</v>
+        <v>4.515331390216802</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.938414576388457</v>
+        <v>-4.930331151230179</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.956947983470592</v>
+        <v>1.960181353533902</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9731977966182509</v>
+        <v>1.004225907878997</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.516588916310673</v>
+        <v>4.53520578306712</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.832379581183147</v>
+        <v>-4.82429615602487</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.983062682077443</v>
+        <v>1.986296052140754</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9731977966182509</v>
+        <v>1.004225907878997</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.500289616835401</v>
+        <v>4.518906483591849</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.649167918050052</v>
+        <v>-4.641084492891775</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.058778296794727</v>
+        <v>2.062011666858037</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9731977966182509</v>
+        <v>1.004225907878997</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.502720566299447</v>
+        <v>4.521337433055894</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.577446471036201</v>
+        <v>-4.569363045877924</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.070411281679644</v>
+        <v>2.073644651742955</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.044919243632102</v>
+        <v>1.075947354892847</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.528697840587133</v>
+        <v>4.547314707343581</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394116</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.555073445428495</v>
+        <v>-4.546990020270218</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.026276237843898</v>
+        <v>2.029509607907209</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.056174994745003</v>
+        <v>1.087203106005749</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.482367037176046</v>
+        <v>4.500983903932494</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.58808974133924</v>
+        <v>-4.580006316180962</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.198267924364956</v>
+        <v>2.201501294428267</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9867376180782517</v>
+        <v>1.017765729338997</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.625902816061351</v>
+        <v>4.644519682817799</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.576562105689631</v>
+        <v>-4.568478680531354</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.194800204453048</v>
+        <v>2.19803357451636</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.045738276279614</v>
+        <v>1.07676638754036</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.653224436810417</v>
+        <v>4.671841303566865</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.673903607032</v>
+        <v>-4.665820181873722</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.159531716437889</v>
+        <v>2.1627650865012</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.001318094114126</v>
+        <v>1.032346205374871</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.630240440032913</v>
+        <v>4.648857306789361</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942769</v>
+        <v>3.705201079427689</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.759759636371967</v>
+        <v>-4.751676211213689</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.126440386894741</v>
+        <v>2.129673756958052</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9589420248879907</v>
+        <v>0.9899701361487363</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.60606588069007</v>
+        <v>4.624682747446517</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.768596433788086</v>
+        <v>-4.760513008629808</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.105324869748795</v>
+        <v>2.108558239812106</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.95149985224664</v>
+        <v>0.9825279635073856</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.584019778925762</v>
+        <v>4.602636645682209</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166746</v>
+        <v>3.715544411667459</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.859978996353544</v>
+        <v>-4.851895571195267</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.078936355767661</v>
+        <v>2.082169725830972</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9149349675272953</v>
+        <v>0.9459630787880409</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.572245359139204</v>
+        <v>4.590862225895652</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889197</v>
+        <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.848272278366538</v>
+        <v>-4.840188853208261</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.185747300786732</v>
+        <v>2.188980670850043</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9266416855143017</v>
+        <v>0.9576697967750473</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.681397647755676</v>
+        <v>4.700014514512123</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.919184352108816</v>
+        <v>-4.911100926950539</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.160414810021225</v>
+        <v>2.163648180084536</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9266416855143017</v>
+        <v>0.9576697967750473</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.684429986487081</v>
+        <v>4.703046853243528</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452574</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.929500450275168</v>
+        <v>-4.921417025116891</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.369193204032743</v>
+        <v>2.372426574096053</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9266416855143017</v>
+        <v>0.9576697967750473</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.897334819765139</v>
+        <v>4.915951686521586</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762294</v>
+        <v>3.623960959762292</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.929406482257796</v>
+        <v>-4.921323057099518</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.368409458151781</v>
+        <v>2.371642828215093</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.9580396581223652</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.89673540348562</v>
+        <v>4.915352270242067</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988025</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.07777270991394</v>
+        <v>-5.069689284755663</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.303294953033677</v>
+        <v>2.306528323096988</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.9580396581223652</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.890967389429973</v>
+        <v>4.90958425618642</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740924</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.076824286795902</v>
+        <v>-5.068740861637624</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.303674322280893</v>
+        <v>2.306907692344204</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.9580396581223652</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.890967389429973</v>
+        <v>4.90958425618642</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.177094104754923</v>
+        <v>-5.169010679596646</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.276294003078376</v>
+        <v>2.279527373141687</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.9580396581223652</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.903694997411066</v>
+        <v>4.922311864167513</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.171101857966112</v>
+        <v>-5.163018432807834</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.280636900218288</v>
+        <v>2.2838702702816</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.9580396581223652</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.905640995835453</v>
+        <v>4.924257862591901</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149219</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.082543896835344</v>
+        <v>-5.074460471677066</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.309714220688365</v>
+        <v>2.312947590751675</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.9580396581223652</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.899295131853222</v>
+        <v>4.91791199860967</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.06478481933227</v>
+        <v>-5.056701394173992</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.31612652912859</v>
+        <v>2.3193598991919</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.9580396581223652</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.898603809292218</v>
+        <v>4.917220676048665</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.965154668283202</v>
+        <v>-4.957071243124925</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.368760775456804</v>
+        <v>2.371994145520115</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.026641697910687</v>
+        <v>1.057669809171433</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.971164085830245</v>
+        <v>4.989780952586692</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455272</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.014554176972213</v>
+        <v>-5.006470751813936</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.538155237479926</v>
+        <v>2.541388607543237</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.036900531342432</v>
+        <v>1.067928642603178</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.166473651388018</v>
+        <v>5.185090518144466</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963136</v>
+        <v>3.749078058963133</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.807869703329837</v>
+        <v>-4.79978627817156</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.608017700039738</v>
+        <v>2.611251070103049</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.243585004984808</v>
+        <v>1.274613116245553</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.277673008676306</v>
+        <v>5.296289875432753</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.842026598327363</v>
+        <v>-4.833943173169086</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.596356455694832</v>
+        <v>2.599589825758144</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.160001235443995</v>
+        <v>1.191029346704741</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.229524260605923</v>
+        <v>5.248141127362371</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652386</v>
+        <v>3.782482115652385</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.749437119265907</v>
+        <v>-4.741353694107629</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.986889361309083</v>
+        <v>2.990122731372393</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.160001235443995</v>
+        <v>1.191029346704741</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.583021374595591</v>
+        <v>5.601638241352038</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108677</v>
+        <v>3.809055905108675</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.809325747089457</v>
+        <v>-4.80124232193118</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.967497021746766</v>
+        <v>2.970730391810076</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.145879320756531</v>
+        <v>1.176907432017276</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.579111337350215</v>
+        <v>5.597728204106662</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.757109437293115</v>
+        <v>-4.749026012134838</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.03821348698883</v>
+        <v>3.041446857052141</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.145879320756531</v>
+        <v>1.176907432017276</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.628941278673743</v>
+        <v>5.64755814543019</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047751</v>
+        <v>3.821827147047749</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.72521192020787</v>
+        <v>-4.717128495049592</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.059786464032939</v>
+        <v>3.06301983409625</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.177776837841776</v>
+        <v>1.208804949102522</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.656893759134901</v>
+        <v>5.675510625891349</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.82526841665076</v>
+        <v>3.825268416650758</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.73996724440801</v>
+        <v>-4.731883819249733</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.04952191839208</v>
+        <v>3.052755288455391</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.177776837841776</v>
+        <v>1.208804949102522</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.652531343174098</v>
+        <v>5.671148209930545</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135755</v>
+        <v>3.845044666135752</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.690502621038099</v>
+        <v>-4.682419195879821</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.060232271156324</v>
+        <v>3.063465641219635</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.227241461211688</v>
+        <v>1.258269572472434</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.673134620612324</v>
+        <v>5.691751487368772</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479229</v>
+        <v>3.825931790479226</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.527394628884483</v>
+        <v>-4.519311203726206</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.121883135732705</v>
+        <v>3.125116505796016</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.390349453365303</v>
+        <v>1.421377564626049</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.767407083619428</v>
+        <v>5.786023950375876</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844247</v>
+        <v>3.847096478844242</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.394587003387317</v>
+        <v>-4.386503578229039</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.184053222622699</v>
+        <v>3.187286592686011</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.390349453365303</v>
+        <v>1.421377564626049</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.776454120310556</v>
+        <v>5.795070987067004</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.83242598779095</v>
+        <v>3.832425987790946</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.457294919861875</v>
+        <v>-4.449211494703597</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.159827521018998</v>
+        <v>3.163060891082309</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.327641536890745</v>
+        <v>1.358669648151491</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.739686835411943</v>
+        <v>5.758303702168391</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578996</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.409286796018182</v>
+        <v>-4.401203370859904</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.141940187346827</v>
+        <v>3.145173557410138</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.327641536890745</v>
+        <v>1.358669648151491</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.702596252202295</v>
+        <v>5.721213118958743</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,45 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.900467959550761</v>
+        <v>3.872253907629887</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.330461138834591</v>
+        <v>-4.322377713676314</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.177402703778214</v>
+        <v>3.180636073841525</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.406467194074336</v>
+        <v>1.437495305335081</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.7538239000704</v>
+        <v>5.772440766826848</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="2" t="n">
+        <v>45563</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>3.899534371230506</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>4.978246581042763</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>-4.322377713676314</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>3.180636073841525</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>1.437495305335081</v>
+      </c>
+      <c r="G2101" t="n">
+        <v>4.971310378029131</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240928.xlsx
+++ b/tame_output/ON/bt/strategyON_20240928.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>104.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>179.0%</t>
+          <t>157.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-37.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.5%</t>
+          <t>417.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-597.3%</t>
+          <t>-636.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-60.1%</t>
+          <t>-75.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-295.9%</t>
+          <t>503.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-83.3%</t>
+          <t>-101.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,31 +1423,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-09-24</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629634802320069</v>
+        <v>-4.728709818338713</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.021253063644787</v>
+        <v>0.9816230572373299</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2032617758913947</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879965</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.611921115442204</v>
+        <v>-4.710996131460847</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.029017122313273</v>
+        <v>0.9893871159058161</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2064431047883115</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.488446844129186</v>
+        <v>-4.587521860147829</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075404902058474</v>
+        <v>1.035774895651017</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2064431047883115</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.268426046092175</v>
+        <v>-4.367501062110819</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.164992258283893</v>
+        <v>1.125362251876435</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3476629498562918</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.135558357028898</v>
+        <v>-4.234633373047541</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.234033516711027</v>
+        <v>1.19440351030357</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3476629498562918</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.015385273664399</v>
+        <v>-4.114460289683042</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.283248594497128</v>
+        <v>1.243618588089671</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4678360332207907</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.880131912334422</v>
+        <v>-3.979206928353065</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.347438041590559</v>
+        <v>1.307808035183102</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6030893945507678</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.940006739692114</v>
+        <v>-4.039081755710757</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.309525602048908</v>
+        <v>1.26989559564145</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5432145671930757</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.820186508781277</v>
+        <v>-3.91926152479992</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.372742863647451</v>
+        <v>1.333112857239994</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5432145671930757</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430695</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.822656215243083</v>
+        <v>-3.921731231261726</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.279399180385171</v>
+        <v>1.239769173977713</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5407448607312695</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.891026401567093</v>
+        <v>-3.990101417585736</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.171312967340868</v>
+        <v>1.131682960933411</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5500205597674844</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.002898681193243</v>
+        <v>-4.101973697211887</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.117000764122299</v>
+        <v>1.077370757714842</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5500205597674844</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.986924015706975</v>
+        <v>-4.085999031725619</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.089965155240833</v>
+        <v>1.050335148833376</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5500205597674844</v>
@@ -46148,10 +46148,10 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.811449755914506</v>
+        <v>-3.91052477193315</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.164722091149609</v>
+        <v>1.125092084742151</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5500205597674844</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.803525381329592</v>
+        <v>-3.902600397348235</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.143633869744782</v>
+        <v>1.104003863337324</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5500205597674844</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.797247178759743</v>
+        <v>-3.896322194778386</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.074683464174171</v>
+        <v>1.035053457766714</v>
       </c>
       <c r="F1941" t="n">
         <v>0.5562987623373334</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.73739455955602</v>
+        <v>-3.836469575574663</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.108796898287793</v>
+        <v>1.069166891880335</v>
       </c>
       <c r="F1942" t="n">
         <v>0.5562987623373334</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.651151096529643</v>
+        <v>-3.750226112548286</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.138240554072204</v>
+        <v>1.098610547664747</v>
       </c>
       <c r="F1943" t="n">
         <v>0.5562987623373334</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.696457915928622</v>
+        <v>-3.795532931947266</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.111893601757137</v>
+        <v>1.07226359534968</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5154885993281026</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.725491020630924</v>
+        <v>-3.824566036649567</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.100832232909319</v>
+        <v>1.061202226501861</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5154885993281026</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.632680539180065</v>
+        <v>-3.731755555198708</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.067229117381028</v>
+        <v>1.02759911097357</v>
       </c>
       <c r="F1946" t="n">
         <v>0.608299080778962</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.677070008509492</v>
+        <v>-3.776145024528136</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.051346805573858</v>
+        <v>1.0117167991664</v>
       </c>
       <c r="F1947" t="n">
         <v>0.5639096114495343</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.656566314623995</v>
+        <v>-3.755641330642638</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.054623991639779</v>
+        <v>1.014993985232322</v>
       </c>
       <c r="F1948" t="n">
         <v>0.5844133053350317</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.740238411336327</v>
+        <v>-3.83931342735497</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.026646448785514</v>
+        <v>0.9870164423780565</v>
       </c>
       <c r="F1949" t="n">
         <v>0.5844133053350317</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.76801880923768</v>
+        <v>-3.867093825256323</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.027031491393512</v>
+        <v>0.9874014849860544</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5566329074336787</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.886399481967818</v>
+        <v>-3.985474497986462</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8180349423021096</v>
+        <v>0.7784049358946523</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4894150552827025</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.99501356041115</v>
+        <v>-4.094088576429793</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8947389716439829</v>
+        <v>0.8551089652365256</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4894150552827025</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.959604522163007</v>
+        <v>-4.05867953818165</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9234156130455631</v>
+        <v>0.8837856066381056</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4894150552827025</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.968065690818468</v>
+        <v>-4.067140706837111</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9174505869257472</v>
+        <v>0.8778205805182901</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4809538866272414</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.790949360783302</v>
+        <v>-3.890024376801945</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9850261477851161</v>
+        <v>0.9453961413776588</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4809538866272414</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.836041605616847</v>
+        <v>-3.93511662163549</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.967672641613611</v>
+        <v>0.9280426352061537</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4190578434578516</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.656666184378079</v>
+        <v>-4.04720968428663</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.033209785415532</v>
+        <v>0.8769923854521124</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5758346016285703</v>
+        <v>0.3952669741528829</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.841733444457655</v>
+        <v>2.733392867972242</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.701680397898686</v>
+        <v>-4.092223897807235</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9960115553388798</v>
+        <v>0.8397941553754598</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5454857063139656</v>
+        <v>0.3649180788382783</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.804331562600482</v>
+        <v>2.695990986115069</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.968684908171121</v>
+        <v>-4.35922840807967</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8949013135688513</v>
+        <v>0.7386839136054315</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3511226682710171</v>
+        <v>0.1705550407953297</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.693405302113658</v>
+        <v>2.585064725628246</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.069882689608294</v>
+        <v>-4.460426189516843</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8536261228904836</v>
+        <v>0.6974087229270638</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2827138547256979</v>
+        <v>0.1021462272500105</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.651563935882968</v>
+        <v>2.543223359397556</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.063371722993981</v>
+        <v>-4.453915222902531</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8538304710905253</v>
+        <v>0.6976130711271056</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2827138547256979</v>
+        <v>0.1021462272500105</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.649163897437285</v>
+        <v>2.540823320951872</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.044333595286684</v>
+        <v>-4.434877095195233</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8579704413816893</v>
+        <v>0.7017530414182696</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2245302433945033</v>
+        <v>0.04396261591881601</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.610778449846813</v>
+        <v>2.502437873361401</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.096849397561504</v>
+        <v>-4.487392897470054</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9562585221059514</v>
+        <v>0.8000411221425316</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2245302433945033</v>
+        <v>0.04396261591881601</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.730072851481003</v>
+        <v>2.621732274995591</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.100257708996084</v>
+        <v>-4.490801208904633</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9557285265182531</v>
+        <v>0.7995111265548334</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2570468124038807</v>
+        <v>0.07647918492819339</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.750416121872763</v>
+        <v>2.642075545387351</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.080901573102237</v>
+        <v>-4.471445073010786</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9694795112727179</v>
+        <v>0.8132621113092982</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2570468124038807</v>
+        <v>0.07647918492819339</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.756424652269689</v>
+        <v>2.648084075784277</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.154231101840329</v>
+        <v>-4.544774601748879</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8380979210546804</v>
+        <v>0.6818805210912606</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2574414748235027</v>
+        <v>0.07687384734781533</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.654611670998662</v>
+        <v>2.54627109451325</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.497386102192977</v>
+        <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.238052323115028</v>
+        <v>-4.628595823023577</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8018087486332182</v>
+        <v>0.6511456541128622</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2574414748235027</v>
+        <v>0.07687384734781533</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.651850987087079</v>
+        <v>2.549064716044731</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.498048450584636</v>
+        <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.231899617062243</v>
+        <v>-4.622443116970793</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8049321794459903</v>
+        <v>0.6542690849256343</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2635941808762869</v>
+        <v>0.08302655340059961</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.656204959110408</v>
+        <v>2.55341868806806</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.497128927324746</v>
+        <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.248708915212745</v>
+        <v>-4.639252415121295</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7972889369258997</v>
+        <v>0.6466258424055438</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2467848827257853</v>
+        <v>0.06621725525009797</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.645199856960217</v>
+        <v>2.542413585917869</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.563464481121567</v>
+        <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.186410916436623</v>
+        <v>-4.576954416345172</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8885436902331696</v>
+        <v>0.7378805957128136</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2920791470002274</v>
+        <v>0.11151151952454</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.738711969321703</v>
+        <v>2.635925698279355</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.365756482835694</v>
+        <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.984620718771465</v>
+        <v>-4.375164218680014</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7715517710133599</v>
+        <v>0.6208886764930039</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4900973391693817</v>
+        <v>0.3095297116936944</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.659814886337323</v>
+        <v>2.557028615294974</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.436046715157869</v>
+        <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.03550743145766</v>
+        <v>-4.426050931366209</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8214873182610571</v>
+        <v>0.6708242237407012</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4392106264831871</v>
+        <v>0.2586429990074999</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.699573091047782</v>
+        <v>2.596786820005433</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.450674451273913</v>
+        <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.948896688807852</v>
+        <v>-4.339440188716402</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8707593514370238</v>
+        <v>0.7200962569166676</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5178363576883454</v>
+        <v>0.3372687302126581</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.76137626588692</v>
+        <v>2.658589994844572</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.449210432098584</v>
+        <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.009105986813137</v>
+        <v>-4.399649486721687</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8452116130595817</v>
+        <v>0.6945485185392253</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4576270596830608</v>
+        <v>0.2770594322073736</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.723786667908421</v>
+        <v>2.621000396866072</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.447702050138513</v>
+        <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.959919338128786</v>
+        <v>-4.350462838037336</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8633778905732508</v>
+        <v>0.7127147960528943</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4576270596830608</v>
+        <v>0.2770594322073736</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.72227828594835</v>
+        <v>2.619492014906001</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.447564917573949</v>
+        <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.915546206490217</v>
+        <v>-4.306089706398767</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8809900106641144</v>
+        <v>0.730326916143758</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5020001913216294</v>
+        <v>0.3214325638459422</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.748765032366927</v>
+        <v>2.645978761324578</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.44195871171254</v>
+        <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.880814885171716</v>
+        <v>-4.271358385080267</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8892763333301053</v>
+        <v>0.7386132388097488</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5020001913216294</v>
+        <v>0.3214325638459422</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.743158826505518</v>
+        <v>2.640372555463169</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.448340468740344</v>
+        <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.83315915461066</v>
+        <v>-4.223702654519211</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.914720382582332</v>
+        <v>0.7640572880619758</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5496559218826851</v>
+        <v>0.3690882944069979</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.778134021869956</v>
+        <v>2.675347750827607</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.453232842115069</v>
+        <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.732640996111906</v>
+        <v>-4.123184496020456</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9598200193565587</v>
+        <v>0.8091569248362025</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6501740803814396</v>
+        <v>0.4696064529057524</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.843337290343933</v>
+        <v>2.740551019301585</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.439987514590941</v>
+        <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.716735666679553</v>
+        <v>-4.107279166588103</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9529368236053721</v>
+        <v>0.8022737290850157</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5710614196722008</v>
+        <v>0.3904937921965135</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.782624366394262</v>
+        <v>2.679838095351914</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.44408521720157</v>
+        <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.671897265071155</v>
+        <v>-4.062440764979705</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9749698868593599</v>
+        <v>0.8243067923390037</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5756048526170703</v>
+        <v>0.395037225141383</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.789448128771812</v>
+        <v>2.686661857729464</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.448246156832648</v>
+        <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.691395721313163</v>
+        <v>-4.081939221221713</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9713314439936345</v>
+        <v>0.8206683494732785</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.527520211337166</v>
+        <v>0.3469525838614787</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.764758283634948</v>
+        <v>2.661972012592599</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.454125759360485</v>
+        <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.647192884227263</v>
+        <v>-4.037736384135813</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9948921813558318</v>
+        <v>0.8442290868354758</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5717230484230664</v>
+        <v>0.3911554209473792</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.797159588414325</v>
+        <v>2.694373317371976</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.452535759829733</v>
+        <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.65475255006431</v>
+        <v>-4.04529604997286</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9902783154902606</v>
+        <v>0.8396152209699044</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6265264524328857</v>
+        <v>0.4459588249571985</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.828451631289465</v>
+        <v>2.725665360247116</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.503783525012772</v>
+        <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.496461132525038</v>
+        <v>-3.887004632433588</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.104842647689009</v>
+        <v>0.954179553168653</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6265264524328857</v>
+        <v>0.4459588249571985</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.879699396472504</v>
+        <v>2.776913125430156</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.502224229607025</v>
+        <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.288819128890561</v>
+        <v>-3.679362628799112</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.186340153737053</v>
+        <v>1.035677059216697</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8341684560673619</v>
+        <v>0.6536008285916746</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.002725303247443</v>
+        <v>2.899939032205094</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.497172457845295</v>
+        <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.237787036168033</v>
+        <v>-3.628330536076584</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.201701219064334</v>
+        <v>1.051038124543978</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8852005487898899</v>
+        <v>0.7046329213142025</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.02829278711923</v>
+        <v>2.925506516076881</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.514359861938</v>
+        <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.172562855040828</v>
+        <v>-3.563106354949378</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.244978295607921</v>
+        <v>1.094315201087565</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9504247299170955</v>
+        <v>0.7698571024414081</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.084614699888258</v>
+        <v>2.981828428845909</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.510320834237281</v>
+        <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.135135834969694</v>
+        <v>-3.525679334878244</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.255910075935655</v>
+        <v>1.105246981415299</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9556762679462771</v>
+        <v>0.7751086404705898</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.083726595005047</v>
+        <v>2.980940323962699</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.511577626568521</v>
+        <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.133777849996148</v>
+        <v>-3.524321349904699</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.257710062256314</v>
+        <v>1.107046967735957</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.030014393484096</v>
+        <v>0.8494467660084084</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.129586262658979</v>
+        <v>3.02679999161663</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.672135397589732</v>
+        <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.105364586896265</v>
+        <v>-3.495908086804815</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.429633138517478</v>
+        <v>1.278970043997122</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9710388307376669</v>
+        <v>0.7904712032619796</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.254758696032332</v>
+        <v>3.151972424989983</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.792248306807549</v>
+        <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.030582325871252</v>
+        <v>-3.421125825779802</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.5796589521453</v>
+        <v>1.428995857624944</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.04582109176268</v>
+        <v>0.8652534642869922</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.419740961865157</v>
+        <v>3.316954690822808</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.783956282821408</v>
+        <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.004498241607444</v>
+        <v>-3.395041741515994</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.581800561864682</v>
+        <v>1.431137467344326</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.04582109176268</v>
+        <v>0.8652534642869922</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.411448937879016</v>
+        <v>3.308662666836667</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.782149478405187</v>
+        <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.916620328498324</v>
+        <v>-3.307163828406874</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.61514492269211</v>
+        <v>1.464481828171754</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.161746734186031</v>
+        <v>0.9811791067103434</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.479197518916806</v>
+        <v>3.376411247874457</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.799703884131979</v>
+        <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.907727867105041</v>
+        <v>-3.298271367013591</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.636256312976215</v>
+        <v>1.485593218455858</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.161746734186031</v>
+        <v>0.9811791067103434</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.496751924643597</v>
+        <v>3.393965653601249</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.791558931536563</v>
+        <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.076203984074918</v>
+        <v>-3.466747483983469</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.560720913592847</v>
+        <v>1.410057819072491</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.13379889846945</v>
+        <v>0.9532312709937626</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.471838270618233</v>
+        <v>3.369051999575884</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.772828628724425</v>
+        <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.629947791445479</v>
+        <v>-3.020491291354029</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.720493087832485</v>
+        <v>1.569829993312129</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.039080228799817</v>
+        <v>0.8585126013241299</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.396276766004315</v>
+        <v>3.293490494961967</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.763492651221329</v>
+        <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.607226687762326</v>
+        <v>-2.997770187670876</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.720245551802651</v>
+        <v>1.569582457282295</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.039080228799817</v>
+        <v>0.8585126013241299</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.386940788501219</v>
+        <v>3.284154517458871</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.922398777072498</v>
+        <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.736428501056368</v>
+        <v>-3.126972000964919</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.827470952336203</v>
+        <v>1.676807857815847</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9098784155057749</v>
+        <v>0.7293107880300875</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.468325826375963</v>
+        <v>3.365539555333615</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.959476599566145</v>
+        <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.762302899530394</v>
+        <v>-3.152846399438944</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.854199015440239</v>
+        <v>1.703535920919883</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.954790024217516</v>
+        <v>0.7742223967418287</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.532350614096655</v>
+        <v>3.429564343054306</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.95615195555569</v>
+        <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.755248209315221</v>
+        <v>-3.145791709223771</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.853696247515854</v>
+        <v>1.703033152995497</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9618447144326898</v>
+        <v>0.7812770869570025</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.533258784215304</v>
+        <v>3.430472513172956</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.966158109200431</v>
+        <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.728296984988733</v>
+        <v>-3.118840484897283</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.87448289089119</v>
+        <v>1.723819796370834</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.976725060460409</v>
+        <v>0.7961574329847216</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.552193145476677</v>
+        <v>3.449406874434328</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.150261241345391</v>
+        <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.74984121281952</v>
+        <v>-3.14038471272807</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.049968331903835</v>
+        <v>1.899305237383479</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.976725060460409</v>
+        <v>0.7961574329847216</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.736296277621637</v>
+        <v>3.633510006579288</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.142377936248384</v>
+        <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.772249330624392</v>
+        <v>-3.162792830532942</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.03312177968488</v>
+        <v>1.882458685164523</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.976725060460409</v>
+        <v>0.7961574329847216</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.72841297252463</v>
+        <v>3.625626701482282</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.144431935798022</v>
+        <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.800473566201992</v>
+        <v>-3.191017066110542</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.023886085003477</v>
+        <v>1.873222990483121</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9947018129117176</v>
+        <v>0.8141341854360302</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.741253023545053</v>
+        <v>3.638466752502704</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.200685653519869</v>
+        <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.809914492090522</v>
+        <v>-3.200457991999072</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.076363432369912</v>
+        <v>1.925700337849556</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.117128930455109</v>
+        <v>0.9365613029794216</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.870963011792934</v>
+        <v>3.768176740750586</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.20357674806517</v>
+        <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.898791123258996</v>
+        <v>-3.289334623167546</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.043703874447823</v>
+        <v>1.893040779927467</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.028252299286635</v>
+        <v>0.8476846718109478</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.820528127637151</v>
+        <v>3.717741856594802</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.201688560958945</v>
+        <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.975121100859902</v>
+        <v>-3.365664600768452</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.011283696301236</v>
+        <v>1.86062060178088</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.028252299286635</v>
+        <v>0.8476846718109478</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.818639940530926</v>
+        <v>3.715853669488578</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887751</v>
+        <v>3.710654104887749</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.196508790561807</v>
+        <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.130077886260031</v>
+        <v>-3.520621386168581</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.944121211744047</v>
+        <v>1.793458117223691</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8732955138865059</v>
+        <v>0.6927278864108185</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.720486098893711</v>
+        <v>3.617699827851363</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.19494280077196</v>
+        <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.291646311787286</v>
+        <v>-3.682189811695836</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.877927851743297</v>
+        <v>1.727264757222941</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7465125900886266</v>
+        <v>0.5659449626129391</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.642850354825136</v>
+        <v>3.540064083782787</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.208016207637878</v>
+        <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.399946973657406</v>
+        <v>-3.790490473565956</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.847680993861168</v>
+        <v>1.697017899340812</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7465125900886266</v>
+        <v>0.5659449626129391</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.655923761691054</v>
+        <v>3.553137490648706</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378387</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.200021404420818</v>
+        <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.41775094537815</v>
+        <v>-3.8082944452867</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.83256460195581</v>
+        <v>1.681901507435454</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6759779671834254</v>
+        <v>0.4954103397077381</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.605608184730874</v>
+        <v>3.502821913688525</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.19854544554782</v>
+        <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.445651732487623</v>
+        <v>-3.836195232396173</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.819928328239023</v>
+        <v>1.669265233718667</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6413810430404906</v>
+        <v>0.4608134155648033</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.583374071372115</v>
+        <v>3.480587800329766</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.195309889525019</v>
+        <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.568177835190517</v>
+        <v>-3.958721335099067</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.767682331135064</v>
+        <v>1.617019236614708</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5188549403375967</v>
+        <v>0.3382873128619094</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.506622853727577</v>
+        <v>3.403836582685229</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585933</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.262015849115523</v>
+        <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.798692331376105</v>
+        <v>-4.189235831284655</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.742182492251333</v>
+        <v>1.591519397730976</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.288340444152008</v>
+        <v>0.1077728166763207</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.435020115606728</v>
+        <v>3.332233844564379</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.40232756811737</v>
+        <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.147437416600549</v>
+        <v>-4.537980916509099</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.742996177163402</v>
+        <v>1.592333082643046</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1795924902331102</v>
+        <v>-0.0009751372425771399</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.510083062257236</v>
+        <v>3.407296791214887</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.47130783726301</v>
+        <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.301423834376689</v>
+        <v>-4.691967334285239</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.750381879198586</v>
+        <v>1.599718784678229</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1795924902331102</v>
+        <v>-0.0009751372425771399</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.579063331402876</v>
+        <v>3.476277060360527</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.45735903938313</v>
+        <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.506023269239698</v>
+        <v>-4.896566769148248</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.654593307373503</v>
+        <v>1.503930212853147</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1795924902331102</v>
+        <v>-0.0009751372425771399</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.565114533522997</v>
+        <v>3.462328262480648</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.469229528438544</v>
+        <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.758498423247422</v>
+        <v>-5.149041923155973</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.565473734825827</v>
+        <v>1.414810640305471</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1795924902331102</v>
+        <v>-0.0009751372425771399</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.576985022578411</v>
+        <v>3.474198751536062</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.470440062957488</v>
+        <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.051394179726834</v>
+        <v>-5.441937679635385</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.449525966753006</v>
+        <v>1.29886287223265</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1795924902331102</v>
+        <v>-0.0009751372425771399</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.578195557097354</v>
+        <v>3.475409286055006</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.47456180518481</v>
+        <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.238058307861643</v>
+        <v>-5.628601807770193</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.378982057726405</v>
+        <v>1.228318963206048</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1528535194085503</v>
+        <v>-0.02771410806713703</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.56627391682994</v>
+        <v>3.463487645787591</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.469639657920999</v>
+        <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.384078994775605</v>
+        <v>-5.774622494684155</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.315651635697009</v>
+        <v>1.164988541176653</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1437704276146933</v>
+        <v>-0.036797199860994</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.555901914489815</v>
+        <v>3.453115643447467</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.631843714620043</v>
+        <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.47579300388519</v>
+        <v>-5.86633650379374</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.441170088752219</v>
+        <v>1.290506994231863</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1437704276146933</v>
+        <v>-0.036797199860994</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.71810597118886</v>
+        <v>3.615319700146511</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.626690352583857</v>
+        <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.50744466294516</v>
+        <v>-5.897988162853709</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.423356063092045</v>
+        <v>1.272692968571689</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1386019703702531</v>
+        <v>-0.04196565710543421</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.709851534806009</v>
+        <v>3.607065263763661</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868145</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.636919770152348</v>
+        <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.576510717518096</v>
+        <v>-5.967054217426646</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.405959058831362</v>
+        <v>1.255295964311006</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07623109287664309</v>
+        <v>-0.1043365345990442</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.682658425878334</v>
+        <v>3.579872154835986</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332693</v>
+        <v>3.783632867332691</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.645845408608251</v>
+        <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.678486839766504</v>
+        <v>-6.069030339675053</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.374094248387901</v>
+        <v>1.223431153867545</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.02574502937176448</v>
+        <v>-0.2063126568474518</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.630398390985192</v>
+        <v>3.527612119942844</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79829678423181</v>
+        <v>3.798296784231808</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.637998295852426</v>
+        <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.568480556289282</v>
+        <v>-5.959024056197832</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.410249649022965</v>
+        <v>1.259586554502609</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.002540457454489276</v>
+        <v>-0.1831080849301766</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.636474021379733</v>
+        <v>3.533687750337384</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818517</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.6422483065744</v>
+        <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.425420980548356</v>
+        <v>-5.815964480456906</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.47172349004131</v>
+        <v>1.321060395520954</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.005472969135490002</v>
+        <v>-0.1750946583401973</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.645532088055695</v>
+        <v>3.542745817013346</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051783</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.649509189456936</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.123974255076519</v>
+        <v>-5.514517754985068</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.599563063112581</v>
+        <v>1.448899968592225</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3069196946073273</v>
+        <v>0.1263520671316399</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.833661006221333</v>
+        <v>3.730874735178984</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.650480367209647</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.148564499311703</v>
+        <v>-5.539107999220252</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.590698143171218</v>
+        <v>1.440035048650862</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3069196946073273</v>
+        <v>0.1263520671316399</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.834632183974044</v>
+        <v>3.731845912931695</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.651323271589403</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.097526123305182</v>
+        <v>-5.488069623213732</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.611956397953582</v>
+        <v>1.461293303433226</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3069196946073273</v>
+        <v>0.1263520671316399</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.835475088353799</v>
+        <v>3.732688817311451</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.670361370463548</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.068677446481722</v>
+        <v>-5.459220946390271</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.642533967557111</v>
+        <v>1.491870873036755</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3357683714307875</v>
+        <v>0.1552007439551002</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.871822393322021</v>
+        <v>3.769036122279672</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.486545366587483</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.972042534463082</v>
+        <v>-5.362586034371631</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.497371928488502</v>
+        <v>1.346708833968146</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4324032834494275</v>
+        <v>0.2518356559737401</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.745987336657139</v>
+        <v>3.643201065614791</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.490047410661447</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.903004523514614</v>
+        <v>-5.293548023423163</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.528489176941853</v>
+        <v>1.377826082421497</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5014412943978955</v>
+        <v>0.3208736669222082</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.790912187300184</v>
+        <v>3.688125916257836</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.474474229737529</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.738508189323652</v>
+        <v>-5.129051689232202</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.57871452969432</v>
+        <v>1.428051435173964</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6659376285888574</v>
+        <v>0.4853700011131701</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.874036806890844</v>
+        <v>3.771250535848496</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077625</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.473661940173959</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.66140958778178</v>
+        <v>-5.051953087690329</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.608741680747499</v>
+        <v>1.458078586227143</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6659376285888574</v>
+        <v>0.4853700011131701</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.873224517327274</v>
+        <v>3.770438246284925</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.483530719299031</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.671794782671669</v>
+        <v>-5.062338282580218</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.614456381916616</v>
+        <v>1.46379328739626</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6555524336989681</v>
+        <v>0.4749848062232808</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.876862179518413</v>
+        <v>3.774075908476064</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.554367725075457</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.690382941393894</v>
+        <v>-5.080926441302443</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.677858124204151</v>
+        <v>1.527195029683795</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6369642749767428</v>
+        <v>0.4563966475010554</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.936546290061503</v>
+        <v>3.833760019019154</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.551236735893755</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.69068148808993</v>
+        <v>-5.081224987998479</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.674607716344035</v>
+        <v>1.523944621823679</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6366657282807069</v>
+        <v>0.4560981008050195</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.93323617286218</v>
+        <v>3.830449901819831</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.555767630833147</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.589858354399502</v>
+        <v>-4.980401854308051</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.719467864759598</v>
+        <v>1.568804770239242</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6491299437650607</v>
+        <v>0.4685623162893733</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.945245597092184</v>
+        <v>3.842459326049835</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.55589688431169</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.399076993647094</v>
+        <v>-4.789620493555644</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.795909662539104</v>
+        <v>1.645246568018748</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8399113045174681</v>
+        <v>0.6593436770417807</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.059843667022171</v>
+        <v>3.957057395979822</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.535733730049286</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.292113635797673</v>
+        <v>-4.682657135706222</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.818531851416469</v>
+        <v>1.667868756896113</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8983759124772696</v>
+        <v>0.7178082850015821</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.074759277535648</v>
+        <v>3.971973006493299</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.570700666661345</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.23678304789591</v>
+        <v>-4.62732654780446</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.875631023189233</v>
+        <v>1.724967928668877</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9537065003790317</v>
+        <v>0.7731388729033443</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.142924566888764</v>
+        <v>4.040138295846416</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.564387234562783</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.224728920982947</v>
+        <v>-4.615272420891497</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.874139241855856</v>
+        <v>1.7234761473355</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9657606272919945</v>
+        <v>0.7851929998163071</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.14384361093798</v>
+        <v>4.041057339895631</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.566267864746918</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.265884040551168</v>
+        <v>-4.656427540459718</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.859557824212703</v>
+        <v>1.708894729692347</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9246055077237736</v>
+        <v>0.7440378802480861</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.121031169381183</v>
+        <v>4.018244898338834</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.579118890624801</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.197835477859639</v>
+        <v>-4.588378977768188</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.899628275167197</v>
+        <v>1.748965180646842</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9926540704153033</v>
+        <v>0.812086442939616</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.174711332873983</v>
+        <v>4.071925061831634</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001343</v>
+        <v>3.645256780013428</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.599321560798395</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.429435871029139</v>
+        <v>-4.819979370937689</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.827190788072991</v>
+        <v>1.676527693552635</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9926540704153033</v>
+        <v>0.812086442939616</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.194914003047577</v>
+        <v>4.092127732005229</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.582927796865277</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.479487416558358</v>
+        <v>-4.870030916466908</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.790776405928186</v>
+        <v>1.64011331140783</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9926540704153033</v>
+        <v>0.812086442939616</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.17852023911446</v>
+        <v>4.075733968072111</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.543179710458744</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.654594249134803</v>
+        <v>-5.045137749043352</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.680985586491075</v>
+        <v>1.530322491970719</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9926540704153033</v>
+        <v>0.812086442939616</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.138772152707926</v>
+        <v>4.035985881665577</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.550202329455684</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.45849409570428</v>
+        <v>-4.849037595612829</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.766448266860224</v>
+        <v>1.615785172339868</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.188754223845826</v>
+        <v>1.008186596370139</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.26345486376318</v>
+        <v>4.160668592720831</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.649373329028588</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.305468703590996</v>
+        <v>-4.696012203499545</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.926829423278442</v>
+        <v>1.776166328758086</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.34177961595911</v>
+        <v>1.161211988483423</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.454441098604055</v>
+        <v>4.351654827561706</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.836839553936881</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.333776017464266</v>
+        <v>-4.724319517372815</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.102972722637427</v>
+        <v>1.95230962811707</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.34177961595911</v>
+        <v>1.161211988483423</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.641907323512347</v>
+        <v>4.539121052469999</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.806242505290963</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.500369242577788</v>
+        <v>-4.890912742486337</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.0057383839461</v>
+        <v>1.855075289425744</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.175186390845588</v>
+        <v>0.9946187633699004</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.511354339798316</v>
+        <v>4.408568068755968</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.809918907952681</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.477333449216222</v>
+        <v>-4.867876949124772</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.018629103952444</v>
+        <v>1.867966009432088</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.175186390845588</v>
+        <v>0.9946187633699004</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.515030742460034</v>
+        <v>4.412244471417686</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.807536963076176</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.448087468760526</v>
+        <v>-4.838630968669075</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.027945551258218</v>
+        <v>1.877282456737862</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.175186390845588</v>
+        <v>0.9946187633699004</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.512648797583529</v>
+        <v>4.409862526541181</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.804830202233811</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.555013016638377</v>
+        <v>-4.945556516546926</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.982468571264713</v>
+        <v>1.831805476744357</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.068260842967736</v>
+        <v>0.887693215492049</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.445786708014453</v>
+        <v>4.343000436972105</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.806259004377046</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.700031575145625</v>
+        <v>-5.090575075054175</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.925889950005048</v>
+        <v>1.775226855484692</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9232422844604879</v>
+        <v>0.7426746569848005</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.360204375053339</v>
+        <v>4.25741810401099</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687014</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.906190243634799</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.818373340930343</v>
+        <v>-5.208916840838892</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.978484482948914</v>
+        <v>1.827821388428557</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.933928323023378</v>
+        <v>0.7533606955476906</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.466547237448825</v>
+        <v>4.363760966406477</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790806</v>
+        <v>3.714879051790804</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.903975940760738</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.869783763251051</v>
+        <v>-5.2603272631596</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.955706011146569</v>
+        <v>1.805042916626213</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.933928323023378</v>
+        <v>0.7533606955476906</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.464332934574765</v>
+        <v>4.361546663532416</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437334</v>
+        <v>3.704757949437332</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.903879068835027</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.949203214458803</v>
+        <v>-5.339746714367352</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.923841358737758</v>
+        <v>1.773178264217402</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.933928323023378</v>
+        <v>0.7533606955476906</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.464236062649054</v>
+        <v>4.361449791606705</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298402</v>
+        <v>3.7368049522984</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.90387296239307</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.04466621237602</v>
+        <v>-5.43520971228457</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.885650053128914</v>
+        <v>1.734986958608558</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.933928323023378</v>
+        <v>0.7533606955476906</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.464229956207097</v>
+        <v>4.361443685164748</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218004</v>
+        <v>3.715372960218002</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.901969358955681</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.980290301525305</v>
+        <v>-5.370833801433855</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.90949681403181</v>
+        <v>1.758833719511455</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9983042338740931</v>
+        <v>0.8177366063984057</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.500951899280136</v>
+        <v>4.398165628237788</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73608941335354</v>
+        <v>3.736089413353538</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.907703176703407</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.035659463657499</v>
+        <v>-5.426202963566048</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.89308296692666</v>
+        <v>1.742419872406304</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9983042338740931</v>
+        <v>0.8177366063984057</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.506685717027863</v>
+        <v>4.403899445985514</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113283</v>
+        <v>3.736822870113281</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.90724154004634</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.053877930655108</v>
+        <v>-5.444421430563657</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.885333943470549</v>
+        <v>1.734670848950193</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9731977966182509</v>
+        <v>0.7926301691425636</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.49116021801729</v>
+        <v>4.388373946974942</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113692</v>
+        <v>3.79027250011369</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.927115932896658</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.965671096507529</v>
+        <v>-5.356214596416079</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.940491069979899</v>
+        <v>1.789827975459543</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9731977966182509</v>
+        <v>0.7926301691425636</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.511034610867609</v>
+        <v>4.408248339825261</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.910816633421386</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.85963610130222</v>
+        <v>-5.250179601210769</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.96660576858675</v>
+        <v>1.815942674066394</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9731977966182509</v>
+        <v>0.7926301691425636</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.494735311392337</v>
+        <v>4.391949040349989</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.913247582885432</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.676424438169125</v>
+        <v>-5.066967938077674</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.042321383304034</v>
+        <v>1.891658288783678</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9731977966182509</v>
+        <v>0.7926301691425636</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.497166260856383</v>
+        <v>4.394379989814034</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.896191988964809</v>
+        <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.604702991155274</v>
+        <v>-4.995246491063823</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.053954368188951</v>
+        <v>1.903291273668595</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.044919243632102</v>
+        <v>0.8643516161564142</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.523143535144071</v>
+        <v>4.420357264101721</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.843107734885981</v>
+        <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.582329965547568</v>
+        <v>-4.972873465456117</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.009819324353206</v>
+        <v>1.859156229832849</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.056174994745003</v>
+        <v>0.8756073672693158</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.476812731732983</v>
+        <v>4.374026460690634</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.028305939771336</v>
+        <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.615346261458313</v>
+        <v>-5.005889761366862</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.181811010874263</v>
+        <v>2.031147916353907</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9867376180782517</v>
+        <v>0.8061699906025641</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.620348510618287</v>
+        <v>4.517562239575938</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.020227165599585</v>
+        <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.603818625808704</v>
+        <v>-4.994362125717253</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.178343290962355</v>
+        <v>2.027680196442</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.045738276279614</v>
+        <v>0.8651706488039266</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.647670131367354</v>
+        <v>4.544883860325005</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236299</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.023895278121373</v>
+        <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.701160127151073</v>
+        <v>-5.091703627059622</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.143074802947196</v>
+        <v>1.99241170842684</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.001318094114126</v>
+        <v>0.8207504666384382</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.624686134589849</v>
+        <v>4.521899863547501</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427688</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.025146360314212</v>
+        <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.787016156491039</v>
+        <v>-5.177559656399588</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.109983473404048</v>
+        <v>1.959320378883692</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9589420248879907</v>
+        <v>0.7783743974123032</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.600511575247006</v>
+        <v>4.497725304204658</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.007565562134713</v>
+        <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.795852953907159</v>
+        <v>-5.186396453815708</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.088867956258102</v>
+        <v>1.938204861737746</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.95149985224664</v>
+        <v>0.7709322247709525</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.578465473482698</v>
+        <v>4.475679202440349</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.017730073179763</v>
+        <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.887235516472617</v>
+        <v>-5.277779016381166</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.062479442276968</v>
+        <v>1.911816347756612</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9149349675272953</v>
+        <v>0.7343673400516078</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.56669105369614</v>
+        <v>4.463904782653792</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889195</v>
+        <v>3.673978374889193</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.11985833100403</v>
+        <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.875528798485611</v>
+        <v>-5.26607229839416</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.169290387296038</v>
+        <v>2.018627292775683</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9266416855143017</v>
+        <v>0.7460740580386142</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.675843342312612</v>
+        <v>4.573057071270264</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409571</v>
+        <v>3.682476099409569</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.122890669735435</v>
+        <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.946440872227889</v>
+        <v>-5.336984372136438</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.143957896530531</v>
+        <v>1.993294802010177</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9266416855143017</v>
+        <v>0.7460740580386142</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.678875681044016</v>
+        <v>4.576089410001669</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452572</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.335795503013493</v>
+        <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.956756970394241</v>
+        <v>-5.34730047030279</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.352736290542049</v>
+        <v>2.202073196021694</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9266416855143017</v>
+        <v>0.7460740580386142</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.891780514322075</v>
+        <v>4.788994243279727</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762292</v>
+        <v>3.62396095976229</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.334974169925583</v>
+        <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.956663002376868</v>
+        <v>-5.347206502285418</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.351952544661088</v>
+        <v>2.201289450140732</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.7464439193859321</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.891181098042555</v>
+        <v>4.788394827000207</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988023</v>
+        <v>3.633213467988021</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.329206155869937</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.105029230033013</v>
+        <v>-5.495572729941562</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.286838039542983</v>
+        <v>2.136174945022628</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.7464439193859321</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.885413083986909</v>
+        <v>4.782626812944561</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.329206155869937</v>
+        <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.104080806914975</v>
+        <v>-5.494624306823524</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.287217408790199</v>
+        <v>2.136554314269844</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.7464439193859321</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.885413083986909</v>
+        <v>4.782626812944561</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.341933763851029</v>
+        <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.204350624873996</v>
+        <v>-5.594894124782545</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.259837089587682</v>
+        <v>2.109173995067327</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.7464439193859321</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.898140691968001</v>
+        <v>4.795354420925653</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.343879762275416</v>
+        <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.198358378085184</v>
+        <v>-5.588901877993734</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.264179986727595</v>
+        <v>2.11351689220724</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.7464439193859321</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.900086690392389</v>
+        <v>4.797300419350041</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.337533898293185</v>
+        <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.109800416954417</v>
+        <v>-5.500343916862966</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.293257307197671</v>
+        <v>2.142594212677316</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.7464439193859321</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.893740826410157</v>
+        <v>4.79095455536781</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.73530072138309</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.336842575732181</v>
+        <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.092041339451343</v>
+        <v>-5.482584839359892</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.299669615637896</v>
+        <v>2.149006521117541</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9270115468616197</v>
+        <v>0.7464439193859321</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.893049503849153</v>
+        <v>4.790263232806805</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.349624761640768</v>
+        <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.992411188402275</v>
+        <v>-5.382954688310824</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.35230386196611</v>
+        <v>2.201640767445755</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.026641697910687</v>
+        <v>0.8460740704349996</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.96560978038718</v>
+        <v>4.862823509344833</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.538779027139494</v>
+        <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.041810697091286</v>
+        <v>-5.432354196999835</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.521698323989232</v>
+        <v>2.371035229468877</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.036900531342432</v>
+        <v>0.8563329038667443</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.160919345944953</v>
+        <v>5.058133074902606</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963134</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.525967700242356</v>
+        <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.83512622344891</v>
+        <v>-5.225669723357459</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.591560786549044</v>
+        <v>2.440897692028689</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.243585004984808</v>
+        <v>1.06301737750912</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.272118703233241</v>
+        <v>5.169332432190893</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162544</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.527969213896461</v>
+        <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.869283118446436</v>
+        <v>-5.259826618354985</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.579899542204139</v>
+        <v>2.429236447683784</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.160001235443995</v>
+        <v>0.9794336079683074</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.223969955162858</v>
+        <v>5.121183684120511</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652384</v>
+        <v>3.782482115652383</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.881466327886129</v>
+        <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.776693639384979</v>
+        <v>-5.167237139293529</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.970432447818389</v>
+        <v>2.819769353298034</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.160001235443995</v>
+        <v>0.9794336079683074</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.577467069152526</v>
+        <v>5.474680798110178</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108675</v>
+        <v>3.809055905108673</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.886029439453232</v>
+        <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.83658226720853</v>
+        <v>-5.227125767117079</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.951040108256072</v>
+        <v>2.800377013735717</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.145879320756531</v>
+        <v>0.9653116932808428</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.57355703190715</v>
+        <v>5.470770760864802</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103568</v>
+        <v>3.835202441103566</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.935859380776759</v>
+        <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.784365957412188</v>
+        <v>-5.174909457320737</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.021756573498136</v>
+        <v>2.871093478977781</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.145879320756531</v>
+        <v>0.9653116932808428</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.623386973230678</v>
+        <v>5.52060070218833</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047749</v>
+        <v>3.821827147047747</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.94467335098677</v>
+        <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.752468440326942</v>
+        <v>-5.143011940235492</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.043329550542246</v>
+        <v>2.89266645602189</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.177776837841776</v>
+        <v>0.9972092103660886</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.651339453691836</v>
+        <v>5.548553182649488</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650759</v>
+        <v>3.825268416650757</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.940310935025967</v>
+        <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.767223764527083</v>
+        <v>-5.157767264435632</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.033065004901386</v>
+        <v>2.882401910381031</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.177776837841776</v>
+        <v>0.9972092103660886</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.646977037731033</v>
+        <v>5.544190766688685</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135753</v>
+        <v>3.845044666135752</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.931235438442247</v>
+        <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.717759141157171</v>
+        <v>-5.108302641065721</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.043775357665631</v>
+        <v>2.893112263145275</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.227241461211688</v>
+        <v>1.046673833736</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.66758031516926</v>
+        <v>5.564794044126912</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479228</v>
+        <v>3.825931790479226</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.927643106157181</v>
+        <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.554651149003556</v>
+        <v>-4.945194648912105</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.105426222242011</v>
+        <v>2.954763127721656</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.390349453365303</v>
+        <v>1.209781825889615</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.761852778176364</v>
+        <v>5.659066507134016</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844245</v>
+        <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.93669014284831</v>
+        <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.421843523506389</v>
+        <v>-4.812387023414939</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.167596309132006</v>
+        <v>3.016933214611651</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.390349453365303</v>
+        <v>1.209781825889615</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.770899814867492</v>
+        <v>5.668113543825144</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790948</v>
+        <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.937547607834431</v>
+        <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.484551439980947</v>
+        <v>-4.875094939889497</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.143370607528304</v>
+        <v>2.992707513007949</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.327641536890745</v>
+        <v>1.147073909415058</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.734132529968878</v>
+        <v>5.631346258926531</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578995</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.900457024624783</v>
+        <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.436543316137255</v>
+        <v>-4.827086816045804</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.125483273856133</v>
+        <v>2.974820179335778</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.327641536890745</v>
+        <v>1.147073909415058</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.697041946759231</v>
+        <v>5.594255675716883</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629888</v>
+        <v>3.872253907629886</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.904389278182734</v>
+        <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.357717658953664</v>
+        <v>-4.748261158862213</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.16094579028752</v>
+        <v>3.010282695767165</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.406467194074336</v>
+        <v>1.225899566598648</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.748269594627335</v>
+        <v>5.645483323584988</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.883559349524203</v>
+        <v>3.5246382103096</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.90612554924826</v>
+        <v>4.693212875353536</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.357717658953664</v>
+        <v>-4.748261158862213</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.16094579028752</v>
+        <v>3.010282695767165</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.406467194074336</v>
+        <v>1.225899566598648</v>
       </c>
       <c r="G2101" t="n">
-        <v>4.899189346234627</v>
+        <v>4.686276672339904</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240928.xlsx
+++ b/tame_output/ON/bt/strategyON_20240928.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>60.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>104.7%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>157.7%</t>
+          <t>178.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.4%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-71.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>417.8%</t>
+          <t>421.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-636.4%</t>
+          <t>-593.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-58.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>503.1%</t>
+          <t>-289.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-101.4%</t>
+          <t>-84.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>128.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,31 +1423,31 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2024-09-24</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>117.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>128.0%</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.84404504132242</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.3770038179956683</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-6.892247858564764</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.3561276111537315</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-7.059056518539125</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.2931831230931952</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.245776226848428</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.2144689352350708</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.628777615591059</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.06116627841643441</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.633264060792448</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.06194321630730881</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-7.99279438329645</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>-0.07651860939624155</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-8.043143446750673</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>-0.08874221482075262</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.140762724172069</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.1247481751675426</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.194834223680427</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1434832186493136</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.198410009772175</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.1394003359673706</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.232062848280648</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1483789168863239</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.371148962899506</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.1886416612404456</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.546273380286049</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2441362074475459</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.780725474300539</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.345136209954938</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.885100205326985</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.3935582931394928</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.603666987659597</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-9.047613671025569</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.45744788958037</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.701300418078284</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.173650464393859</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.505168878298571</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.676048795268541</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.116578692497928</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.4783498338537981</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.676048795268541</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.258250534222048</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.5364937974421879</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.676048795268541</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.208659689797214</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.5016040495073817</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.626457950843708</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.059741355325357</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.4550878493653223</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.595208360108535</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.833896202605946</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.3551707152413486</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.553281684521371</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.709317546268354</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.304200108150253</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.553281684521371</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.684280864699844</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.2915516613607414</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.527952596970635</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.612147689411962</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.2569646870069526</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.527952596970635</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.644238203941597</v>
+        <v>-8.608944028986157</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2795381552126726</v>
+        <v>-0.2654204852304956</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.524748936544829</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.550779169956373</v>
+        <v>-8.515484995000932</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2520380229314902</v>
+        <v>-0.2379203529493132</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.524748936544829</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.540125988402941</v>
+        <v>-8.504831813447501</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2496113108094913</v>
+        <v>-0.2354936408273143</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.524748936544829</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.442218949726451</v>
+        <v>-8.40692477477101</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.210748810312356</v>
+        <v>-0.196631140330179</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.456763186684273</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.418265408750493</v>
+        <v>-8.382971233795052</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2004988877764791</v>
+        <v>-0.1863812177943021</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.432809645708315</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.154205470427696</v>
+        <v>-8.118911295472255</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1081352286091124</v>
+        <v>-0.09401755862693539</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.168749707385519</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.447125846922858</v>
+        <v>-7.411831671967417</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.171909587132522</v>
+        <v>0.186027257114699</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.168749707385519</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.406941548556667</v>
+        <v>-7.371647373601227</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1883269303668396</v>
+        <v>0.2024446003490166</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.128565409019328</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.243541677617305</v>
+        <v>-7.208247502661864</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2530536999633415</v>
+        <v>0.2671713699455185</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9651655380799653</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.08542429823853</v>
+        <v>-7.050130123283089</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3242250805527038</v>
+        <v>0.3383427505348808</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.8070481587011898</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.935757907231014</v>
+        <v>-6.900463732275574</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.381199426642751</v>
+        <v>0.395317096624928</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7141446674586539</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.803482433600128</v>
+        <v>-6.768188258644687</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3353704021022601</v>
+        <v>0.3494880720844371</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.5818691938277673</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631621218035225</v>
+        <v>-6.596327043079785</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4069299490158578</v>
+        <v>0.4210476189980348</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4100079782628644</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.546656551305906</v>
+        <v>-6.511362376350466</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4538221569312442</v>
+        <v>0.4679398269134212</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.3250433115335448</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.652246541079011</v>
+        <v>-6.61695236612357</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2836102314227835</v>
+        <v>0.2977279014049605</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.4306333013066492</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.584011956453583</v>
+        <v>-6.548717781498143</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3594484071500412</v>
+        <v>0.3735660771322182</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.4122179784341132</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.436071915045984</v>
+        <v>-6.400777740090543</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3020036150746739</v>
+        <v>0.3161212850568509</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3918970625255556</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.383102392791995</v>
+        <v>-6.347808217836555</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.314477437722791</v>
+        <v>0.328595107704968</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.3389275402715667</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.217314196831705</v>
+        <v>-6.182020021876264</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.373832104011814</v>
+        <v>0.387949773993991</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.3389275402715667</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.183950990352936</v>
+        <v>-6.148656815397495</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4016397409844648</v>
+        <v>0.4157574109666418</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.3389275402715667</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.075691853230414</v>
+        <v>-6.040397678274974</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4394755162926685</v>
+        <v>0.4535931862748455</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.3389275402715667</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.952400718413283</v>
+        <v>-5.917106543457843</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4862900642300976</v>
+        <v>0.5004077342122746</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.2156364054544362</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.899703851281992</v>
+        <v>-5.864409676326551</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5150697893199392</v>
+        <v>0.5291874593021162</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.1629395383231451</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.655938409298548</v>
+        <v>-5.620644234343107</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6083566744603677</v>
+        <v>0.6224743444425447</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.1629395383231451</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.566162736922076</v>
+        <v>-5.530868561966635</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6463912573309725</v>
+        <v>0.6605089273131495</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.101340093408835</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.316312342973001</v>
+        <v>-5.28101816801756</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7390734898943045</v>
+        <v>0.7531911598764816</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.101340093408835</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.140420250505569</v>
+        <v>-5.105126075550128</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8130294504019262</v>
+        <v>0.8271471203841032</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.101340093408835</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.968973787483105</v>
+        <v>-4.933679612527665</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8949355416654652</v>
+        <v>0.9090532116476422</v>
       </c>
       <c r="F1921" t="n">
         <v>0.07010636961362809</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.888951500373985</v>
+        <v>-4.853657325418544</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9259649341254106</v>
+        <v>0.9400826041075876</v>
       </c>
       <c r="F1922" t="n">
         <v>0.1501286567227491</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.82531575814005</v>
+        <v>-4.790021583184609</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9561140320733017</v>
+        <v>0.9702317020554787</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2137643989566836</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.731618439923655</v>
+        <v>-4.696324264968214</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9747872181436554</v>
+        <v>0.9889048881258324</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2137643989566836</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.742121062988944</v>
+        <v>-4.706826888033503</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9723292455424173</v>
+        <v>0.9864469155245943</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2032617758913947</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.728709818338713</v>
+        <v>-4.594340627364629</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9816230572373299</v>
+        <v>1.035370733626964</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2032617758913947</v>
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.710996131460847</v>
+        <v>-4.581316567783857</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9893871159058161</v>
+        <v>1.041258941376613</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.1916139162608738</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.99800785567689</v>
+        <v>2.989110342560427</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.587521860147829</v>
+        <v>-4.457842296470839</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.035774895651017</v>
+        <v>1.087646721121813</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2064431047883115</v>
+        <v>0.1916139162608738</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.995005926896884</v>
+        <v>2.986108413780421</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.367501062110819</v>
+        <v>-4.237821498433829</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.125362251876435</v>
+        <v>1.177234077347232</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3476629498562918</v>
+        <v>0.3328337613288541</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.081316870948286</v>
+        <v>3.072419357831823</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.234633373047541</v>
+        <v>-4.104953809370551</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.19440351030357</v>
+        <v>1.246275335774366</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3476629498562918</v>
+        <v>0.3328337613288541</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.097211053750109</v>
+        <v>3.088313540633647</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.114460289683042</v>
+        <v>-3.984780726006052</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.243618588089671</v>
+        <v>1.295490413560467</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4678360332207907</v>
+        <v>0.453006844693353</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.170460748209111</v>
+        <v>3.161563235092648</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.979206928353065</v>
+        <v>-3.849527364676075</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.307808035183102</v>
+        <v>1.359679860653898</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6030893945507678</v>
+        <v>0.5882602060233302</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.261700867568536</v>
+        <v>3.252803354452074</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942103</v>
+        <v>3.735839222942105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.039081755710757</v>
+        <v>-3.909402192033768</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.26989559564145</v>
+        <v>1.321767421112247</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5432145671930757</v>
+        <v>0.5283853786656381</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.211813462555347</v>
+        <v>3.202915949438884</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.91926152479992</v>
+        <v>-3.78958196112293</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.333112857239994</v>
+        <v>1.384984682710791</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5432145671930757</v>
+        <v>0.5283853786656381</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.227102631789556</v>
+        <v>3.218205118673093</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.921731231261726</v>
+        <v>-3.792051667584736</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.239769173977713</v>
+        <v>1.29164099944851</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5407448607312695</v>
+        <v>0.5259156722038318</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.133265007234913</v>
+        <v>3.124367494118451</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003603</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.990101417585736</v>
+        <v>-3.860421853908746</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.131682960933411</v>
+        <v>1.183554786404207</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5351913712400468</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.058092288141944</v>
+        <v>3.049194775025481</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.101973697211887</v>
+        <v>-3.972294133534897</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.077370757714842</v>
+        <v>1.129242583185638</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5351913712400468</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.048528996773835</v>
+        <v>3.039631483657372</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.085999031725619</v>
+        <v>-3.956319468048629</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.050335148833376</v>
+        <v>1.102206974304173</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5351913712400468</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.015103521697863</v>
+        <v>3.0062060085814</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.91052477193315</v>
+        <v>-3.78084520825616</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.125092084742151</v>
+        <v>1.176963910212948</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5351913712400468</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.01967075368965</v>
+        <v>3.010773240573188</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.902600397348235</v>
+        <v>-3.772920833671245</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.104003863337324</v>
+        <v>1.155875688808121</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5500205597674844</v>
+        <v>0.5351913712400468</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.995412782450857</v>
+        <v>2.986515269334395</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.896322194778386</v>
+        <v>-3.766642631101397</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.035053457766714</v>
+        <v>1.08692528323751</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5562987623373334</v>
+        <v>0.5414695738098958</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.927718017394216</v>
+        <v>2.918820504277754</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264165</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.836469575574663</v>
+        <v>-3.706790011897673</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.069166891880335</v>
+        <v>1.121038717351132</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5562987623373334</v>
+        <v>0.5414695738098958</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.937890403826349</v>
+        <v>2.928992890709886</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742301</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.750226112548286</v>
+        <v>-3.620546548871296</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.098610547664747</v>
+        <v>1.150482373135543</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5562987623373334</v>
+        <v>0.5414695738098958</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.932836674400209</v>
+        <v>2.923939161283747</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.795532931947266</v>
+        <v>-3.665853368270276</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.07226359534968</v>
+        <v>1.124135420820477</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5154885993281026</v>
+        <v>0.500659410800665</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.900126352039196</v>
+        <v>2.891228838922734</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.824566036649567</v>
+        <v>-3.694886472972577</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.061202226501861</v>
+        <v>1.113074051972658</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5154885993281026</v>
+        <v>0.500659410800665</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.900678225072298</v>
+        <v>2.891780711955835</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.731755555198708</v>
+        <v>-3.602075991521718</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.02759911097357</v>
+        <v>1.079470936444367</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.608299080778962</v>
+        <v>0.5934698922515244</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.885637205834179</v>
+        <v>2.876739692717717</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.776145024528136</v>
+        <v>-3.646465460851146</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.0117167991664</v>
+        <v>1.063588624637197</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5639096114495343</v>
+        <v>0.5490804229220967</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.860877000161123</v>
+        <v>2.851979487044661</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.755641330642638</v>
+        <v>-3.625961766965649</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.014993985232322</v>
+        <v>1.066865810703119</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5844133053350317</v>
+        <v>0.569584116807594</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.868254925004145</v>
+        <v>2.859357411887682</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.83931342735497</v>
+        <v>-3.70963386367798</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9870164423780565</v>
+        <v>1.038888267848853</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5844133053350317</v>
+        <v>0.569584116807594</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.873746220834812</v>
+        <v>2.86484870771835</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.867093825256323</v>
+        <v>-3.737414261579334</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9874014849860544</v>
+        <v>1.039273310456851</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5566329074336787</v>
+        <v>0.541803718906241</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.868575183862539</v>
+        <v>2.859677670746076</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.985474497986462</v>
+        <v>-3.855794934309472</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7784049358946523</v>
+        <v>0.8302767613654489</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4894150552827025</v>
+        <v>0.4745858667552648</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.666600192572607</v>
+        <v>2.657702679456144</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.094088576429793</v>
+        <v>-3.964409012752803</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8551089652365256</v>
+        <v>0.9069807907073222</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4894150552827025</v>
+        <v>0.4745858667552648</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.786749853291812</v>
+        <v>2.77785234017535</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.05867953818165</v>
+        <v>-3.92899997450466</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8837856066381056</v>
+        <v>0.9356574321089024</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4894150552827025</v>
+        <v>0.4745858667552648</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.801262879394135</v>
+        <v>2.792365366277673</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.067140706837111</v>
+        <v>-3.937461143160121</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8778205805182901</v>
+        <v>0.9296924059890865</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4809538866272414</v>
+        <v>0.4661246980998038</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.793605619543228</v>
+        <v>2.784708106426765</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.890024376801945</v>
+        <v>-3.760344813124955</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9453961413776588</v>
+        <v>0.9972679668484554</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4809538866272414</v>
+        <v>0.4661246980998038</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.79033464838853</v>
+        <v>2.781437135272067</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.93511662163549</v>
+        <v>-3.805437057958501</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9280426352061537</v>
+        <v>0.9799144606769503</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4190578434578516</v>
+        <v>0.404228654930414</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.753880414248809</v>
+        <v>2.744982901132346</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.04720968428663</v>
+        <v>-3.626061636719733</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8769923854521124</v>
+        <v>1.045451604478872</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.3952669741528829</v>
+        <v>0.5610054131011326</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.733392867972242</v>
+        <v>2.832835931341192</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.092223897807235</v>
+        <v>-3.671075850240339</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8397941553754598</v>
+        <v>1.008253374402219</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.3649180788382783</v>
+        <v>0.530656517786528</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.695990986115069</v>
+        <v>2.795434049484019</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.35922840807967</v>
+        <v>-3.938080360512775</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7386839136054315</v>
+        <v>0.9071431326321906</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.1705550407953297</v>
+        <v>0.3362934797435794</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.585064725628246</v>
+        <v>2.684507788997196</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.460426189516843</v>
+        <v>-4.039278141949947</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6974087229270638</v>
+        <v>0.8658679419538229</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1021462272500105</v>
+        <v>0.2678846661982602</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.543223359397556</v>
+        <v>2.642666422766506</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.453915222902531</v>
+        <v>-4.032767175335635</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6976130711271056</v>
+        <v>0.8660722901538647</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1021462272500105</v>
+        <v>0.2678846661982602</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.540823320951872</v>
+        <v>2.640266384320822</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.434877095195233</v>
+        <v>-4.013729047628337</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7017530414182696</v>
+        <v>0.8702122604450286</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.04396261591881601</v>
+        <v>0.2097010548670657</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.502437873361401</v>
+        <v>2.601880936730351</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.487392897470054</v>
+        <v>-4.066244849903158</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8000411221425316</v>
+        <v>0.9685003411692907</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.04396261591881601</v>
+        <v>0.2097010548670657</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.621732274995591</v>
+        <v>2.721175338364541</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.490801208904633</v>
+        <v>-4.069653161337738</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.7995111265548334</v>
+        <v>0.9679703455815925</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.07647918492819339</v>
+        <v>0.2422176238764431</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.642075545387351</v>
+        <v>2.741518608756301</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.471445073010786</v>
+        <v>-4.05029702544389</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8132621113092982</v>
+        <v>0.9817213303360572</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.07647918492819339</v>
+        <v>0.2422176238764431</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.648084075784277</v>
+        <v>2.747527139153227</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.544774601748879</v>
+        <v>-4.123626554181983</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.6818805210912606</v>
+        <v>0.8503397401180197</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.07687384734781533</v>
+        <v>0.242612286296065</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.54627109451325</v>
+        <v>2.645714157882199</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.628595823023577</v>
+        <v>-4.207447775456681</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6511456541128622</v>
+        <v>0.8196048731396213</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.07687384734781533</v>
+        <v>0.242612286296065</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.549064716044731</v>
+        <v>2.64850777941368</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.622443116970793</v>
+        <v>-4.201295069403897</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.6542690849256343</v>
+        <v>0.8227283039523934</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.08302655340059961</v>
+        <v>0.2487649923488493</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.55341868806806</v>
+        <v>2.652861751437009</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.639252415121295</v>
+        <v>-4.218104367554399</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6466258424055438</v>
+        <v>0.8150850614323029</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.06621725525009797</v>
+        <v>0.2319556941983477</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.542413585917869</v>
+        <v>2.641856649286819</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.576954416345172</v>
+        <v>-4.155806368778276</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7378805957128136</v>
+        <v>0.9063398147395727</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.11151151952454</v>
+        <v>0.2772499584727897</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.635925698279355</v>
+        <v>2.735368761648305</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.375164218680014</v>
+        <v>-3.954016171113119</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6208886764930039</v>
+        <v>0.789347895519763</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.3095297116936944</v>
+        <v>0.4752681506419441</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.557028615294974</v>
+        <v>2.656471678663924</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.426050931366209</v>
+        <v>-4.004902883799313</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6708242237407012</v>
+        <v>0.8392834427674603</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.2586429990074999</v>
+        <v>0.4243814379557496</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.596786820005433</v>
+        <v>2.696229883374383</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.339440188716402</v>
+        <v>-3.918292141149506</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7200962569166676</v>
+        <v>0.8885554759434269</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3372687302126581</v>
+        <v>0.5030071691609078</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.658589994844572</v>
+        <v>2.758033058213521</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.399649486721687</v>
+        <v>-3.97850143915479</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6945485185392253</v>
+        <v>0.8630077375659848</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2770594322073736</v>
+        <v>0.4427978711556233</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.621000396866072</v>
+        <v>2.720443460235022</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.350462838037336</v>
+        <v>-3.929314790470439</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7127147960528943</v>
+        <v>0.8811740150796539</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2770594322073736</v>
+        <v>0.4427978711556233</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.619492014906001</v>
+        <v>2.718935078274951</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.306089706398767</v>
+        <v>-3.88494165883187</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.730326916143758</v>
+        <v>0.8987861351705175</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3214325638459422</v>
+        <v>0.4871710027941919</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.645978761324578</v>
+        <v>2.745421824693528</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.271358385080267</v>
+        <v>-3.850210337513369</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7386132388097488</v>
+        <v>0.9070724578365084</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3214325638459422</v>
+        <v>0.4871710027941919</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.640372555463169</v>
+        <v>2.739815618832119</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.223702654519211</v>
+        <v>-3.802554606952314</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7640572880619758</v>
+        <v>0.9325165070887351</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3690882944069979</v>
+        <v>0.5348267333552476</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.675347750827607</v>
+        <v>2.774790814196557</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.123184496020456</v>
+        <v>-3.702036448453559</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8091569248362025</v>
+        <v>0.9776161438629618</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4696064529057524</v>
+        <v>0.6353448918540021</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.740551019301585</v>
+        <v>2.839994082670534</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.107279166588103</v>
+        <v>-3.686131119021207</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8022737290850157</v>
+        <v>0.9707329481117752</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.3904937921965135</v>
+        <v>0.5562322311447632</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.679838095351914</v>
+        <v>2.779281158720863</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.062440764979705</v>
+        <v>-3.641292717412809</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8243067923390037</v>
+        <v>0.992766011365763</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.395037225141383</v>
+        <v>0.5607756640896326</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.686661857729464</v>
+        <v>2.786104921098413</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.081939221221713</v>
+        <v>-3.660791173654817</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8206683494732785</v>
+        <v>0.9891275685000376</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3469525838614787</v>
+        <v>0.5126910228097283</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.661972012592599</v>
+        <v>2.761415075961549</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.037736384135813</v>
+        <v>-3.616588336568916</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8442290868354758</v>
+        <v>1.012688305862235</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3911554209473792</v>
+        <v>0.5568938598956288</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.694373317371976</v>
+        <v>2.793816380740926</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.04529604997286</v>
+        <v>-3.624148002405963</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8396152209699044</v>
+        <v>1.008074439996664</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4459588249571985</v>
+        <v>0.6116972639054481</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.725665360247116</v>
+        <v>2.825108423616066</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.887004632433588</v>
+        <v>-3.465856584866691</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.954179553168653</v>
+        <v>1.122638772195412</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4459588249571985</v>
+        <v>0.6116972639054481</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.776913125430156</v>
+        <v>2.876356188799105</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.679362628799112</v>
+        <v>-3.258214581232215</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.035677059216697</v>
+        <v>1.204136278243456</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6536008285916746</v>
+        <v>0.8193392675399243</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.899939032205094</v>
+        <v>2.999382095574044</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.628330536076584</v>
+        <v>-3.207182488509687</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.051038124543978</v>
+        <v>1.219497343570737</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7046329213142025</v>
+        <v>0.8703713602624522</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.925506516076881</v>
+        <v>3.024949579445831</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.563106354949378</v>
+        <v>-3.141958307382481</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.094315201087565</v>
+        <v>1.262774420114325</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7698571024414081</v>
+        <v>0.9355955413896578</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.981828428845909</v>
+        <v>3.081271492214859</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.525679334878244</v>
+        <v>-3.104531287311347</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.105246981415299</v>
+        <v>1.273706200442058</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.7751086404705898</v>
+        <v>0.9408470794188395</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.980940323962699</v>
+        <v>3.080383387331648</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.524321349904699</v>
+        <v>-3.103173302337802</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.107046967735957</v>
+        <v>1.275506186762717</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8494467660084084</v>
+        <v>1.015185204956658</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.02679999161663</v>
+        <v>3.12624305498558</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.495908086804815</v>
+        <v>-3.074760039237918</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.278970043997122</v>
+        <v>1.447429263023881</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.7904712032619796</v>
+        <v>0.9562096422102293</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.151972424989983</v>
+        <v>3.251415488358933</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.421125825779802</v>
+        <v>-2.999977778212906</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.428995857624944</v>
+        <v>1.597455076651703</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8652534642869922</v>
+        <v>1.030991903235242</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.316954690822808</v>
+        <v>3.416397754191758</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.395041741515994</v>
+        <v>-2.973893693949098</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.431137467344326</v>
+        <v>1.599596686371086</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8652534642869922</v>
+        <v>1.030991903235242</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.308662666836667</v>
+        <v>3.408105730205617</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.307163828406874</v>
+        <v>-2.886015780839977</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.464481828171754</v>
+        <v>1.632941047198513</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9811791067103434</v>
+        <v>1.146917545658593</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.376411247874457</v>
+        <v>3.475854311243407</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.298271367013591</v>
+        <v>-2.877123319446694</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.485593218455858</v>
+        <v>1.654052437482618</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9811791067103434</v>
+        <v>1.146917545658593</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.393965653601249</v>
+        <v>3.493408716970199</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945368</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.466747483983469</v>
+        <v>-3.045599436416572</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.410057819072491</v>
+        <v>1.578517038099251</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9532312709937626</v>
+        <v>1.118969709942012</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.369051999575884</v>
+        <v>3.468495062944834</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.79557406678271</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.020491291354029</v>
+        <v>-2.599343243787132</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.569829993312129</v>
+        <v>1.738289212338888</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8585126013241299</v>
+        <v>1.02425104027238</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.293490494961967</v>
+        <v>3.392933558330916</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.997770187670876</v>
+        <v>-2.576622140103979</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.569582457282295</v>
+        <v>1.738041676309054</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8585126013241299</v>
+        <v>1.02425104027238</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.284154517458871</v>
+        <v>3.383597580827821</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.126972000964919</v>
+        <v>-2.705823953398022</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.676807857815847</v>
+        <v>1.845267076842606</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.7293107880300875</v>
+        <v>0.8950492269783374</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.365539555333615</v>
+        <v>3.464982618702565</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.152846399438944</v>
+        <v>-2.731698351872048</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.703535920919883</v>
+        <v>1.871995139946642</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7742223967418287</v>
+        <v>0.9399608356900786</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.429564343054306</v>
+        <v>3.529007406423256</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.145791709223771</v>
+        <v>-2.724643661656874</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.703033152995497</v>
+        <v>1.871492372022257</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.7812770869570025</v>
+        <v>0.9470155259052524</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.430472513172956</v>
+        <v>3.529915576541905</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331118</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.118840484897283</v>
+        <v>-2.697692437330386</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.723819796370834</v>
+        <v>1.892279015397593</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.7961574329847216</v>
+        <v>0.9618958719329715</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.449406874434328</v>
+        <v>3.548849937803278</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.14038471272807</v>
+        <v>-2.719236665161173</v>
       </c>
       <c r="E2003" t="n">
-        <v>1.899305237383479</v>
+        <v>2.067764456410238</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.7961574329847216</v>
+        <v>0.9618958719329715</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.633510006579288</v>
+        <v>3.732953069948238</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.162792830532942</v>
+        <v>-2.741644782966045</v>
       </c>
       <c r="E2004" t="n">
-        <v>1.882458685164523</v>
+        <v>2.050917904191283</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.7961574329847216</v>
+        <v>0.9618958719329715</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.625626701482282</v>
+        <v>3.725069764851231</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.191017066110542</v>
+        <v>-2.769869018543646</v>
       </c>
       <c r="E2005" t="n">
-        <v>1.873222990483121</v>
+        <v>2.04168220950988</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8141341854360302</v>
+        <v>0.9798726243842801</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.638466752502704</v>
+        <v>3.737909815871654</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.200457991999072</v>
+        <v>-2.779309944432176</v>
       </c>
       <c r="E2006" t="n">
-        <v>1.925700337849556</v>
+        <v>2.094159556876315</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9365613029794216</v>
+        <v>1.102299741927672</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.768176740750586</v>
+        <v>3.867619804119536</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.289334623167546</v>
+        <v>-2.868186575600649</v>
       </c>
       <c r="E2007" t="n">
-        <v>1.893040779927467</v>
+        <v>2.061499998954226</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8476846718109478</v>
+        <v>1.013423110759198</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.717741856594802</v>
+        <v>3.817184919963752</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.365664600768452</v>
+        <v>-2.944516553201555</v>
       </c>
       <c r="E2008" t="n">
-        <v>1.86062060178088</v>
+        <v>2.029079820807639</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8476846718109478</v>
+        <v>1.013423110759198</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.715853669488578</v>
+        <v>3.815296732857528</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887749</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.520621386168581</v>
+        <v>-3.099473338601685</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.793458117223691</v>
+        <v>1.96191733625045</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.6927278864108185</v>
+        <v>0.8584663253590685</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.617699827851363</v>
+        <v>3.717142891220313</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.682189811695836</v>
+        <v>-3.26104176412894</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.727264757222941</v>
+        <v>1.8957239762497</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.5659449626129391</v>
+        <v>0.7316834015611892</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.540064083782787</v>
+        <v>3.639507147151737</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.75459613538935</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.790490473565956</v>
+        <v>-3.369342425999059</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.697017899340812</v>
+        <v>1.865477118367571</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.5659449626129391</v>
+        <v>0.7316834015611892</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.553137490648706</v>
+        <v>3.652580554017656</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378387</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.8082944452867</v>
+        <v>-3.387146397719803</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.681901507435454</v>
+        <v>1.850360726462213</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.4954103397077381</v>
+        <v>0.661148778655988</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.502821913688525</v>
+        <v>3.602264977057475</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.836195232396173</v>
+        <v>-3.415047184829276</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.669265233718667</v>
+        <v>1.837724452745426</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.4608134155648033</v>
+        <v>0.6265518545130532</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.480587800329766</v>
+        <v>3.580030863698716</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.958721335099067</v>
+        <v>-3.53757328753217</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.617019236614708</v>
+        <v>1.785478455641467</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3382873128619094</v>
+        <v>0.5040257518101593</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.403836582685229</v>
+        <v>3.503279646054179</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585933</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.189235831284655</v>
+        <v>-3.768087783717759</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.591519397730976</v>
+        <v>1.759978616757736</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1077728166763207</v>
+        <v>0.2735112556245706</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.332233844564379</v>
+        <v>3.431676907933329</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.537980916509099</v>
+        <v>-4.116832868942202</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.592333082643046</v>
+        <v>1.760792301669805</v>
       </c>
       <c r="F2016" t="n">
-        <v>-0.0009751372425771399</v>
+        <v>0.1647633017056728</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.407296791214887</v>
+        <v>3.506739854583838</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.691967334285239</v>
+        <v>-4.270819286718343</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.599718784678229</v>
+        <v>1.768178003704989</v>
       </c>
       <c r="F2017" t="n">
-        <v>-0.0009751372425771399</v>
+        <v>0.1647633017056728</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.476277060360527</v>
+        <v>3.575720123729477</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.896566769148248</v>
+        <v>-4.475418721581351</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.503930212853147</v>
+        <v>1.672389431879906</v>
       </c>
       <c r="F2018" t="n">
-        <v>-0.0009751372425771399</v>
+        <v>0.1647633017056728</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.462328262480648</v>
+        <v>3.561771325849598</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.149041923155973</v>
+        <v>-4.727893875589076</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.414810640305471</v>
+        <v>1.583269859332231</v>
       </c>
       <c r="F2019" t="n">
-        <v>-0.0009751372425771399</v>
+        <v>0.1647633017056728</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.474198751536062</v>
+        <v>3.573641814905012</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.441937679635385</v>
+        <v>-5.020789632068488</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.29886287223265</v>
+        <v>1.46732209125941</v>
       </c>
       <c r="F2020" t="n">
-        <v>-0.0009751372425771399</v>
+        <v>0.1647633017056728</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.475409286055006</v>
+        <v>3.574852349423956</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.628601807770193</v>
+        <v>-5.207453760203296</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.228318963206048</v>
+        <v>1.396778182232808</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.02771410806713703</v>
+        <v>0.1380243308811129</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.463487645787591</v>
+        <v>3.562930709156541</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.774622494684155</v>
+        <v>-5.353474447117258</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.164988541176653</v>
+        <v>1.333447760203412</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.036797199860994</v>
+        <v>0.1289412390872559</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.453115643447467</v>
+        <v>3.552558706816416</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.86633650379374</v>
+        <v>-5.445188456226843</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.290506994231863</v>
+        <v>1.458966213258623</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.036797199860994</v>
+        <v>0.1289412390872559</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.615319700146511</v>
+        <v>3.714762763515461</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.897988162853709</v>
+        <v>-5.476840115286812</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.272692968571689</v>
+        <v>1.441152187598449</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.04196565710543421</v>
+        <v>0.1237727818428157</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.607065263763661</v>
+        <v>3.706508327132611</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.967054217426646</v>
+        <v>-5.545906169859749</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.255295964311006</v>
+        <v>1.423755183337765</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1043365345990442</v>
+        <v>0.06140190434920567</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.579872154835986</v>
+        <v>3.679315218204936</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.069030339675053</v>
+        <v>-5.647882292108156</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.223431153867545</v>
+        <v>1.391890372894305</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.2063126568474518</v>
+        <v>-0.0405742178992019</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.527612119942844</v>
+        <v>3.627055183311794</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231808</v>
+        <v>3.79829678423181</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.959024056197832</v>
+        <v>-5.537876008630935</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.259586554502609</v>
+        <v>1.428045773529369</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1831080849301766</v>
+        <v>-0.0173696459819267</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.533687750337384</v>
+        <v>3.633130813706334</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818517</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.815964480456906</v>
+        <v>-5.394816432890009</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.321060395520954</v>
+        <v>1.489519614547714</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1750946583401973</v>
+        <v>-0.009356219391947418</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.542745817013346</v>
+        <v>3.642188880382296</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051783</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.514517754985068</v>
+        <v>-5.093369707418171</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.448899968592225</v>
+        <v>1.617359187618984</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1263520671316399</v>
+        <v>0.2920905060798898</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.730874735178984</v>
+        <v>3.830317798547934</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.539107999220252</v>
+        <v>-5.117959951653355</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.440035048650862</v>
+        <v>1.608494267677622</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1263520671316399</v>
+        <v>0.2920905060798898</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.731845912931695</v>
+        <v>3.831288976300645</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.488069623213732</v>
+        <v>-5.066921575646835</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.461293303433226</v>
+        <v>1.629752522459985</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1263520671316399</v>
+        <v>0.2920905060798898</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.732688817311451</v>
+        <v>3.832131880680401</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.459220946390271</v>
+        <v>-5.038072898823375</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.491870873036755</v>
+        <v>1.660330092063515</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.1552007439551002</v>
+        <v>0.3209391829033501</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.769036122279672</v>
+        <v>3.868479185648622</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.362586034371631</v>
+        <v>-4.941437986804734</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.346708833968146</v>
+        <v>1.515168052994905</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.2518356559737401</v>
+        <v>0.41757409492199</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.643201065614791</v>
+        <v>3.74264412898374</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.293548023423163</v>
+        <v>-4.872399975856267</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.377826082421497</v>
+        <v>1.546285301448257</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3208736669222082</v>
+        <v>0.4866121058704581</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.688125916257836</v>
+        <v>3.787568979626786</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.77502886083346</v>
       </c>
       <c r="C2035" t="n">
         <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.129051689232202</v>
+        <v>-4.707903641665305</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.428051435173964</v>
+        <v>1.596510654200724</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4853700011131701</v>
+        <v>0.65110844006142</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.771250535848496</v>
+        <v>3.870693599217445</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077625</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.051953087690329</v>
+        <v>-4.630805040123432</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.458078586227143</v>
+        <v>1.626537805253903</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4853700011131701</v>
+        <v>0.65110844006142</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.770438246284925</v>
+        <v>3.869881309653875</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147911</v>
       </c>
       <c r="C2037" t="n">
         <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.062338282580218</v>
+        <v>-4.641190235013322</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.46379328739626</v>
+        <v>1.632252506423019</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4749848062232808</v>
+        <v>0.6407232451715307</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.774075908476064</v>
+        <v>3.873518971845014</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735281</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.080926441302443</v>
+        <v>-4.659778393735547</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.527195029683795</v>
+        <v>1.695654248710555</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4563966475010554</v>
+        <v>0.6221350864493054</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.833760019019154</v>
+        <v>3.933203082388104</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.081224987998479</v>
+        <v>-4.660076940431582</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.523944621823679</v>
+        <v>1.692403840850439</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4560981008050195</v>
+        <v>0.6218365397532695</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.830449901819831</v>
+        <v>3.929892965188781</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.980401854308051</v>
+        <v>-4.559253806741155</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.568804770239242</v>
+        <v>1.737263989266001</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4685623162893733</v>
+        <v>0.6343007552376233</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.842459326049835</v>
+        <v>3.941902389418784</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.789620493555644</v>
+        <v>-4.368472445988747</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.645246568018748</v>
+        <v>1.813705787045508</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6593436770417807</v>
+        <v>0.8250821159900307</v>
       </c>
       <c r="G2041" t="n">
-        <v>3.957057395979822</v>
+        <v>4.056500459348772</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.682657135706222</v>
+        <v>-4.261509088139325</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.667868756896113</v>
+        <v>1.836327975922873</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7178082850015821</v>
+        <v>0.8835467239498321</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.971973006493299</v>
+        <v>4.071416069862249</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.62732654780446</v>
+        <v>-4.206178500237563</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.724967928668877</v>
+        <v>1.893427147695636</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7731388729033443</v>
+        <v>0.9388773118515943</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.040138295846416</v>
+        <v>4.139581359215366</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.615272420891497</v>
+        <v>-4.1941243733246</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.7234761473355</v>
+        <v>1.891935366362259</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7851929998163071</v>
+        <v>0.9509314387645571</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.041057339895631</v>
+        <v>4.140500403264581</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.656427540459718</v>
+        <v>-4.235279492892821</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.708894729692347</v>
+        <v>1.877353948719106</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7440378802480861</v>
+        <v>0.9097763191963362</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.018244898338834</v>
+        <v>4.117687961707784</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.588378977768188</v>
+        <v>-4.167230930201291</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.748965180646842</v>
+        <v>1.917424399673601</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.812086442939616</v>
+        <v>0.977824881887866</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.071925061831634</v>
+        <v>4.171368125200584</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013428</v>
+        <v>3.645256780013427</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.819979370937689</v>
+        <v>-4.398831323370792</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.676527693552635</v>
+        <v>1.844986912579395</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.812086442939616</v>
+        <v>0.977824881887866</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.092127732005229</v>
+        <v>4.191570795374179</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.870030916466908</v>
+        <v>-4.448882868900011</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.64011331140783</v>
+        <v>1.808572530434589</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.812086442939616</v>
+        <v>0.977824881887866</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.075733968072111</v>
+        <v>4.175177031441061</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.045137749043352</v>
+        <v>-4.623989701476455</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.530322491970719</v>
+        <v>1.698781710997478</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.812086442939616</v>
+        <v>0.977824881887866</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.035985881665577</v>
+        <v>4.135428945034527</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.849037595612829</v>
+        <v>-4.427889548045933</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.615785172339868</v>
+        <v>1.784244391366627</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.008186596370139</v>
+        <v>1.173925035318389</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.160668592720831</v>
+        <v>4.260111656089781</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.696012203499545</v>
+        <v>-4.274864155932648</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.776166328758086</v>
+        <v>1.944625547784845</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.161211988483423</v>
+        <v>1.326950427431673</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.351654827561706</v>
+        <v>4.451097890930656</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.724319517372815</v>
+        <v>-4.303171469805918</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.95230962811707</v>
+        <v>2.12076884714383</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.161211988483423</v>
+        <v>1.326950427431673</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.539121052469999</v>
+        <v>4.638564115838949</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620436</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.890912742486337</v>
+        <v>-4.469764694919441</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.855075289425744</v>
+        <v>2.023534508452504</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9946187633699004</v>
+        <v>1.16035720231815</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.408568068755968</v>
+        <v>4.508011132124918</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.867876949124772</v>
+        <v>-4.446728901557875</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.867966009432088</v>
+        <v>2.036425228458848</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9946187633699004</v>
+        <v>1.16035720231815</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.412244471417686</v>
+        <v>4.511687534786636</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.838630968669075</v>
+        <v>-4.417482921102178</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.877282456737862</v>
+        <v>2.045741675764622</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9946187633699004</v>
+        <v>1.16035720231815</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.409862526541181</v>
+        <v>4.509305589910131</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256373</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.945556516546926</v>
+        <v>-4.524408468980029</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.831805476744357</v>
+        <v>2.000264695771116</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.887693215492049</v>
+        <v>1.053431654440299</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.343000436972105</v>
+        <v>4.442443500341055</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.090575075054175</v>
+        <v>-4.669427027487278</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.775226855484692</v>
+        <v>1.943686074511451</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7426746569848005</v>
+        <v>0.9084130959330505</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.25741810401099</v>
+        <v>4.35686116737994</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687014</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.208916840838892</v>
+        <v>-4.787768793271995</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.827821388428557</v>
+        <v>1.996280607455317</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7533606955476906</v>
+        <v>0.9190991344959406</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.363760966406477</v>
+        <v>4.463204029775427</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.2603272631596</v>
+        <v>-4.839179215592703</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.805042916626213</v>
+        <v>1.973502135652973</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7533606955476906</v>
+        <v>0.9190991344959406</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.361546663532416</v>
+        <v>4.460989726901366</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.339746714367352</v>
+        <v>-4.918598666800455</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.773178264217402</v>
+        <v>1.941637483244161</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7533606955476906</v>
+        <v>0.9190991344959406</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.361449791606705</v>
+        <v>4.460892854975655</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.43520971228457</v>
+        <v>-5.014061664717673</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.734986958608558</v>
+        <v>1.903446177635317</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7533606955476906</v>
+        <v>0.9190991344959406</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.361443685164748</v>
+        <v>4.460886748533698</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.370833801433855</v>
+        <v>-4.949685753866958</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.758833719511455</v>
+        <v>1.927292938538214</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.8177366063984057</v>
+        <v>0.9834750453466558</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.398165628237788</v>
+        <v>4.497608691606738</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.426202963566048</v>
+        <v>-5.005054915999152</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.742419872406304</v>
+        <v>1.910879091433063</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.8177366063984057</v>
+        <v>0.9834750453466558</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.403899445985514</v>
+        <v>4.503342509354464</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.444421430563657</v>
+        <v>-5.02327338299676</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.734670848950193</v>
+        <v>1.903130067976952</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.7926301691425636</v>
+        <v>0.9583686080908136</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.388373946974942</v>
+        <v>4.487817010343892</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.356214596416079</v>
+        <v>-4.935066548849182</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.789827975459543</v>
+        <v>1.958287194486302</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.7926301691425636</v>
+        <v>0.9583686080908136</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.408248339825261</v>
+        <v>4.507691403194211</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.250179601210769</v>
+        <v>-4.829031553643873</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.815942674066394</v>
+        <v>1.984401893093153</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.7926301691425636</v>
+        <v>0.9583686080908136</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.391949040349989</v>
+        <v>4.491392103718939</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.066967938077674</v>
+        <v>-4.645819890510777</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.891658288783678</v>
+        <v>2.060117507810437</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.7926301691425636</v>
+        <v>0.9583686080908136</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.394379989814034</v>
+        <v>4.493823053182984</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.995246491063823</v>
+        <v>-4.574098443496927</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.903291273668595</v>
+        <v>2.071750492695354</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.8643516161564142</v>
+        <v>1.030090055104664</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.420357264101721</v>
+        <v>4.519800327470671</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.972873465456117</v>
+        <v>-4.55172541788922</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.859156229832849</v>
+        <v>2.027615448859609</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.8756073672693158</v>
+        <v>1.041345806217566</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.374026460690634</v>
+        <v>4.473469524059584</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71560744645673</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.005889761366862</v>
+        <v>-4.584741713799965</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.031147916353907</v>
+        <v>2.199607135380666</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8061699906025641</v>
+        <v>0.9719084295508142</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.517562239575938</v>
+        <v>4.617005302944889</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.71376253688368</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.994362125717253</v>
+        <v>-4.573214078150357</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.027680196442</v>
+        <v>2.196139415468759</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.8651706488039266</v>
+        <v>1.030909087752177</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.544883860325005</v>
+        <v>4.644326923693955</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236299</v>
+        <v>3.7171506992363</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.091703627059622</v>
+        <v>-4.670555579492725</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.99241170842684</v>
+        <v>2.1608709274536</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8207504666384382</v>
+        <v>0.9864889055866883</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.521899863547501</v>
+        <v>4.621342926916451</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.177559656399588</v>
+        <v>-4.756411608832692</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.959320378883692</v>
+        <v>2.127779597910451</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7783743974123032</v>
+        <v>0.9441128363605533</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.497725304204658</v>
+        <v>4.597168367573608</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.186396453815708</v>
+        <v>-4.765248406248811</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.938204861737746</v>
+        <v>2.106664080764506</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7709322247709525</v>
+        <v>0.9366706637192026</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.475679202440349</v>
+        <v>4.575122265809299</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.715544411667457</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.277779016381166</v>
+        <v>-4.85663096881427</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.911816347756612</v>
+        <v>2.080275566783372</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.7343673400516078</v>
+        <v>0.9001057789998579</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.463904782653792</v>
+        <v>4.563347846022742</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889193</v>
+        <v>3.673978374889194</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.26607229839416</v>
+        <v>-4.844924250827264</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.018627292775683</v>
+        <v>2.187086511802442</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.7460740580386142</v>
+        <v>0.9118124969868643</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.573057071270264</v>
+        <v>4.672500134639214</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409569</v>
+        <v>3.68247609940957</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.336984372136438</v>
+        <v>-4.915836324569542</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.993294802010177</v>
+        <v>2.161754021036936</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.7460740580386142</v>
+        <v>0.9118124969868643</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.576089410001669</v>
+        <v>4.675532473370619</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.34730047030279</v>
+        <v>-4.926152422735893</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.202073196021694</v>
+        <v>2.370532415048453</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.7460740580386142</v>
+        <v>0.9118124969868643</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.788994243279727</v>
+        <v>4.888437306648677</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.347206502285418</v>
+        <v>-4.926058454718521</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.201289450140732</v>
+        <v>2.369748669167492</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.7464439193859321</v>
+        <v>0.9121823583341823</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.788394827000207</v>
+        <v>4.887837890369157</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988021</v>
+        <v>3.63321346798802</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.495572729941562</v>
+        <v>-5.074424682374666</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.136174945022628</v>
+        <v>2.304634164049388</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.7464439193859321</v>
+        <v>0.9121823583341823</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.782626812944561</v>
+        <v>4.882069876313511</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740924</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.494624306823524</v>
+        <v>-5.073476259256627</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.136554314269844</v>
+        <v>2.305013533296603</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.7464439193859321</v>
+        <v>0.9121823583341823</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.782626812944561</v>
+        <v>4.882069876313511</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.594894124782545</v>
+        <v>-5.173746077215648</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.109173995067327</v>
+        <v>2.277633214094087</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.7464439193859321</v>
+        <v>0.9121823583341823</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.795354420925653</v>
+        <v>4.894797484294603</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.588901877993734</v>
+        <v>-5.167753830426837</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.11351689220724</v>
+        <v>2.281976111233999</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.7464439193859321</v>
+        <v>0.9121823583341823</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.797300419350041</v>
+        <v>4.896743482718991</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.500343916862966</v>
+        <v>-5.079195869296069</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.142594212677316</v>
+        <v>2.311053431704075</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.7464439193859321</v>
+        <v>0.9121823583341823</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.79095455536781</v>
+        <v>4.89039761873676</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383088</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.482584839359892</v>
+        <v>-5.061436791792995</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.149006521117541</v>
+        <v>2.3174657401443</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.7464439193859321</v>
+        <v>0.9121823583341823</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.790263232806805</v>
+        <v>4.889706296175755</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.382954688310824</v>
+        <v>-4.961806640743927</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.201640767445755</v>
+        <v>2.370099986472514</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.8460740704349996</v>
+        <v>1.01181250938325</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.862823509344833</v>
+        <v>4.962266572713783</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.775357097455272</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.432354196999835</v>
+        <v>-5.011206149432939</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.371035229468877</v>
+        <v>2.539494448495636</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.8563329038667443</v>
+        <v>1.022071342814995</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.058133074902606</v>
+        <v>5.157576138271556</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.749078058963134</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.225669723357459</v>
+        <v>-4.804521675790562</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.440897692028689</v>
+        <v>2.609356911055449</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.06301737750912</v>
+        <v>1.22875581645737</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.169332432190893</v>
+        <v>5.268775495559844</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162544</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.259826618354985</v>
+        <v>-4.838678570788089</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.429236447683784</v>
+        <v>2.597695666710543</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.9794336079683074</v>
+        <v>1.145172046916558</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.121183684120511</v>
+        <v>5.220626747489461</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652383</v>
+        <v>3.782482115652384</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.167237139293529</v>
+        <v>-4.746089091726632</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.819769353298034</v>
+        <v>2.988228572324793</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.9794336079683074</v>
+        <v>1.145172046916558</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.474680798110178</v>
+        <v>5.574123861479128</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108673</v>
+        <v>3.809055905108674</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.227125767117079</v>
+        <v>-4.805977719550182</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.800377013735717</v>
+        <v>2.968836232762476</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.9653116932808428</v>
+        <v>1.131050132229093</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.470770760864802</v>
+        <v>5.570213824233752</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.174909457320737</v>
+        <v>-4.753761409753841</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.871093478977781</v>
+        <v>3.03955269800454</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.9653116932808428</v>
+        <v>1.131050132229093</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.52060070218833</v>
+        <v>5.62004376555728</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.143011940235492</v>
+        <v>-4.721863892668595</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.89266645602189</v>
+        <v>3.06112567504865</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.9972092103660886</v>
+        <v>1.162947649314339</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.548553182649488</v>
+        <v>5.647996246018439</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.157767264435632</v>
+        <v>-4.736619216868736</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.882401910381031</v>
+        <v>3.050861129407791</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.9972092103660886</v>
+        <v>1.162947649314339</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.544190766688685</v>
+        <v>5.643633830057635</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.108302641065721</v>
+        <v>-4.687154593498824</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.893112263145275</v>
+        <v>3.061571482172035</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.046673833736</v>
+        <v>1.212412272684251</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.564794044126912</v>
+        <v>5.664237107495862</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479226</v>
+        <v>3.825931790479225</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.945194648912105</v>
+        <v>-4.524046601345209</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.954763127721656</v>
+        <v>3.123222346748415</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.209781825889615</v>
+        <v>1.375520264837866</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.659066507134016</v>
+        <v>5.758509570502966</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844243</v>
+        <v>3.847096478844247</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.812387023414939</v>
+        <v>-4.391238975848042</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.016933214611651</v>
+        <v>3.18539243363841</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.209781825889615</v>
+        <v>1.375520264837866</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.668113543825144</v>
+        <v>5.767556607194094</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790947</v>
+        <v>3.83242598779095</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.875094939889497</v>
+        <v>-4.4539468923226</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.992707513007949</v>
+        <v>3.161166732034709</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.147073909415058</v>
+        <v>1.312812348363308</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.631346258926531</v>
+        <v>5.730789322295481</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578993</v>
+        <v>3.861579399578996</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.827086816045804</v>
+        <v>-4.405938768478907</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.974820179335778</v>
+        <v>3.143279398362538</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.147073909415058</v>
+        <v>1.312812348363308</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.594255675716883</v>
+        <v>5.693698739085833</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629886</v>
+        <v>3.872253907629888</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.748261158862213</v>
+        <v>-4.327113111295317</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.010282695767165</v>
+        <v>3.178741914793925</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.225899566598648</v>
+        <v>1.391638005546898</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.645483323584988</v>
+        <v>5.744926386953938</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.5246382103096</v>
+        <v>3.889937278966912</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.693212875353536</v>
+        <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.748261158862213</v>
+        <v>-4.31751401018758</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.010282695767165</v>
+        <v>3.177480647844056</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.225899566598648</v>
+        <v>1.391638005546898</v>
       </c>
       <c r="G2101" t="n">
-        <v>4.686276672339904</v>
+        <v>5.739825479560975</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240928.xlsx
+++ b/tame_output/ON/bt/strategyON_20240928.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>178.9%</t>
+          <t>179.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.2%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.3%</t>
+          <t>-606.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-58.5%</t>
+          <t>-63.4%</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-289.0%</t>
+          <t>-284.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-84.8%</t>
+          <t>-85.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.6%</t>
+          <t>128.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>117.1%</t>
+          <t>117.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>128.2%</t>
         </is>
       </c>
     </row>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.84404504132242</v>
+        <v>-6.879339216277861</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3770038179956683</v>
+        <v>0.3628861480134917</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.892247858564764</v>
+        <v>-6.927542033520205</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3561276111537315</v>
+        <v>0.3420099411715549</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.059056518539125</v>
+        <v>-7.181546978503919</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2931831230931952</v>
+        <v>0.2441869391072777</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8737429271534751</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.605594265297281</v>
+        <v>2.592916398530508</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.245776226848428</v>
+        <v>-7.368266686813222</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2144689352350708</v>
+        <v>0.1654727512491534</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8737429271534751</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.601567960762878</v>
+        <v>2.588890093996105</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.628777615591059</v>
+        <v>-7.751268075555853</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.06116627841643441</v>
+        <v>0.01217009443051698</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.8737429271534751</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.601465859441294</v>
+        <v>2.588787992674521</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.633264060792448</v>
+        <v>-7.755754520757241</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.06194321630730881</v>
+        <v>0.01294703232139183</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.8782293723548638</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.601345508291891</v>
+        <v>2.588667641525118</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.99279438329645</v>
+        <v>-8.115284843261243</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.07651860939624155</v>
+        <v>-0.125514793382159</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.8782293723548638</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.606695811589941</v>
+        <v>2.594017944823168</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.043143446750673</v>
+        <v>-8.165633906715465</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.08874221482075262</v>
+        <v>-0.1377383988066705</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9074486578644647</v>
+        <v>-0.9285784358090858</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.584402393474585</v>
+        <v>2.571724526707812</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.140762724172069</v>
+        <v>-8.263253184136861</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1247481751675426</v>
+        <v>-0.17374435915346</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.005067935285861</v>
+        <v>-1.026197713230482</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.516194710876743</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.194834223680427</v>
+        <v>-8.31732468364522</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1434832186493136</v>
+        <v>-0.1924794026352314</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.059139434794221</v>
+        <v>-1.080269212738842</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.4866453674933</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.198410009772175</v>
+        <v>-8.320900469736968</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1394003359673706</v>
+        <v>-0.188396519953288</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.084668356710713</v>
+        <v>-1.105798134655335</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.476841211462046</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.232062848280648</v>
+        <v>-8.354553308245441</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1483789168863239</v>
+        <v>-0.1973751008722413</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.185081724627751</v>
+        <v>-1.206211502572372</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.42107574519626</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.371148962899506</v>
+        <v>-8.493639422864298</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1886416612404456</v>
+        <v>-0.237637845226363</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.345297617191229</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.352995777918367</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.546273380286049</v>
+        <v>-8.668763840250842</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2441362074475459</v>
+        <v>-0.2931323914334638</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.520422034577773</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.262476348233958</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.780725474300539</v>
+        <v>-8.903215934265331</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.345136209954938</v>
+        <v>-0.3941323939408554</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.520422034577773</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.255257183332362</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.885100205326985</v>
+        <v>-9.007590665291778</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3935582931394928</v>
+        <v>-0.4425544771254102</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.624796765604218</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.185960153942518</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.047613671025569</v>
+        <v>-9.170104130990362</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.45744788958037</v>
+        <v>-0.5064440735662878</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.722430196022905</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.128495885529862</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.173650464393859</v>
+        <v>-9.296140924358651</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.505168878298571</v>
+        <v>-0.5541650622844889</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.697178573213163</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.146340587844822</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.116578692497928</v>
+        <v>-9.23906915246272</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4783498338537981</v>
+        <v>-0.5273460178397156</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.697178573213163</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.150330923531223</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.258250534222048</v>
+        <v>-9.380740994186841</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5364937974421879</v>
+        <v>-0.5854899814281054</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.697178573213163</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.148855696632482</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.208659689797214</v>
+        <v>-9.331150149762006</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5016040495073817</v>
+        <v>-0.5506002334932996</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.647587728788329</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.193663613452254</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.059741355325357</v>
+        <v>-9.18223181529015</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4550878493653223</v>
+        <v>-0.5040840333512397</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.616338138053156</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.199362234246675</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.833896202605946</v>
+        <v>-8.956386662570738</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3551707152413486</v>
+        <v>-0.4041668992272665</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.574411462465992</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.234097312635182</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.709317546268354</v>
+        <v>-8.831808006233146</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.304200108150253</v>
+        <v>-0.3531962921361709</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.574411462465992</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.235236457191241</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.684280864699844</v>
+        <v>-8.806771324664636</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2915516613607414</v>
+        <v>-0.3405478453466593</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.549082374915256</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.25306768388379</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.612147689411962</v>
+        <v>-8.734638149376755</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2569646870069526</v>
+        <v>-0.3059608709928701</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.549082374915256</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.258801388122426</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.608944028986157</v>
+        <v>-8.731434488950949</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2654204852304956</v>
+        <v>-0.314416669216413</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.54587871448945</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.263664188750818</v>
+        <v>2.250986321984045</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.515484995000932</v>
+        <v>-8.637975454965725</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2379203529493132</v>
+        <v>-0.2869165369352307</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.54587871448945</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.25378070743791</v>
+        <v>2.241102840671137</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.504831813447501</v>
+        <v>-8.627322273412293</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2354936408273143</v>
+        <v>-0.2844898248132322</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.524748936544829</v>
+        <v>-1.54587871448945</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.251946146938536</v>
+        <v>2.239268280171764</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.40692477477101</v>
+        <v>-8.529415234735803</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.196631140330179</v>
+        <v>-0.2456273243160965</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.456763186684273</v>
+        <v>-1.477892964628894</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.292437281881409</v>
+        <v>2.279759415114636</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.382971233795052</v>
+        <v>-8.505461693759845</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1863812177943021</v>
+        <v>-0.2353774017802199</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.432809645708315</v>
+        <v>-1.453939423652936</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.307477912612478</v>
+        <v>2.294800045845705</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.118911295472255</v>
+        <v>-8.241401755437048</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.09401755862693539</v>
+        <v>-0.1430137426128533</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.18987948533014</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.452653559444403</v>
+        <v>2.43997569267763</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.411831671967417</v>
+        <v>-7.53432213193221</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.186027257114699</v>
+        <v>0.1370310731287812</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.168749707385519</v>
+        <v>-1.18987948533014</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.449866525784102</v>
+        <v>2.43718865901733</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.371647373601227</v>
+        <v>-7.494137833566019</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2024446003490166</v>
+        <v>0.1534484163630987</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.128565409019328</v>
+        <v>-1.149695186963949</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.474320728691658</v>
+        <v>2.461642861924886</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.208247502661864</v>
+        <v>-7.330737962626657</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2671713699455185</v>
+        <v>0.2181751859596006</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9651655380799653</v>
+        <v>-0.9862953160245866</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.571727472476033</v>
+        <v>2.55904960570926</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.050130123283089</v>
+        <v>-7.172620583247881</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3383427505348808</v>
+        <v>0.2893465665489634</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8070481587011898</v>
+        <v>-0.8281779366458112</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.67452232894115</v>
+        <v>2.661844462174377</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.900463732275574</v>
+        <v>-7.022954192240366</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.395317096624928</v>
+        <v>0.3463209126390101</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7141446674586539</v>
+        <v>-0.7352744454032752</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.727372213373712</v>
+        <v>2.71469434660694</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.768188258644687</v>
+        <v>-6.89067871860948</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3494880720844371</v>
+        <v>0.3004918880985192</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5818691938277673</v>
+        <v>-0.6029989717723886</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.707998283559399</v>
+        <v>2.695320416792626</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.596327043079785</v>
+        <v>-6.718817503044577</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4210476189980348</v>
+        <v>0.3720514350121169</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4100079782628644</v>
+        <v>-0.4311377562074857</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.813930073585978</v>
+        <v>2.801252206819205</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.511362376350466</v>
+        <v>-6.633852836315258</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4679398269134212</v>
+        <v>0.4189436429275033</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3250433115335448</v>
+        <v>-0.3461730894781662</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.877815214847228</v>
+        <v>2.865137348080455</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.61695236612357</v>
+        <v>-6.739442826088363</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2977279014049605</v>
+        <v>0.2487317174190431</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4306333013066492</v>
+        <v>-0.4517630792512705</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.686485291384147</v>
+        <v>2.673807424617374</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.548717781498143</v>
+        <v>-6.671208241462935</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3735660771322182</v>
+        <v>0.3245698931463004</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4122179784341132</v>
+        <v>-0.4333477563787345</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.746078826984755</v>
+        <v>2.733400960217982</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.400777740090543</v>
+        <v>-6.523268200055336</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3161212850568509</v>
+        <v>0.267125101070933</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3918970625255556</v>
+        <v>-0.413026840470177</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.641650567891482</v>
+        <v>2.628972701124709</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.347808217836555</v>
+        <v>-6.470298677801347</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.328595107704968</v>
+        <v>0.2795989237190502</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3600573182161881</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.664718294990398</v>
+        <v>2.652040428223625</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.182020021876264</v>
+        <v>-6.304510481841056</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.387949773993991</v>
+        <v>0.3389535900080736</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3600573182161881</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.657757682895304</v>
+        <v>2.645079816128531</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.148656815397495</v>
+        <v>-6.271147275362288</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4157574109666418</v>
+        <v>0.3667612269807239</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3600573182161881</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.672220037276448</v>
+        <v>2.659542170509674</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.040397678274974</v>
+        <v>-6.162888138239766</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4535931862748455</v>
+        <v>0.4045970022889276</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3389275402715667</v>
+        <v>-0.3600573182161881</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.666752157735643</v>
+        <v>2.654074290968869</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.917106543457843</v>
+        <v>-6.039597003422635</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5004077342122746</v>
+        <v>0.4514115502263567</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2156364054544362</v>
+        <v>-0.2367661833990576</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.738224932636498</v>
+        <v>2.725547065869725</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.864409676326551</v>
+        <v>-5.986900136291344</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5291874593021162</v>
+        <v>0.4801912753161988</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1840693162677664</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.777544031152598</v>
+        <v>2.764866164385825</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.620644234343107</v>
+        <v>-5.7431346943079</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6224743444425447</v>
+        <v>0.5734781604566273</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1629395383231451</v>
+        <v>-0.1840693162677664</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.773324739499648</v>
+        <v>2.760646872732875</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.530868561966635</v>
+        <v>-5.653359021931427</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6605089273131495</v>
+        <v>0.611512743327232</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.1224698713534564</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.81240872036825</v>
+        <v>2.799730853601477</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.28101816801756</v>
+        <v>-5.403508627982353</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7531911598764816</v>
+        <v>0.7041949758905641</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.1224698713534564</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.805150795351952</v>
+        <v>2.792472928585179</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.105126075550128</v>
+        <v>-5.227616535514921</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8271471203841032</v>
+        <v>0.7781509363981853</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.101340093408835</v>
+        <v>-0.1224698713534564</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.808749918872601</v>
+        <v>2.796072052105828</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.933679612527665</v>
+        <v>-5.056170072492457</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9090532116476422</v>
+        <v>0.8600570276617248</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.07010636961362809</v>
+        <v>0.04897659166900675</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.924945302740633</v>
+        <v>2.91226743597386</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.853657325418544</v>
+        <v>-4.976147785383336</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9400826041075876</v>
+        <v>0.8910864201216699</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1501286567227491</v>
+        <v>0.1289988787781277</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.971979152622402</v>
+        <v>2.959301285855629</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.790021583184609</v>
+        <v>-4.912512043149402</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9702317020554787</v>
+        <v>0.9212355180695611</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.1926346210120622</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.01485539901708</v>
+        <v>3.002177532250307</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.696324264968214</v>
+        <v>-4.818814724933007</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9889048881258324</v>
+        <v>0.9399087041399148</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2137643989566836</v>
+        <v>0.1926346210120622</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.996049657800876</v>
+        <v>2.983371791034103</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.706826888033503</v>
+        <v>-4.829317347998296</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9864469155245943</v>
+        <v>0.9374507315386764</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.1821319979467734</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.99149116058658</v>
+        <v>2.978813293819807</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.594340627364629</v>
+        <v>-4.716831087329421</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.035370733626964</v>
+        <v>0.9863745496410465</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2032617758913947</v>
+        <v>0.1821319979467734</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.9954204744214</v>
+        <v>2.982742607654627</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.581316567783857</v>
+        <v>-4.699117400451556</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.041258941376613</v>
+        <v>0.9941386083095327</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1916139162608738</v>
+        <v>0.1853133268436902</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.989110342560427</v>
+        <v>2.985329988910117</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.457842296470839</v>
+        <v>-4.575643129138538</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.087646721121813</v>
+        <v>1.040526388054734</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1916139162608738</v>
+        <v>0.1853133268436902</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.986108413780421</v>
+        <v>2.982328060130111</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.237821498433829</v>
+        <v>-4.355622331101527</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.177234077347232</v>
+        <v>1.130113744280152</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3328337613288541</v>
+        <v>0.3265331719116704</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.072419357831823</v>
+        <v>3.068639004181513</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.104953809370551</v>
+        <v>-4.222754642038249</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.246275335774366</v>
+        <v>1.199155002707286</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3328337613288541</v>
+        <v>0.3265331719116704</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.088313540633647</v>
+        <v>3.084533186983336</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.984780726006052</v>
+        <v>-4.102581558673751</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.295490413560467</v>
+        <v>1.248370080493387</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.453006844693353</v>
+        <v>0.4467062552761694</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.161563235092648</v>
+        <v>3.157782881442337</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.849527364676075</v>
+        <v>-3.967328197343774</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.359679860653898</v>
+        <v>1.312559527586818</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5882602060233302</v>
+        <v>0.5819596166061465</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.252803354452074</v>
+        <v>3.249023000801764</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.909402192033768</v>
+        <v>-4.027203024701466</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.321767421112247</v>
+        <v>1.274647088045167</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5283853786656381</v>
+        <v>0.5220847892484544</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.202915949438884</v>
+        <v>3.199135595788574</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.78958196112293</v>
+        <v>-3.907382793790628</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.384984682710791</v>
+        <v>1.337864349643711</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5283853786656381</v>
+        <v>0.5220847892484544</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.218205118673093</v>
+        <v>3.214424765022783</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.792051667584736</v>
+        <v>-3.909852500252434</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.29164099944851</v>
+        <v>1.24452066638143</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5259156722038318</v>
+        <v>0.5196150827866481</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.124367494118451</v>
+        <v>3.120587140468141</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.860421853908746</v>
+        <v>-3.978222686576444</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.183554786404207</v>
+        <v>1.136434453337127</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5351913712400468</v>
+        <v>0.5288907818228631</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.049194775025481</v>
+        <v>3.045414421375171</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.972294133534897</v>
+        <v>-4.090094966202595</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.129242583185638</v>
+        <v>1.082122250118558</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5351913712400468</v>
+        <v>0.5288907818228631</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.039631483657372</v>
+        <v>3.035851130007062</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.956319468048629</v>
+        <v>-4.074120300716327</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.102206974304173</v>
+        <v>1.055086641237093</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5351913712400468</v>
+        <v>0.5288907818228631</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.0062060085814</v>
+        <v>3.002425654931089</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.78084520825616</v>
+        <v>-3.898646040923858</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.176963910212948</v>
+        <v>1.129843577145868</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5351913712400468</v>
+        <v>0.5288907818228631</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.010773240573188</v>
+        <v>3.006992886922878</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.772920833671245</v>
+        <v>-3.890721666338944</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.155875688808121</v>
+        <v>1.108755355741041</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5351913712400468</v>
+        <v>0.5288907818228631</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.986515269334395</v>
+        <v>2.982734915684085</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.766642631101397</v>
+        <v>-3.884443463769095</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.08692528323751</v>
+        <v>1.03980495017043</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5414695738098958</v>
+        <v>0.5351689843927121</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.918820504277754</v>
+        <v>2.915040150627444</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264165</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.706790011897673</v>
+        <v>-3.824590844565372</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.121038717351132</v>
+        <v>1.073918384284052</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5414695738098958</v>
+        <v>0.5351689843927121</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.928992890709886</v>
+        <v>2.925212537059576</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742301</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.620546548871296</v>
+        <v>-3.738347381538994</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.150482373135543</v>
+        <v>1.103362040068463</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5414695738098958</v>
+        <v>0.5351689843927121</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.923939161283747</v>
+        <v>2.920158807633436</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.665853368270276</v>
+        <v>-3.783654200937974</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.124135420820477</v>
+        <v>1.077015087753397</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.500659410800665</v>
+        <v>0.4943588213834813</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.891228838922734</v>
+        <v>2.887448485272424</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.694886472972577</v>
+        <v>-3.812687305640276</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.113074051972658</v>
+        <v>1.065953718905578</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.500659410800665</v>
+        <v>0.4943588213834813</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.891780711955835</v>
+        <v>2.888000358305525</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.602075991521718</v>
+        <v>-3.719876824189416</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.079470936444367</v>
+        <v>1.032350603377287</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5934698922515244</v>
+        <v>0.5871693028343407</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.876739692717717</v>
+        <v>2.872959339067406</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.646465460851146</v>
+        <v>-3.764266293518844</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.063588624637197</v>
+        <v>1.016468291570117</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5490804229220967</v>
+        <v>0.542779833504913</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.851979487044661</v>
+        <v>2.84819913339435</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.625961766965649</v>
+        <v>-3.743762599633347</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.066865810703119</v>
+        <v>1.019745477636039</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.569584116807594</v>
+        <v>0.5632835273904103</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.859357411887682</v>
+        <v>2.855577058237372</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.70963386367798</v>
+        <v>-3.827434696345679</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.038888267848853</v>
+        <v>0.9917679347817732</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.569584116807594</v>
+        <v>0.5632835273904103</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.86484870771835</v>
+        <v>2.861068354068039</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.737414261579334</v>
+        <v>-3.855215094247032</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.039273310456851</v>
+        <v>0.992152977389771</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.541803718906241</v>
+        <v>0.5355031294890573</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.859677670746076</v>
+        <v>2.855897317095766</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.855794934309472</v>
+        <v>-3.97359576697717</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8302767613654489</v>
+        <v>0.783156428298369</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4745858667552648</v>
+        <v>0.4682852773380811</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.657702679456144</v>
+        <v>2.653922325805834</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.964409012752803</v>
+        <v>-4.082209845420501</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9069807907073222</v>
+        <v>0.8598604576402422</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4745858667552648</v>
+        <v>0.4682852773380811</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.77785234017535</v>
+        <v>2.77407198652504</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.92899997450466</v>
+        <v>-4.046800807172358</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9356574321089024</v>
+        <v>0.8885370990418222</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4745858667552648</v>
+        <v>0.4682852773380811</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.792365366277673</v>
+        <v>2.788585012627363</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.937461143160121</v>
+        <v>-4.055261975827819</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9296924059890865</v>
+        <v>0.8825720729220068</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4661246980998038</v>
+        <v>0.4598241086826201</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.784708106426765</v>
+        <v>2.780927752776455</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.760344813124955</v>
+        <v>-3.878145645792653</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9972679668484554</v>
+        <v>0.9501476337813755</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4661246980998038</v>
+        <v>0.4598241086826201</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.781437135272067</v>
+        <v>2.777656781621757</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.805437057958501</v>
+        <v>-3.923237890626199</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9799144606769503</v>
+        <v>0.9327941276098703</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.404228654930414</v>
+        <v>0.3979280655132303</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.744982901132346</v>
+        <v>2.741202547482036</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.626061636719733</v>
+        <v>-3.743862469387431</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.045451604478872</v>
+        <v>0.9983312714117918</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5610054131011326</v>
+        <v>0.5547048236839489</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.832835931341192</v>
+        <v>2.829055577690882</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.671075850240339</v>
+        <v>-3.788876682908037</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.008253374402219</v>
+        <v>0.9611330413351391</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.530656517786528</v>
+        <v>0.5243559283693443</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.795434049484019</v>
+        <v>2.791653695833709</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.938080360512775</v>
+        <v>-4.055881193180473</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9071431326321906</v>
+        <v>0.8600227995651106</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3362934797435794</v>
+        <v>0.3299928903263957</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.684507788997196</v>
+        <v>2.680727435346885</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.039278141949947</v>
+        <v>-4.157078974617646</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8658679419538229</v>
+        <v>0.8187476088867429</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2678846661982602</v>
+        <v>0.2615840767810765</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.642666422766506</v>
+        <v>2.638886069116195</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.032767175335635</v>
+        <v>-4.150568008003333</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8660722901538647</v>
+        <v>0.8189519570867847</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2678846661982602</v>
+        <v>0.2615840767810765</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.640266384320822</v>
+        <v>2.636486030670512</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.013729047628337</v>
+        <v>-4.131529880296036</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8702122604450286</v>
+        <v>0.8230919273779485</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2097010548670657</v>
+        <v>0.203400465449882</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.601880936730351</v>
+        <v>2.59810058308004</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.066244849903158</v>
+        <v>-4.184045682570856</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9685003411692907</v>
+        <v>0.9213800081022108</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2097010548670657</v>
+        <v>0.203400465449882</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.721175338364541</v>
+        <v>2.717394984714231</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.069653161337738</v>
+        <v>-4.187453994005436</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9679703455815925</v>
+        <v>0.9208500125145123</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2422176238764431</v>
+        <v>0.2359170344592594</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.741518608756301</v>
+        <v>2.737738255105991</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.05029702544389</v>
+        <v>-4.168097858111588</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9817213303360572</v>
+        <v>0.9346009972689773</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2422176238764431</v>
+        <v>0.2359170344592594</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.747527139153227</v>
+        <v>2.743746785502917</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.123626554181983</v>
+        <v>-4.241427386849681</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8503397401180197</v>
+        <v>0.8032194070509397</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.242612286296065</v>
+        <v>0.2363116968788813</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.645714157882199</v>
+        <v>2.641933804231889</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.207447775456681</v>
+        <v>-4.32524860812438</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8196048731396213</v>
+        <v>0.7724845400725413</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.242612286296065</v>
+        <v>0.2363116968788813</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.64850777941368</v>
+        <v>2.64472742576337</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.503602756027699</v>
+        <v>2.501473645662264</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.201295069403897</v>
+        <v>-4.319095902071595</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8227283039523934</v>
+        <v>0.7734788605198779</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2487649923488493</v>
+        <v>0.2424644029316656</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.652861751437009</v>
+        <v>2.646952287421263</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.500554122402374</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.218104367554399</v>
+        <v>-4.335905200222097</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8150850614323029</v>
+        <v>0.7658356179997874</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2319556941983477</v>
+        <v>0.225655104781164</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.641856649286819</v>
+        <v>2.635947185271073</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.566889676199195</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.155806368778276</v>
+        <v>-4.273607201445975</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9063398147395727</v>
+        <v>0.8570903713070572</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2772499584727897</v>
+        <v>0.270949369055606</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.735368761648305</v>
+        <v>2.729459297632559</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.369181677913322</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.954016171113119</v>
+        <v>-4.071817003780817</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.789347895519763</v>
+        <v>0.7400984520872473</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4752681506419441</v>
+        <v>0.4689675612247604</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.656471678663924</v>
+        <v>2.650562214648179</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.439471910235497</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.004902883799313</v>
+        <v>-4.122703716467012</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8392834427674603</v>
+        <v>0.7900339993349448</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4243814379557496</v>
+        <v>0.4180808485385659</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.696229883374383</v>
+        <v>2.690320419358637</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.454099646351541</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.918292141149506</v>
+        <v>-4.036092973817205</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8885554759434269</v>
+        <v>0.8393060325109112</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5030071691609078</v>
+        <v>0.4967065797437241</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.758033058213521</v>
+        <v>2.752123594197776</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.452635627176213</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.97850143915479</v>
+        <v>-4.09630227182249</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8630077375659848</v>
+        <v>0.8137582941334689</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4427978711556233</v>
+        <v>0.4364972817384396</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.720443460235022</v>
+        <v>2.714533996219277</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.451127245216141</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.929314790470439</v>
+        <v>-4.047115623138138</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8811740150796539</v>
+        <v>0.831924571647138</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4427978711556233</v>
+        <v>0.4364972817384396</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.718935078274951</v>
+        <v>2.713025614259205</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.450990112651577</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.88494165883187</v>
+        <v>-4.00274249149957</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8987861351705175</v>
+        <v>0.8495366917380016</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4871710027941919</v>
+        <v>0.4808704133770082</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.745421824693528</v>
+        <v>2.739512360677783</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.445383906790168</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.850210337513369</v>
+        <v>-3.968011170181069</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9070724578365084</v>
+        <v>0.8578230144039924</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4871710027941919</v>
+        <v>0.4808704133770082</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.739815618832119</v>
+        <v>2.733906154816373</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.451765663817972</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.802554606952314</v>
+        <v>-3.920355439620013</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9325165070887351</v>
+        <v>0.883267063656219</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5348267333552476</v>
+        <v>0.5285261439380639</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.774790814196557</v>
+        <v>2.76888135018081</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.456658037192697</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.702036448453559</v>
+        <v>-3.819837281121258</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9776161438629618</v>
+        <v>0.9283667004304457</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6353448918540021</v>
+        <v>0.6290443024368184</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.839994082670534</v>
+        <v>2.834084618654788</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.443412709668569</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.686131119021207</v>
+        <v>-3.803931951688906</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9707329481117752</v>
+        <v>0.9214835046792589</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5562322311447632</v>
+        <v>0.5499316417275795</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.779281158720863</v>
+        <v>2.773371694705117</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.447510412279198</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.641292717412809</v>
+        <v>-3.759093550080508</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.992766011365763</v>
+        <v>0.9435165679332467</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5607756640896326</v>
+        <v>0.5544750746724489</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.786104921098413</v>
+        <v>2.780195457082667</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.451671351910276</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.660791173654817</v>
+        <v>-3.778592006322516</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9891275685000376</v>
+        <v>0.9398781250675214</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5126910228097283</v>
+        <v>0.5063904333925446</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.761415075961549</v>
+        <v>2.755505611945803</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.457550954438113</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.616588336568916</v>
+        <v>-3.734389169236616</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.012688305862235</v>
+        <v>0.9634388624297188</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5568938598956288</v>
+        <v>0.5505932704784451</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.793816380740926</v>
+        <v>2.78790691672518</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.45596095490736</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.624148002405963</v>
+        <v>-3.741948835073662</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.008074439996664</v>
+        <v>0.9588249965641475</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6116972639054481</v>
+        <v>0.6053966744882644</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.825108423616066</v>
+        <v>2.819198959600319</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.5072087200904</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.465856584866691</v>
+        <v>-3.58365741753439</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.122638772195412</v>
+        <v>1.073389328762896</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6116972639054481</v>
+        <v>0.6053966744882644</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.876356188799105</v>
+        <v>2.870446724783359</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.505649424684653</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.258214581232215</v>
+        <v>-3.376015413899914</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.204136278243456</v>
+        <v>1.15488683481094</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8193392675399243</v>
+        <v>0.8130386781227406</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.999382095574044</v>
+        <v>2.993472631558298</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.500597652922923</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.207182488509687</v>
+        <v>-3.324983321177386</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.219497343570737</v>
+        <v>1.170247900138221</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8703713602624522</v>
+        <v>0.8640707708452685</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.024949579445831</v>
+        <v>3.019040115430085</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.517785057015628</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.141958307382481</v>
+        <v>-3.25975914005018</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.262774420114325</v>
+        <v>1.213524976681808</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9355955413896578</v>
+        <v>0.9292949519724741</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.081271492214859</v>
+        <v>3.075362028199113</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.513746029314909</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.104531287311347</v>
+        <v>-3.222332119979046</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.273706200442058</v>
+        <v>1.224456757009542</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9408470794188395</v>
+        <v>0.9345464900016558</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.080383387331648</v>
+        <v>3.074473923315902</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.515002821646149</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.103173302337802</v>
+        <v>-3.220974135005501</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.275506186762717</v>
+        <v>1.226256743330201</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.015185204956658</v>
+        <v>1.008884615539474</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.12624305498558</v>
+        <v>3.120333590969834</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.67556059266736</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.074760039237918</v>
+        <v>-3.192560871905617</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.447429263023881</v>
+        <v>1.398179819591365</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9562096422102293</v>
+        <v>0.9499090527930456</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.251415488358933</v>
+        <v>3.245506024343187</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>2.795673501885177</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.999977778212906</v>
+        <v>-3.117778610880605</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.597455076651703</v>
+        <v>1.548205633219187</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.030991903235242</v>
+        <v>1.024691313818058</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.416397754191758</v>
+        <v>3.410488290176012</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>2.787381477899036</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.973893693949098</v>
+        <v>-3.091694526616797</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.599596686371086</v>
+        <v>1.550347242938569</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.030991903235242</v>
+        <v>1.024691313818058</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.408105730205617</v>
+        <v>3.402196266189871</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>2.785574673482815</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.886015780839977</v>
+        <v>-3.003816613507676</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.632941047198513</v>
+        <v>1.583691603765997</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.146917545658593</v>
+        <v>1.140616956241409</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.475854311243407</v>
+        <v>3.469944847227661</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>2.803129079209607</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.877123319446694</v>
+        <v>-2.994924152114393</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.654052437482618</v>
+        <v>1.604802994050101</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.146917545658593</v>
+        <v>1.140616956241409</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.493408716970199</v>
+        <v>3.487499252954453</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>2.794984126614191</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.045599436416572</v>
+        <v>-3.163400269084271</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.578517038099251</v>
+        <v>1.529267594666734</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.118969709942012</v>
+        <v>1.112669120524828</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.468495062944834</v>
+        <v>3.462585598929088</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79557406678271</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>2.776253823802052</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.599343243787132</v>
+        <v>-2.717144076454831</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.738289212338888</v>
+        <v>1.689039768906372</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.02425104027238</v>
+        <v>1.017950450855196</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.392933558330916</v>
+        <v>3.38702409431517</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>2.766917846298957</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.576622140103979</v>
+        <v>-2.694422972771679</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.738041676309054</v>
+        <v>1.688792232876538</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.02425104027238</v>
+        <v>1.017950450855196</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.383597580827821</v>
+        <v>3.377688116812075</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>2.925823972150126</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.705823953398022</v>
+        <v>-2.823624786065721</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.845267076842606</v>
+        <v>1.79601763341009</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8950492269783374</v>
+        <v>0.8887486375611535</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.464982618702565</v>
+        <v>3.459073154686819</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>2.962901794643773</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.731698351872048</v>
+        <v>-2.849499184539747</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.871995139946642</v>
+        <v>1.822745696514126</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9399608356900786</v>
+        <v>0.9336602462728947</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.529007406423256</v>
+        <v>3.52309794240751</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>2.959577150633318</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.724643661656874</v>
+        <v>-2.842444494324573</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.871492372022257</v>
+        <v>1.822242928589741</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9470155259052524</v>
+        <v>0.9407149364880685</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.529915576541905</v>
+        <v>3.524006112526159</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331118</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>2.969583304278059</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.697692437330386</v>
+        <v>-2.815493269998085</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.892279015397593</v>
+        <v>1.843029571965077</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9618958719329715</v>
+        <v>0.9555952825157876</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.548849937803278</v>
+        <v>3.542940473787532</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.153686436423019</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.719236665161173</v>
+        <v>-2.837037497828872</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.067764456410238</v>
+        <v>2.018515012977722</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9618958719329715</v>
+        <v>0.9555952825157876</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.732953069948238</v>
+        <v>3.727043605932492</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.145803131326012</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.741644782966045</v>
+        <v>-2.859445615633744</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.050917904191283</v>
+        <v>2.001668460758767</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9618958719329715</v>
+        <v>0.9555952825157876</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.725069764851231</v>
+        <v>3.719160300835485</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.14785713087565</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.769869018543646</v>
+        <v>-2.887669851211345</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.04168220950988</v>
+        <v>1.992432766077364</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9798726243842801</v>
+        <v>0.9735720349670962</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.737909815871654</v>
+        <v>3.732000351855907</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.204110848597497</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.779309944432176</v>
+        <v>-2.897110777099875</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.094159556876315</v>
+        <v>2.044910113443799</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.102299741927672</v>
+        <v>1.095999152510488</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.867619804119536</v>
+        <v>3.86171034010379</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.207001943142798</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.868186575600649</v>
+        <v>-2.985987408268349</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.061499998954226</v>
+        <v>2.01225055552171</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.013423110759198</v>
+        <v>1.007122521342014</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.817184919963752</v>
+        <v>3.811275455948006</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.205113756036573</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.944516553201555</v>
+        <v>-3.062317385869255</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.029079820807639</v>
+        <v>1.979830377375123</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.013423110759198</v>
+        <v>1.007122521342014</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.815296732857528</v>
+        <v>3.809387268841781</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.199933985639435</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.099473338601685</v>
+        <v>-3.217274171269384</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.96191733625045</v>
+        <v>1.912667892817934</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8584663253590685</v>
+        <v>0.8521657359418846</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.717142891220313</v>
+        <v>3.711233427204566</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.198367995849587</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.26104176412894</v>
+        <v>-3.378842596796639</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.8957239762497</v>
+        <v>1.846474532817184</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7316834015611892</v>
+        <v>0.7253828121440052</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.639507147151737</v>
+        <v>3.633597683135991</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.211441402715506</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.369342425999059</v>
+        <v>-3.487143258666758</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.865477118367571</v>
+        <v>1.816227674935055</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7316834015611892</v>
+        <v>0.7253828121440052</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.652580554017656</v>
+        <v>3.646671090001909</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.203446599498446</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.387146397719803</v>
+        <v>-3.504947230387502</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.850360726462213</v>
+        <v>1.801111283029697</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.661148778655988</v>
+        <v>0.6548481892388041</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.602264977057475</v>
+        <v>3.596355513041729</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.201970640625448</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.415047184829276</v>
+        <v>-3.532848017496975</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.837724452745426</v>
+        <v>1.78847500931291</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6265518545130532</v>
+        <v>0.6202512650958693</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.580030863698716</v>
+        <v>3.57412139968297</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.198735084602647</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.53757328753217</v>
+        <v>-3.655374120199869</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.785478455641467</v>
+        <v>1.736229012208951</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5040257518101593</v>
+        <v>0.4977251623929754</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.503279646054179</v>
+        <v>3.497370182038432</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.265441044193151</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.768087783717759</v>
+        <v>-3.885888616385458</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.759978616757736</v>
+        <v>1.710729173325219</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2735112556245706</v>
+        <v>0.2672106662073866</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.431676907933329</v>
+        <v>3.425767443917583</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.405752763194998</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.116832868942202</v>
+        <v>-4.234633701609901</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.760792301669805</v>
+        <v>1.711542858237289</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1647633017056728</v>
+        <v>0.1584627122884888</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.506739854583838</v>
+        <v>3.500830390568091</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.474733032340637</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.270819286718343</v>
+        <v>-4.388620119386042</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.768178003704989</v>
+        <v>1.718928560272473</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1647633017056728</v>
+        <v>0.1584627122884888</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.575720123729477</v>
+        <v>3.569810659713731</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.460784234460758</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.475418721581351</v>
+        <v>-4.593219554249051</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.672389431879906</v>
+        <v>1.62313998844739</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1647633017056728</v>
+        <v>0.1584627122884888</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.561771325849598</v>
+        <v>3.555861861833852</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.472654723516172</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.727893875589076</v>
+        <v>-4.845694708256775</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.583269859332231</v>
+        <v>1.534020415899714</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1647633017056728</v>
+        <v>0.1584627122884888</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.573641814905012</v>
+        <v>3.567732350889266</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.473865258035116</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.020789632068488</v>
+        <v>-5.138590464736187</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.46732209125941</v>
+        <v>1.418072647826893</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1647633017056728</v>
+        <v>0.1584627122884888</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.574852349423956</v>
+        <v>3.56894288540821</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.477987000262437</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.207453760203296</v>
+        <v>-5.325254592870995</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.396778182232808</v>
+        <v>1.347528738800291</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1380243308811129</v>
+        <v>0.131723741463929</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.562930709156541</v>
+        <v>3.557021245140795</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.473064852998627</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.353474447117258</v>
+        <v>-5.471275279784957</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.333447760203412</v>
+        <v>1.284198316770896</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1289412390872559</v>
+        <v>0.122640649670072</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.552558706816416</v>
+        <v>3.54664924280067</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.635268909697671</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.445188456226843</v>
+        <v>-5.562989288894542</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.458966213258623</v>
+        <v>1.409716769826106</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1289412390872559</v>
+        <v>0.122640649670072</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.714762763515461</v>
+        <v>3.708853299499714</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.630115547661485</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.476840115286812</v>
+        <v>-5.594640947954511</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.441152187598449</v>
+        <v>1.391902744165932</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1237727818428157</v>
+        <v>0.1174721924256318</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.706508327132611</v>
+        <v>3.700598863116864</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.640344965229976</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.545906169859749</v>
+        <v>-5.663707002527448</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.423755183337765</v>
+        <v>1.374505739905249</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.06140190434920567</v>
+        <v>0.05510131493202175</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.679315218204936</v>
+        <v>3.67340575418919</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.649270603685879</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.647882292108156</v>
+        <v>-5.765683124775856</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.391890372894305</v>
+        <v>1.342640929461788</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0405742178992019</v>
+        <v>-0.04687480731638582</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.627055183311794</v>
+        <v>3.621145719296047</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.79829678423181</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.641423490930054</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.537876008630935</v>
+        <v>-5.655676841298634</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.428045773529369</v>
+        <v>1.378796330096852</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.0173696459819267</v>
+        <v>-0.02367023539911062</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.633130813706334</v>
+        <v>3.627221349690588</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.645673501652028</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.394816432890009</v>
+        <v>-5.512617265557708</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.489519614547714</v>
+        <v>1.440270171115197</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.009356219391947418</v>
+        <v>-0.01565680880913134</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.642188880382296</v>
+        <v>3.63627941636655</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.652934384534564</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.093369707418171</v>
+        <v>-5.21117054008587</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.617359187618984</v>
+        <v>1.568109744186468</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2920905060798898</v>
+        <v>0.2857899166627059</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.830317798547934</v>
+        <v>3.824408334532188</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.653905562287275</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.117959951653355</v>
+        <v>-5.235760784321054</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.608494267677622</v>
+        <v>1.559244824245105</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2920905060798898</v>
+        <v>0.2857899166627059</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.831288976300645</v>
+        <v>3.825379512284899</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.65474846666703</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.066921575646835</v>
+        <v>-5.184722408314534</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.629752522459985</v>
+        <v>1.580503079027469</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2920905060798898</v>
+        <v>0.2857899166627059</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.832131880680401</v>
+        <v>3.826222416664654</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.673786565541176</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.038072898823375</v>
+        <v>-5.155873731491074</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.660330092063515</v>
+        <v>1.611080648630999</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3209391829033501</v>
+        <v>0.3146385934861662</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.868479185648622</v>
+        <v>3.862569721632876</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.48997056166511</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.941437986804734</v>
+        <v>-5.059238819472434</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.515168052994905</v>
+        <v>1.465918609562389</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.41757409492199</v>
+        <v>0.4112735055048061</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.74264412898374</v>
+        <v>3.736734664967994</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077642</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.493472605739075</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.872399975856267</v>
+        <v>-4.990200808523966</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.546285301448257</v>
+        <v>1.49703585801574</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4866121058704581</v>
+        <v>0.4803115164532742</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.787568979626786</v>
+        <v>3.78165951561104</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083346</v>
+        <v>3.775028860833461</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.477899424815157</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.707903641665305</v>
+        <v>-4.825704474333004</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.596510654200724</v>
+        <v>1.547261210768208</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.65110844006142</v>
+        <v>0.6448078506442361</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.870693599217445</v>
+        <v>3.864784135201699</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.82103066007763</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.477087135251587</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.630805040123432</v>
+        <v>-4.748605872791131</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.626537805253903</v>
+        <v>1.577288361821386</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.65110844006142</v>
+        <v>0.6448078506442361</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.869881309653875</v>
+        <v>3.863971845638129</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147911</v>
+        <v>3.832307024147912</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.486955914376659</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.641190235013322</v>
+        <v>-4.758991067681021</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.632252506423019</v>
+        <v>1.583003062990503</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6407232451715307</v>
+        <v>0.6344226557543468</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.873518971845014</v>
+        <v>3.867609507829267</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735284</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.557792920153084</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.659778393735547</v>
+        <v>-4.777579226403246</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.695654248710555</v>
+        <v>1.646404805278038</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6221350864493054</v>
+        <v>0.6158344970321215</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.933203082388104</v>
+        <v>3.927293618372357</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.554661930971383</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.660076940431582</v>
+        <v>-4.777877773099282</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.692403840850439</v>
+        <v>1.643154397417922</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6218365397532695</v>
+        <v>0.6155359503360855</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.929892965188781</v>
+        <v>3.923983501173034</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108859</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.559192825910774</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.559253806741155</v>
+        <v>-4.677054639408854</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.737263989266001</v>
+        <v>1.688014545833485</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6343007552376233</v>
+        <v>0.6280001658204394</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.941902389418784</v>
+        <v>3.935992925403038</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.559322079389318</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.368472445988747</v>
+        <v>-4.486273278656446</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.813705787045508</v>
+        <v>1.764456343612991</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8250821159900307</v>
+        <v>0.8187815265728468</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.056500459348772</v>
+        <v>4.050590995333026</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.539158925126914</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.261509088139325</v>
+        <v>-4.379309920807025</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.836327975922873</v>
+        <v>1.787078532490356</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8835467239498321</v>
+        <v>0.8772461345326482</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.071416069862249</v>
+        <v>4.065506605846504</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.574125861738973</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.206178500237563</v>
+        <v>-4.323979332905262</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.893427147695636</v>
+        <v>1.84417770426312</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9388773118515943</v>
+        <v>0.9325767224344104</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.139581359215366</v>
+        <v>4.133671895199619</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.56781242964041</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.1941243733246</v>
+        <v>-4.311925205992299</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.891935366362259</v>
+        <v>1.842685922929743</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9509314387645571</v>
+        <v>0.9446308493473732</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.140500403264581</v>
+        <v>4.134590939248834</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.569693059824546</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.235279492892821</v>
+        <v>-4.35308032556052</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.877353948719106</v>
+        <v>1.82810450528659</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9097763191963362</v>
+        <v>0.9034757297791522</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.117687961707784</v>
+        <v>4.111778497692038</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.582544085702429</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.167230930201291</v>
+        <v>-4.28503176286899</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.917424399673601</v>
+        <v>1.868174956241085</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.977824881887866</v>
+        <v>0.9715242924706821</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.171368125200584</v>
+        <v>4.165458661184838</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013427</v>
+        <v>3.645256780013429</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.602746755876023</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.398831323370792</v>
+        <v>-4.516632156038491</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.844986912579395</v>
+        <v>1.795737469146879</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.977824881887866</v>
+        <v>0.9715242924706821</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.191570795374179</v>
+        <v>4.185661331358432</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.586352991942905</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.448882868900011</v>
+        <v>-4.56668370156771</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.808572530434589</v>
+        <v>1.759323087002073</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.977824881887866</v>
+        <v>0.9715242924706821</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.175177031441061</v>
+        <v>4.169267567425314</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.546604905536372</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.623989701476455</v>
+        <v>-4.741790534144155</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.698781710997478</v>
+        <v>1.649532267564962</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.977824881887866</v>
+        <v>0.9715242924706821</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.135428945034527</v>
+        <v>4.129519481018781</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660853</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.553627524533312</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.427889548045933</v>
+        <v>-4.545690380713632</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.784244391366627</v>
+        <v>1.734994947934111</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.173925035318389</v>
+        <v>1.167624445901205</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.260111656089781</v>
+        <v>4.254202192074034</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395089</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.652798524106216</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.274864155932648</v>
+        <v>-4.392664988600347</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.944625547784845</v>
+        <v>1.895376104352329</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.326950427431673</v>
+        <v>1.320649838014489</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.451097890930656</v>
+        <v>4.44518842691491</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791152</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.840264749014509</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.303171469805918</v>
+        <v>-4.420972302473618</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.12076884714383</v>
+        <v>2.071519403711314</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.326950427431673</v>
+        <v>1.320649838014489</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.638564115838949</v>
+        <v>4.632654651823202</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620436</v>
+        <v>3.699115615620438</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.809667700368591</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.469764694919441</v>
+        <v>-4.58756552758714</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.023534508452504</v>
+        <v>1.974285065019987</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.16035720231815</v>
+        <v>1.154056612900966</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.508011132124918</v>
+        <v>4.502101668109171</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285649</v>
+        <v>3.708182519285651</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.813344103030309</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.446728901557875</v>
+        <v>-4.564529734225574</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.036425228458848</v>
+        <v>1.987175785026332</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.16035720231815</v>
+        <v>1.154056612900966</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.511687534786636</v>
+        <v>4.505778070770889</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399472</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.810962158153804</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.417482921102178</v>
+        <v>-4.535283753769877</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.045741675764622</v>
+        <v>1.996492232332105</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.16035720231815</v>
+        <v>1.154056612900966</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.509305589910131</v>
+        <v>4.503396125894384</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256373</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.808255397311439</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.524408468980029</v>
+        <v>-4.642209301647728</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.000264695771116</v>
+        <v>1.9510152523386</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.053431654440299</v>
+        <v>1.047131065023115</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.442443500341055</v>
+        <v>4.436534036325309</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701002</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.809684199454674</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.669427027487278</v>
+        <v>-4.787227860154977</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.943686074511451</v>
+        <v>1.894436631078935</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9084130959330505</v>
+        <v>0.9021125065158666</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.35686116737994</v>
+        <v>4.350951703364194</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687014</v>
+        <v>3.711852429687016</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.909615438712426</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.787768793271995</v>
+        <v>-4.905569625939695</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.996280607455317</v>
+        <v>1.947031164022801</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9190991344959406</v>
+        <v>0.9127985450787567</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.463204029775427</v>
+        <v>4.457294565759681</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790804</v>
+        <v>3.714879051790806</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.907401135838366</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.839179215592703</v>
+        <v>-4.956980048260403</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.973502135652973</v>
+        <v>1.924252692220457</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9190991344959406</v>
+        <v>0.9127985450787567</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.460989726901366</v>
+        <v>4.45508026288562</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437332</v>
+        <v>3.704757949437334</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.907304263912655</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.918598666800455</v>
+        <v>-5.036399499468154</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.941637483244161</v>
+        <v>1.892388039811645</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9190991344959406</v>
+        <v>0.9127985450787567</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.460892854975655</v>
+        <v>4.454983390959909</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.7368049522984</v>
+        <v>3.736804952298402</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.907298157470698</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.014061664717673</v>
+        <v>-5.131862497385372</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.903446177635317</v>
+        <v>1.854196734202801</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9190991344959406</v>
+        <v>0.9127985450787567</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.460886748533698</v>
+        <v>4.454977284517952</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218002</v>
+        <v>3.715372960218004</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.905394554033308</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.949685753866958</v>
+        <v>-5.067486586534657</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.927292938538214</v>
+        <v>1.878043495105698</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.9834750453466558</v>
+        <v>0.9771744559294718</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.497608691606738</v>
+        <v>4.491699227590992</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353538</v>
+        <v>3.73608941335354</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.911128371781035</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.005054915999152</v>
+        <v>-5.122855748666851</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.910879091433063</v>
+        <v>1.861629648000547</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.9834750453466558</v>
+        <v>0.9771744559294718</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.503342509354464</v>
+        <v>4.497433045338719</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113281</v>
+        <v>3.736822870113283</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.910666735123967</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.02327338299676</v>
+        <v>-5.141074215664459</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.903130067976952</v>
+        <v>1.853880624544436</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9583686080908136</v>
+        <v>0.9520680186736297</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.487817010343892</v>
+        <v>4.481907546328145</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79027250011369</v>
+        <v>3.790272500113692</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.930541127974286</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.935066548849182</v>
+        <v>-5.052867381516881</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.958287194486302</v>
+        <v>1.909037751053785</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9583686080908136</v>
+        <v>0.9520680186736297</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.507691403194211</v>
+        <v>4.501781939178464</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016443</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.914241828499014</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.829031553643873</v>
+        <v>-4.946832386311572</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.984401893093153</v>
+        <v>1.935152449660637</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9583686080908136</v>
+        <v>0.9520680186736297</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.491392103718939</v>
+        <v>4.485482639703192</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.794705093307674</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.91667277796306</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.645819890510777</v>
+        <v>-4.763620723178477</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.060117507810437</v>
+        <v>2.010868064377921</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9583686080908136</v>
+        <v>0.9520680186736297</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.493823053182984</v>
+        <v>4.487913589167238</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863555</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.901746294407872</v>
+        <v>3.899617184042437</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.574098443496927</v>
+        <v>-4.691899276164626</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.071750492695354</v>
+        <v>2.022501049262839</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.030090055104664</v>
+        <v>1.02378946568748</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.519800327470671</v>
+        <v>4.513890863454925</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.848662040329044</v>
+        <v>3.846532929963609</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.55172541788922</v>
+        <v>-4.669526250556919</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.027615448859609</v>
+        <v>1.978366005427093</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.041345806217566</v>
+        <v>1.035045216800382</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.473469524059584</v>
+        <v>4.467560060043838</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456733</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.0338602452144</v>
+        <v>4.031731134848964</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.584741713799965</v>
+        <v>-4.702542546467664</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.199607135380666</v>
+        <v>2.15035769194815</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.9719084295508142</v>
+        <v>0.9656078401336303</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.617005302944889</v>
+        <v>4.611095838929142</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71376253688368</v>
+        <v>3.713762536883682</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.025781471042649</v>
+        <v>4.023652360677213</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.573214078150357</v>
+        <v>-4.691014910818056</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.196139415468759</v>
+        <v>2.146889972036242</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.030909087752177</v>
+        <v>1.024608498334993</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.644326923693955</v>
+        <v>4.638417459678209</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.7171506992363</v>
+        <v>3.717150699236302</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.029449583564437</v>
+        <v>4.027320473199001</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.670555579492725</v>
+        <v>-4.788356412160424</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.1608709274536</v>
+        <v>2.111621484021084</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.9864889055866883</v>
+        <v>0.9801883161695044</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.621342926916451</v>
+        <v>4.615433462900704</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.705201079427688</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.030700665757275</v>
+        <v>4.02857155539184</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.756411608832692</v>
+        <v>-4.874212441500391</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.127779597910451</v>
+        <v>2.078530154477935</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9441128363605533</v>
+        <v>0.9378122469433694</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.597168367573608</v>
+        <v>4.591258903557861</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610385</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.013119867577777</v>
+        <v>4.010990757212341</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.765248406248811</v>
+        <v>-4.88304923891651</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.106664080764506</v>
+        <v>2.057414637331989</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.9366706637192026</v>
+        <v>0.9303700743020187</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.575122265809299</v>
+        <v>4.569212801793553</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667457</v>
+        <v>3.715544411667459</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.023284378622827</v>
+        <v>4.021155268257391</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.85663096881427</v>
+        <v>-4.974431801481969</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.080275566783372</v>
+        <v>2.031026123350856</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9001057789998579</v>
+        <v>0.893805189582674</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.563347846022742</v>
+        <v>4.557438382006995</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889194</v>
+        <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.125412636447095</v>
+        <v>4.123283526081659</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.844924250827264</v>
+        <v>-4.962725083494963</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.187086511802442</v>
+        <v>2.137837068369926</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9118124969868643</v>
+        <v>0.9055119075696804</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.672500134639214</v>
+        <v>4.666590670623467</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940957</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.1284449751785</v>
+        <v>4.126315864813064</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.915836324569542</v>
+        <v>-5.033637157237241</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.161754021036936</v>
+        <v>2.112504577604419</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9118124969868643</v>
+        <v>0.9055119075696804</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.675532473370619</v>
+        <v>4.669623009354872</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452574</v>
+        <v>3.672895177452575</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.341349808456558</v>
+        <v>4.339220698091122</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.926152422735893</v>
+        <v>-5.043953255403593</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.370532415048453</v>
+        <v>2.321282971615937</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9118124969868643</v>
+        <v>0.9055119075696804</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.888437306648677</v>
+        <v>4.88252784263293</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.62396095976229</v>
+        <v>3.623960959762292</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.340528475368647</v>
+        <v>4.338399365003212</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.926058454718521</v>
+        <v>-5.04385928738622</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.369748669167492</v>
+        <v>2.320499225734975</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9121823583341823</v>
+        <v>0.9058817689169983</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.887837890369157</v>
+        <v>4.881928426353411</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.63321346798802</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.334760461313001</v>
+        <v>4.332631350947565</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.074424682374666</v>
+        <v>-5.192225515042365</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.304634164049388</v>
+        <v>2.255384720616871</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9121823583341823</v>
+        <v>0.9058817689169983</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.882069876313511</v>
+        <v>4.876160412297764</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740924</v>
+        <v>3.647907242740926</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.334760461313001</v>
+        <v>4.332631350947565</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.073476259256627</v>
+        <v>-5.191277091924326</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.305013533296603</v>
+        <v>2.255764089864087</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9121823583341823</v>
+        <v>0.9058817689169983</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.882069876313511</v>
+        <v>4.876160412297764</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663629</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.347488069294093</v>
+        <v>4.345358958928657</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.173746077215648</v>
+        <v>-5.291546909883348</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.277633214094087</v>
+        <v>2.228383770661571</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9121823583341823</v>
+        <v>0.9058817689169983</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.894797484294603</v>
+        <v>4.888888020278856</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.717071158424773</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.349434067718481</v>
+        <v>4.347304957353045</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.167753830426837</v>
+        <v>-5.285554663094536</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.281976111233999</v>
+        <v>2.232726667801483</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9121823583341823</v>
+        <v>0.9058817689169983</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.896743482718991</v>
+        <v>4.890834018703244</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149219</v>
+        <v>3.741942347149221</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.34308820373625</v>
+        <v>4.340959093370814</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.079195869296069</v>
+        <v>-5.196996701963768</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.311053431704075</v>
+        <v>2.261803988271559</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9121823583341823</v>
+        <v>0.9058817689169983</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.89039761873676</v>
+        <v>4.884488154721013</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383093</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.342396881175246</v>
+        <v>4.34026777080981</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.061436791792995</v>
+        <v>-5.179237624460694</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.3174657401443</v>
+        <v>2.268216296711784</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9121823583341823</v>
+        <v>0.9058817689169983</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.889706296175755</v>
+        <v>4.883796832160009</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720999</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.355179067083832</v>
+        <v>4.353049956718396</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.961806640743927</v>
+        <v>-5.079607473411627</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.370099986472514</v>
+        <v>2.320850543039998</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.01181250938325</v>
+        <v>1.005511919966066</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.962266572713783</v>
+        <v>4.956357108698036</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455272</v>
+        <v>3.775357097455274</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.544333332582559</v>
+        <v>4.542204222217123</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.011206149432939</v>
+        <v>-5.129006982100638</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.539494448495636</v>
+        <v>2.49024500506312</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.022071342814995</v>
+        <v>1.015770753397811</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.157576138271556</v>
+        <v>5.151666674255809</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963134</v>
+        <v>3.749078058963136</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.531522005685421</v>
+        <v>4.529392895319985</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.804521675790562</v>
+        <v>-4.922322508458262</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.609356911055449</v>
+        <v>2.560107467622932</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.22875581645737</v>
+        <v>1.222455227040186</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.268775495559844</v>
+        <v>5.262866031544097</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162544</v>
+        <v>3.740284389162546</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.533523519339526</v>
+        <v>4.53139440897409</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.838678570788089</v>
+        <v>-5.018045329943249</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.597695666710543</v>
+        <v>2.523819852683042</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.145172046916558</v>
+        <v>1.158229532951346</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.220626747489461</v>
+        <v>5.226332128744898</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652384</v>
+        <v>3.782482115652386</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.887020633329193</v>
+        <v>4.884891522963757</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.746089091726632</v>
+        <v>-4.925455850881792</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.988228572324793</v>
+        <v>2.914352758297293</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.145172046916558</v>
+        <v>1.158229532951346</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.574123861479128</v>
+        <v>5.579829242734565</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108674</v>
+        <v>3.809055905108676</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.891583744896296</v>
+        <v>4.88945463453086</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.805977719550182</v>
+        <v>-4.985344478705342</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.968836232762476</v>
+        <v>2.894960418734976</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.131050132229093</v>
+        <v>1.144107618263882</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.570213824233752</v>
+        <v>5.57591920548919</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103566</v>
+        <v>3.835202441103568</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.941413686219824</v>
+        <v>4.939284575854388</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.753761409753841</v>
+        <v>-4.933128168909001</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.03955269800454</v>
+        <v>2.96567688397704</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.131050132229093</v>
+        <v>1.144107618263882</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.62004376555728</v>
+        <v>5.625749146812717</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047747</v>
+        <v>3.821827147047749</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.950227656429835</v>
+        <v>4.948098546064399</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.721863892668595</v>
+        <v>-4.901230651823755</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.06112567504865</v>
+        <v>2.987249861021149</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.162947649314339</v>
+        <v>1.176005135349128</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.647996246018439</v>
+        <v>5.653701627273875</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650757</v>
+        <v>3.825268416650759</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.945865240469032</v>
+        <v>4.943736130103596</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.736619216868736</v>
+        <v>-4.915985976023896</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.050861129407791</v>
+        <v>2.97698531538029</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.162947649314339</v>
+        <v>1.176005135349128</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.643633830057635</v>
+        <v>5.649339211313072</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135752</v>
+        <v>3.845044666135753</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.936789743885312</v>
+        <v>4.934660633519876</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.687154593498824</v>
+        <v>-4.866521352653984</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.061571482172035</v>
+        <v>2.987695668144534</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.212412272684251</v>
+        <v>1.225469758719039</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.664237107495862</v>
+        <v>5.6699424887513</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479225</v>
+        <v>3.825931790479227</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.933197411600246</v>
+        <v>4.93106830123481</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.524046601345209</v>
+        <v>-4.703413360500369</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.123222346748415</v>
+        <v>3.049346532720915</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.375520264837866</v>
+        <v>1.388577750872654</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.758509570502966</v>
+        <v>5.764214951758403</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844247</v>
+        <v>3.847096478844248</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.942244448291374</v>
+        <v>4.940115337925938</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.391238975848042</v>
+        <v>-4.570605735003202</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.18539243363841</v>
+        <v>3.11151661961091</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.375520264837866</v>
+        <v>1.388577750872654</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.767556607194094</v>
+        <v>5.773261988449532</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.83242598779095</v>
+        <v>3.832425987790952</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.943101913277496</v>
+        <v>4.94097280291206</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.4539468923226</v>
+        <v>-4.63331365147776</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.161166732034709</v>
+        <v>3.087290918007208</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.312812348363308</v>
+        <v>1.325869834398097</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.730789322295481</v>
+        <v>5.736494703550918</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578996</v>
+        <v>3.861579399578998</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.906011330067848</v>
+        <v>4.903882219702412</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.405938768478907</v>
+        <v>-4.585305527634067</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.143279398362538</v>
+        <v>3.069403584335038</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.312812348363308</v>
+        <v>1.325869834398097</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.693698739085833</v>
+        <v>5.699404120341271</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629888</v>
+        <v>3.872253907629887</v>
       </c>
       <c r="C2100" t="n">
-        <v>4.909943583625799</v>
+        <v>4.907814473260363</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.327113111295317</v>
+        <v>-4.506479870450477</v>
       </c>
       <c r="E2100" t="n">
-        <v>3.178741914793925</v>
+        <v>3.104866100766424</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.391638005546898</v>
+        <v>1.404695491581687</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.744926386953938</v>
+        <v>5.750631768209375</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.889937278966912</v>
+        <v>3.901103310085938</v>
       </c>
       <c r="C2101" t="n">
-        <v>4.904842676232835</v>
+        <v>4.909197526489375</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.31751401018758</v>
+        <v>-4.451884948056121</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.177480647844056</v>
+        <v>3.128087122953178</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.391638005546898</v>
+        <v>1.387628465380792</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.739825479560975</v>
+        <v>5.74177460571785</v>
       </c>
     </row>
   </sheetData>
